--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13095" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13224" uniqueCount="1011">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:48:48+00:00</t>
+    <t>2026-03-19T07:57:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2130,6 +2130,40 @@
     <t>Indicates the context of the order details by reference.</t>
   </si>
   <si>
+    <t>ServiceRequest.orderDetail.parameterFocus.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameterFocus.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameterFocus.concept</t>
+  </si>
+  <si>
+    <t>Reference to a concept (by class)</t>
+  </si>
+  <si>
+    <t>A reference to a concept - e.g. the information is identified by its general class to the degree of precision found in the terminology.</t>
+  </si>
+  <si>
+    <t>CodeableReference.concept</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameterFocus.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference
+</t>
+  </si>
+  <si>
+    <t>Reference to a resource (by instance)</t>
+  </si>
+  <si>
+    <t>A reference to a resource the provides exact details about the information being referenced.</t>
+  </si>
+  <si>
+    <t>CodeableReference.reference</t>
+  </si>
+  <si>
     <t>ServiceRequest.orderDetail.parameter</t>
   </si>
   <si>
@@ -2167,7 +2201,7 @@
   </si>
   <si>
     <t>Quantity
-CodeableConcept</t>
+CodeableConceptstring</t>
   </si>
   <si>
     <t>The value for the order detail</t>
@@ -2614,8 +2648,11 @@
     <t>Specimen.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">PractitionerRole {http://hl7.no/fhir/ig/ParekIG/StructureDefinition/parek-collector-pr}
-</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PractitionerRole {http://hl7.no/fhir/ig/ParekIG/StructureDefinition/parek-collector-pr}
+Device {http://hl7.no/fhir/ig/ParekIG/StructureDefinition/parek-device}</t>
   </si>
   <si>
     <t>Specimen.extension</t>
@@ -4081,7 +4118,7 @@
         <v>2</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
     </row>
     <row r="108">
@@ -4089,7 +4126,7 @@
         <v>4</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>816</v>
+        <v>827</v>
       </c>
     </row>
     <row r="109">
@@ -4105,7 +4142,7 @@
         <v>8</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>817</v>
+        <v>828</v>
       </c>
     </row>
     <row r="111">
@@ -4165,7 +4202,7 @@
         <v>22</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>818</v>
+        <v>829</v>
       </c>
     </row>
     <row r="119">
@@ -4201,7 +4238,7 @@
         <v>29</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>819</v>
+        <v>830</v>
       </c>
     </row>
     <row r="124">
@@ -4209,7 +4246,7 @@
         <v>31</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>820</v>
+        <v>831</v>
       </c>
     </row>
     <row r="125">
@@ -4235,7 +4272,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK391"/>
+  <dimension ref="A1:AK395"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.671875" customWidth="true" bestFit="true"/>
@@ -32476,7 +32513,7 @@
       </c>
       <c r="F270" s="2"/>
       <c r="G270" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H270" t="s" s="2">
         <v>81</v>
@@ -32579,10 +32616,10 @@
       </c>
       <c r="F271" s="2"/>
       <c r="G271" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H271" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I271" t="s" s="2">
         <v>73</v>
@@ -32591,16 +32628,16 @@
         <v>73</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>678</v>
+        <v>162</v>
       </c>
       <c r="N271" t="s" s="2">
-        <v>679</v>
+        <v>163</v>
       </c>
       <c r="O271" s="2"/>
       <c r="P271" s="2"/>
@@ -32651,19 +32688,19 @@
         <v>73</v>
       </c>
       <c r="AG271" t="s" s="2">
-        <v>677</v>
+        <v>164</v>
       </c>
       <c r="AH271" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI271" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ271" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK271" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272">
@@ -32671,21 +32708,21 @@
         <v>569</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D272" s="2"/>
       <c r="E272" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F272" s="2"/>
       <c r="G272" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H272" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I272" t="s" s="2">
         <v>73</v>
@@ -32697,15 +32734,17 @@
         <v>73</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="N272" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O272" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O272" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P272" s="2"/>
       <c r="Q272" t="s" s="2">
         <v>73</v>
@@ -32742,31 +32781,31 @@
         <v>73</v>
       </c>
       <c r="AC272" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD272" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE272" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG272" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AH272" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI272" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ272" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK272" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
     </row>
     <row r="273">
@@ -32774,21 +32813,21 @@
         <v>569</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D273" s="2"/>
       <c r="E273" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F273" s="2"/>
       <c r="G273" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H273" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I273" t="s" s="2">
         <v>73</v>
@@ -32797,20 +32836,18 @@
         <v>73</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>127</v>
+        <v>204</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>128</v>
+        <v>680</v>
       </c>
       <c r="N273" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O273" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>681</v>
+      </c>
+      <c r="O273" s="2"/>
       <c r="P273" s="2"/>
       <c r="Q273" t="s" s="2">
         <v>73</v>
@@ -32859,19 +32896,19 @@
         <v>73</v>
       </c>
       <c r="AG273" t="s" s="2">
-        <v>171</v>
+        <v>682</v>
       </c>
       <c r="AH273" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI273" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ273" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK273" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="274">
@@ -32879,46 +32916,42 @@
         <v>569</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H274" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I274" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J274" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K274" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>127</v>
+        <v>684</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>355</v>
+        <v>685</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O274" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P274" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="O274" s="2"/>
+      <c r="P274" s="2"/>
       <c r="Q274" t="s" s="2">
         <v>73</v>
       </c>
@@ -32966,19 +32999,19 @@
         <v>73</v>
       </c>
       <c r="AG274" t="s" s="2">
-        <v>357</v>
+        <v>687</v>
       </c>
       <c r="AH274" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ274" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK274" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="275">
@@ -32986,10 +33019,10 @@
         <v>569</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" t="s" s="2">
@@ -33000,7 +33033,7 @@
         <v>81</v>
       </c>
       <c r="H275" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I275" t="s" s="2">
         <v>73</v>
@@ -33012,13 +33045,13 @@
         <v>82</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>204</v>
+        <v>347</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="O275" s="2"/>
       <c r="P275" s="2"/>
@@ -33045,13 +33078,13 @@
         <v>73</v>
       </c>
       <c r="Y275" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z275" t="s" s="2">
-        <v>686</v>
+        <v>73</v>
       </c>
       <c r="AA275" t="s" s="2">
-        <v>687</v>
+        <v>73</v>
       </c>
       <c r="AB275" t="s" s="2">
         <v>73</v>
@@ -33069,13 +33102,13 @@
         <v>73</v>
       </c>
       <c r="AG275" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="AH275" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI275" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ275" t="s" s="2">
         <v>73</v>
@@ -33089,10 +33122,10 @@
         <v>569</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" t="s" s="2">
@@ -33100,7 +33133,7 @@
       </c>
       <c r="F276" s="2"/>
       <c r="G276" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H276" t="s" s="2">
         <v>81</v>
@@ -33112,20 +33145,18 @@
         <v>73</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>689</v>
+        <v>173</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>690</v>
+        <v>162</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="O276" t="s" s="2">
-        <v>692</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O276" s="2"/>
       <c r="P276" s="2"/>
       <c r="Q276" t="s" s="2">
         <v>73</v>
@@ -33174,19 +33205,19 @@
         <v>73</v>
       </c>
       <c r="AG276" t="s" s="2">
-        <v>688</v>
+        <v>164</v>
       </c>
       <c r="AH276" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI276" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ276" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK276" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="277">
@@ -33194,21 +33225,21 @@
         <v>569</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F277" s="2"/>
       <c r="G277" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H277" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I277" t="s" s="2">
         <v>73</v>
@@ -33217,21 +33248,21 @@
         <v>73</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>694</v>
+        <v>127</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>695</v>
+        <v>128</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="O277" s="2"/>
-      <c r="P277" t="s" s="2">
-        <v>697</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O277" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P277" s="2"/>
       <c r="Q277" t="s" s="2">
         <v>73</v>
       </c>
@@ -33279,19 +33310,19 @@
         <v>73</v>
       </c>
       <c r="AG277" t="s" s="2">
-        <v>693</v>
+        <v>171</v>
       </c>
       <c r="AH277" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI277" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ277" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK277" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="278">
@@ -33299,42 +33330,46 @@
         <v>569</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F278" s="2"/>
       <c r="G278" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H278" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I278" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J278" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K278" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>699</v>
+        <v>127</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>700</v>
+        <v>355</v>
       </c>
       <c r="N278" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="O278" s="2"/>
-      <c r="P278" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O278" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P278" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q278" t="s" s="2">
         <v>73</v>
       </c>
@@ -33382,19 +33417,19 @@
         <v>73</v>
       </c>
       <c r="AG278" t="s" s="2">
-        <v>698</v>
+        <v>357</v>
       </c>
       <c r="AH278" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI278" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ278" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK278" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="279">
@@ -33402,10 +33437,10 @@
         <v>569</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" t="s" s="2">
@@ -33413,7 +33448,7 @@
       </c>
       <c r="F279" s="2"/>
       <c r="G279" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H279" t="s" s="2">
         <v>81</v>
@@ -33425,16 +33460,16 @@
         <v>73</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>162</v>
+        <v>695</v>
       </c>
       <c r="N279" t="s" s="2">
-        <v>163</v>
+        <v>696</v>
       </c>
       <c r="O279" s="2"/>
       <c r="P279" s="2"/>
@@ -33461,13 +33496,13 @@
         <v>73</v>
       </c>
       <c r="Y279" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z279" t="s" s="2">
-        <v>73</v>
+        <v>697</v>
       </c>
       <c r="AA279" t="s" s="2">
-        <v>73</v>
+        <v>698</v>
       </c>
       <c r="AB279" t="s" s="2">
         <v>73</v>
@@ -33485,19 +33520,19 @@
         <v>73</v>
       </c>
       <c r="AG279" t="s" s="2">
-        <v>164</v>
+        <v>694</v>
       </c>
       <c r="AH279" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AI279" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ279" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK279" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="280">
@@ -33505,21 +33540,21 @@
         <v>569</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F280" s="2"/>
       <c r="G280" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H280" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I280" t="s" s="2">
         <v>73</v>
@@ -33528,19 +33563,19 @@
         <v>73</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>127</v>
+        <v>700</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>128</v>
+        <v>701</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>167</v>
+        <v>702</v>
       </c>
       <c r="O280" t="s" s="2">
-        <v>130</v>
+        <v>703</v>
       </c>
       <c r="P280" s="2"/>
       <c r="Q280" t="s" s="2">
@@ -33578,31 +33613,31 @@
         <v>73</v>
       </c>
       <c r="AC280" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD280" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AE280" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="AG280" t="s" s="2">
-        <v>171</v>
+        <v>699</v>
       </c>
       <c r="AH280" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ280" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK280" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="281">
@@ -33636,18 +33671,18 @@
         <v>82</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>173</v>
+        <v>705</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>174</v>
+        <v>706</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O281" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="P281" s="2"/>
+        <v>707</v>
+      </c>
+      <c r="O281" s="2"/>
+      <c r="P281" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="Q281" t="s" s="2">
         <v>73</v>
       </c>
@@ -33695,7 +33730,7 @@
         <v>73</v>
       </c>
       <c r="AG281" t="s" s="2">
-        <v>177</v>
+        <v>704</v>
       </c>
       <c r="AH281" t="s" s="2">
         <v>74</v>
@@ -33704,7 +33739,7 @@
         <v>81</v>
       </c>
       <c r="AJ281" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="AK281" t="s" s="2">
         <v>93</v>
@@ -33715,10 +33750,10 @@
         <v>569</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" t="s" s="2">
@@ -33726,7 +33761,7 @@
       </c>
       <c r="F282" s="2"/>
       <c r="G282" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H282" t="s" s="2">
         <v>81</v>
@@ -33741,17 +33776,15 @@
         <v>82</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>95</v>
+        <v>710</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>180</v>
+        <v>711</v>
       </c>
       <c r="N282" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O282" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>712</v>
+      </c>
+      <c r="O282" s="2"/>
       <c r="P282" s="2"/>
       <c r="Q282" t="s" s="2">
         <v>73</v>
@@ -33776,13 +33809,13 @@
         <v>73</v>
       </c>
       <c r="Y282" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z282" t="s" s="2">
-        <v>184</v>
+        <v>73</v>
       </c>
       <c r="AA282" t="s" s="2">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="AB282" t="s" s="2">
         <v>73</v>
@@ -33800,10 +33833,10 @@
         <v>73</v>
       </c>
       <c r="AG282" t="s" s="2">
-        <v>186</v>
+        <v>709</v>
       </c>
       <c r="AH282" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AI282" t="s" s="2">
         <v>81</v>
@@ -33820,10 +33853,10 @@
         <v>569</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" t="s" s="2">
@@ -33831,7 +33864,7 @@
       </c>
       <c r="F283" s="2"/>
       <c r="G283" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H283" t="s" s="2">
         <v>81</v>
@@ -33843,20 +33876,18 @@
         <v>73</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="N283" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O283" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O283" s="2"/>
       <c r="P283" s="2"/>
       <c r="Q283" t="s" s="2">
         <v>73</v>
@@ -33905,7 +33936,7 @@
         <v>73</v>
       </c>
       <c r="AG283" t="s" s="2">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="AH283" t="s" s="2">
         <v>74</v>
@@ -33914,10 +33945,10 @@
         <v>81</v>
       </c>
       <c r="AJ283" t="s" s="2">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="AK283" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="284">
@@ -33925,21 +33956,21 @@
         <v>569</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F284" s="2"/>
       <c r="G284" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H284" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I284" t="s" s="2">
         <v>73</v>
@@ -33951,15 +33982,17 @@
         <v>73</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="N284" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O284" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O284" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P284" s="2"/>
       <c r="Q284" t="s" s="2">
         <v>73</v>
@@ -33996,31 +34029,31 @@
         <v>73</v>
       </c>
       <c r="AC284" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD284" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE284" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG284" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AH284" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI284" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ284" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK284" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
     </row>
     <row r="285">
@@ -34028,21 +34061,21 @@
         <v>569</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F285" s="2"/>
       <c r="G285" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H285" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I285" t="s" s="2">
         <v>73</v>
@@ -34051,19 +34084,19 @@
         <v>73</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="N285" t="s" s="2">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="O285" t="s" s="2">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="P285" s="2"/>
       <c r="Q285" t="s" s="2">
@@ -34101,31 +34134,31 @@
         <v>73</v>
       </c>
       <c r="AC285" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD285" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AE285" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="AG285" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AH285" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI285" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ285" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="AK285" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="286">
@@ -34133,10 +34166,10 @@
         <v>569</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" t="s" s="2">
@@ -34153,26 +34186,24 @@
         <v>73</v>
       </c>
       <c r="J286" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K286" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="N286" t="s" s="2">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="O286" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="P286" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="P286" s="2"/>
       <c r="Q286" t="s" s="2">
         <v>73</v>
       </c>
@@ -34196,13 +34227,13 @@
         <v>73</v>
       </c>
       <c r="Y286" t="s" s="2">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="Z286" t="s" s="2">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="AA286" t="s" s="2">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="AB286" t="s" s="2">
         <v>73</v>
@@ -34220,7 +34251,7 @@
         <v>73</v>
       </c>
       <c r="AG286" t="s" s="2">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="AH286" t="s" s="2">
         <v>74</v>
@@ -34240,10 +34271,10 @@
         <v>569</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" t="s" s="2">
@@ -34251,7 +34282,7 @@
       </c>
       <c r="F287" s="2"/>
       <c r="G287" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H287" t="s" s="2">
         <v>81</v>
@@ -34266,20 +34297,18 @@
         <v>82</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="N287" t="s" s="2">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="O287" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="P287" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="P287" s="2"/>
       <c r="Q287" t="s" s="2">
         <v>73</v>
       </c>
@@ -34303,13 +34332,13 @@
         <v>73</v>
       </c>
       <c r="Y287" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z287" t="s" s="2">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="AA287" t="s" s="2">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="AB287" t="s" s="2">
         <v>73</v>
@@ -34327,7 +34356,7 @@
         <v>73</v>
       </c>
       <c r="AG287" t="s" s="2">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="AH287" t="s" s="2">
         <v>74</v>
@@ -34336,7 +34365,7 @@
         <v>81</v>
       </c>
       <c r="AJ287" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="AK287" t="s" s="2">
         <v>93</v>
@@ -34347,10 +34376,10 @@
         <v>569</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" t="s" s="2">
@@ -34358,7 +34387,7 @@
       </c>
       <c r="F288" s="2"/>
       <c r="G288" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H288" t="s" s="2">
         <v>81</v>
@@ -34370,23 +34399,19 @@
         <v>73</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="N288" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O288" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P288" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O288" s="2"/>
+      <c r="P288" s="2"/>
       <c r="Q288" t="s" s="2">
         <v>73</v>
       </c>
@@ -34398,7 +34423,7 @@
         <v>73</v>
       </c>
       <c r="U288" t="s" s="2">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="V288" t="s" s="2">
         <v>73</v>
@@ -34410,11 +34435,13 @@
         <v>73</v>
       </c>
       <c r="Y288" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Z288" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z288" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA288" t="s" s="2">
-        <v>712</v>
+        <v>73</v>
       </c>
       <c r="AB288" t="s" s="2">
         <v>73</v>
@@ -34432,7 +34459,7 @@
         <v>73</v>
       </c>
       <c r="AG288" t="s" s="2">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="AH288" t="s" s="2">
         <v>74</v>
@@ -34441,10 +34468,10 @@
         <v>81</v>
       </c>
       <c r="AJ288" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK288" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="289">
@@ -34452,21 +34479,21 @@
         <v>569</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H289" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I289" t="s" s="2">
         <v>73</v>
@@ -34475,19 +34502,19 @@
         <v>73</v>
       </c>
       <c r="K289" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="N289" t="s" s="2">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="O289" t="s" s="2">
-        <v>223</v>
+        <v>130</v>
       </c>
       <c r="P289" s="2"/>
       <c r="Q289" t="s" s="2">
@@ -34501,7 +34528,7 @@
         <v>73</v>
       </c>
       <c r="U289" t="s" s="2">
-        <v>224</v>
+        <v>73</v>
       </c>
       <c r="V289" t="s" s="2">
         <v>73</v>
@@ -34525,31 +34552,31 @@
         <v>73</v>
       </c>
       <c r="AC289" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD289" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE289" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG289" t="s" s="2">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="AH289" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI289" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ289" t="s" s="2">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="AK289" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="290">
@@ -34557,10 +34584,10 @@
         <v>569</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" t="s" s="2">
@@ -34577,22 +34604,26 @@
         <v>73</v>
       </c>
       <c r="J290" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K290" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="N290" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O290" s="2"/>
-      <c r="P290" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O290" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="P290" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="Q290" t="s" s="2">
         <v>73</v>
       </c>
@@ -34616,13 +34647,13 @@
         <v>73</v>
       </c>
       <c r="Y290" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z290" t="s" s="2">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="AA290" t="s" s="2">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="AB290" t="s" s="2">
         <v>73</v>
@@ -34640,7 +34671,7 @@
         <v>73</v>
       </c>
       <c r="AG290" t="s" s="2">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="AH290" t="s" s="2">
         <v>74</v>
@@ -34660,10 +34691,10 @@
         <v>569</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" t="s" s="2">
@@ -34686,18 +34717,20 @@
         <v>82</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="N291" t="s" s="2">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="O291" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="P291" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="P291" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="Q291" t="s" s="2">
         <v>73</v>
       </c>
@@ -34721,13 +34754,13 @@
         <v>73</v>
       </c>
       <c r="Y291" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="Z291" t="s" s="2">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="AA291" t="s" s="2">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="AB291" t="s" s="2">
         <v>73</v>
@@ -34745,7 +34778,7 @@
         <v>73</v>
       </c>
       <c r="AG291" t="s" s="2">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="AH291" t="s" s="2">
         <v>74</v>
@@ -34765,10 +34798,10 @@
         <v>569</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" t="s" s="2">
@@ -34776,7 +34809,7 @@
       </c>
       <c r="F292" s="2"/>
       <c r="G292" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H292" t="s" s="2">
         <v>81</v>
@@ -34791,18 +34824,20 @@
         <v>82</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="N292" t="s" s="2">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="O292" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="P292" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="P292" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="Q292" t="s" s="2">
         <v>73</v>
       </c>
@@ -34814,7 +34849,7 @@
         <v>73</v>
       </c>
       <c r="U292" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="V292" t="s" s="2">
         <v>73</v>
@@ -34826,13 +34861,11 @@
         <v>73</v>
       </c>
       <c r="Y292" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z292" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="Z292" s="2"/>
       <c r="AA292" t="s" s="2">
-        <v>73</v>
+        <v>723</v>
       </c>
       <c r="AB292" t="s" s="2">
         <v>73</v>
@@ -34850,7 +34883,7 @@
         <v>73</v>
       </c>
       <c r="AG292" t="s" s="2">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="AH292" t="s" s="2">
         <v>74</v>
@@ -34859,7 +34892,7 @@
         <v>81</v>
       </c>
       <c r="AJ292" t="s" s="2">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="AK292" t="s" s="2">
         <v>93</v>
@@ -34870,10 +34903,10 @@
         <v>569</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" t="s" s="2">
@@ -34881,10 +34914,10 @@
       </c>
       <c r="F293" s="2"/>
       <c r="G293" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H293" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I293" t="s" s="2">
         <v>73</v>
@@ -34896,15 +34929,17 @@
         <v>82</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>718</v>
+        <v>173</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>719</v>
+        <v>221</v>
       </c>
       <c r="N293" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="O293" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O293" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P293" s="2"/>
       <c r="Q293" t="s" s="2">
         <v>73</v>
@@ -34917,7 +34952,7 @@
         <v>73</v>
       </c>
       <c r="U293" t="s" s="2">
-        <v>73</v>
+        <v>224</v>
       </c>
       <c r="V293" t="s" s="2">
         <v>73</v>
@@ -34953,16 +34988,16 @@
         <v>73</v>
       </c>
       <c r="AG293" t="s" s="2">
-        <v>717</v>
+        <v>225</v>
       </c>
       <c r="AH293" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI293" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ293" t="s" s="2">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="AK293" t="s" s="2">
         <v>93</v>
@@ -34973,14 +35008,14 @@
         <v>569</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" t="s" s="2">
-        <v>722</v>
+        <v>73</v>
       </c>
       <c r="F294" s="2"/>
       <c r="G294" t="s" s="2">
@@ -34999,13 +35034,13 @@
         <v>82</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>723</v>
+        <v>152</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>724</v>
+        <v>228</v>
       </c>
       <c r="N294" t="s" s="2">
-        <v>725</v>
+        <v>229</v>
       </c>
       <c r="O294" s="2"/>
       <c r="P294" s="2"/>
@@ -35056,7 +35091,7 @@
         <v>73</v>
       </c>
       <c r="AG294" t="s" s="2">
-        <v>721</v>
+        <v>230</v>
       </c>
       <c r="AH294" t="s" s="2">
         <v>74</v>
@@ -35083,11 +35118,11 @@
       </c>
       <c r="D295" s="2"/>
       <c r="E295" t="s" s="2">
-        <v>727</v>
+        <v>73</v>
       </c>
       <c r="F295" s="2"/>
       <c r="G295" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H295" t="s" s="2">
         <v>81</v>
@@ -35102,15 +35137,17 @@
         <v>82</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>728</v>
+        <v>233</v>
       </c>
       <c r="N295" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="O295" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="O295" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P295" s="2"/>
       <c r="Q295" t="s" s="2">
         <v>73</v>
@@ -35159,7 +35196,7 @@
         <v>73</v>
       </c>
       <c r="AG295" t="s" s="2">
-        <v>726</v>
+        <v>236</v>
       </c>
       <c r="AH295" t="s" s="2">
         <v>74</v>
@@ -35179,10 +35216,10 @@
         <v>569</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" t="s" s="2">
@@ -35205,15 +35242,17 @@
         <v>82</v>
       </c>
       <c r="L296" t="s" s="2">
-        <v>731</v>
+        <v>173</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>732</v>
+        <v>238</v>
       </c>
       <c r="N296" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="O296" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O296" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P296" s="2"/>
       <c r="Q296" t="s" s="2">
         <v>73</v>
@@ -35238,13 +35277,13 @@
         <v>73</v>
       </c>
       <c r="Y296" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z296" t="s" s="2">
-        <v>734</v>
+        <v>73</v>
       </c>
       <c r="AA296" t="s" s="2">
-        <v>735</v>
+        <v>73</v>
       </c>
       <c r="AB296" t="s" s="2">
         <v>73</v>
@@ -35262,7 +35301,7 @@
         <v>73</v>
       </c>
       <c r="AG296" t="s" s="2">
-        <v>730</v>
+        <v>241</v>
       </c>
       <c r="AH296" t="s" s="2">
         <v>74</v>
@@ -35271,7 +35310,7 @@
         <v>81</v>
       </c>
       <c r="AJ296" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="AK296" t="s" s="2">
         <v>93</v>
@@ -35282,21 +35321,21 @@
         <v>569</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" t="s" s="2">
-        <v>737</v>
+        <v>73</v>
       </c>
       <c r="F297" s="2"/>
       <c r="G297" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H297" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I297" t="s" s="2">
         <v>73</v>
@@ -35308,13 +35347,13 @@
         <v>82</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>406</v>
+        <v>729</v>
       </c>
       <c r="M297" t="s" s="2">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="N297" t="s" s="2">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="O297" s="2"/>
       <c r="P297" s="2"/>
@@ -35365,13 +35404,13 @@
         <v>73</v>
       </c>
       <c r="AG297" t="s" s="2">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="AH297" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI297" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ297" t="s" s="2">
         <v>73</v>
@@ -35385,18 +35424,18 @@
         <v>569</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" t="s" s="2">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="F298" s="2"/>
       <c r="G298" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H298" t="s" s="2">
         <v>81</v>
@@ -35411,17 +35450,15 @@
         <v>82</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="N298" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="O298" t="s" s="2">
-        <v>745</v>
-      </c>
+        <v>736</v>
+      </c>
+      <c r="O298" s="2"/>
       <c r="P298" s="2"/>
       <c r="Q298" t="s" s="2">
         <v>73</v>
@@ -35470,7 +35507,7 @@
         <v>73</v>
       </c>
       <c r="AG298" t="s" s="2">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="AH298" t="s" s="2">
         <v>74</v>
@@ -35490,18 +35527,18 @@
         <v>569</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" t="s" s="2">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="F299" s="2"/>
       <c r="G299" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H299" t="s" s="2">
         <v>81</v>
@@ -35516,17 +35553,15 @@
         <v>82</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="N299" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="O299" t="s" s="2">
-        <v>750</v>
-      </c>
+        <v>740</v>
+      </c>
+      <c r="O299" s="2"/>
       <c r="P299" s="2"/>
       <c r="Q299" t="s" s="2">
         <v>73</v>
@@ -35551,13 +35586,13 @@
         <v>73</v>
       </c>
       <c r="Y299" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z299" t="s" s="2">
-        <v>751</v>
+        <v>73</v>
       </c>
       <c r="AA299" t="s" s="2">
-        <v>752</v>
+        <v>73</v>
       </c>
       <c r="AB299" t="s" s="2">
         <v>73</v>
@@ -35575,7 +35610,7 @@
         <v>73</v>
       </c>
       <c r="AG299" t="s" s="2">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="AH299" t="s" s="2">
         <v>74</v>
@@ -35595,21 +35630,21 @@
         <v>569</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" t="s" s="2">
-        <v>754</v>
+        <v>73</v>
       </c>
       <c r="F300" s="2"/>
       <c r="G300" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H300" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I300" t="s" s="2">
         <v>73</v>
@@ -35621,17 +35656,15 @@
         <v>82</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="O300" t="s" s="2">
-        <v>758</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="O300" s="2"/>
       <c r="P300" s="2"/>
       <c r="Q300" t="s" s="2">
         <v>73</v>
@@ -35656,13 +35689,13 @@
         <v>73</v>
       </c>
       <c r="Y300" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z300" t="s" s="2">
-        <v>73</v>
+        <v>745</v>
       </c>
       <c r="AA300" t="s" s="2">
-        <v>73</v>
+        <v>746</v>
       </c>
       <c r="AB300" t="s" s="2">
         <v>73</v>
@@ -35680,13 +35713,13 @@
         <v>73</v>
       </c>
       <c r="AG300" t="s" s="2">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="AH300" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI300" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ300" t="s" s="2">
         <v>73</v>
@@ -35700,21 +35733,21 @@
         <v>569</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" t="s" s="2">
-        <v>73</v>
+        <v>748</v>
       </c>
       <c r="F301" s="2"/>
       <c r="G301" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H301" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I301" t="s" s="2">
         <v>73</v>
@@ -35726,13 +35759,13 @@
         <v>82</v>
       </c>
       <c r="L301" t="s" s="2">
-        <v>760</v>
+        <v>406</v>
       </c>
       <c r="M301" t="s" s="2">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="N301" t="s" s="2">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="O301" s="2"/>
       <c r="P301" s="2"/>
@@ -35759,13 +35792,13 @@
         <v>73</v>
       </c>
       <c r="Y301" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z301" t="s" s="2">
-        <v>763</v>
+        <v>73</v>
       </c>
       <c r="AA301" t="s" s="2">
-        <v>764</v>
+        <v>73</v>
       </c>
       <c r="AB301" t="s" s="2">
         <v>73</v>
@@ -35783,13 +35816,13 @@
         <v>73</v>
       </c>
       <c r="AG301" t="s" s="2">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="AH301" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI301" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ301" t="s" s="2">
         <v>73</v>
@@ -35803,21 +35836,21 @@
         <v>569</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" t="s" s="2">
-        <v>73</v>
+        <v>752</v>
       </c>
       <c r="F302" s="2"/>
       <c r="G302" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H302" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I302" t="s" s="2">
         <v>73</v>
@@ -35829,16 +35862,16 @@
         <v>82</v>
       </c>
       <c r="L302" t="s" s="2">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="M302" t="s" s="2">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="N302" t="s" s="2">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="O302" t="s" s="2">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="P302" s="2"/>
       <c r="Q302" t="s" s="2">
@@ -35864,13 +35897,13 @@
         <v>73</v>
       </c>
       <c r="Y302" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z302" t="s" s="2">
-        <v>770</v>
+        <v>73</v>
       </c>
       <c r="AA302" t="s" s="2">
-        <v>771</v>
+        <v>73</v>
       </c>
       <c r="AB302" t="s" s="2">
         <v>73</v>
@@ -35888,13 +35921,13 @@
         <v>73</v>
       </c>
       <c r="AG302" t="s" s="2">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="AH302" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI302" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ302" t="s" s="2">
         <v>73</v>
@@ -35908,21 +35941,21 @@
         <v>569</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" t="s" s="2">
-        <v>73</v>
+        <v>758</v>
       </c>
       <c r="F303" s="2"/>
       <c r="G303" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H303" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I303" t="s" s="2">
         <v>73</v>
@@ -35931,18 +35964,20 @@
         <v>73</v>
       </c>
       <c r="K303" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L303" t="s" s="2">
-        <v>773</v>
+        <v>204</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>774</v>
+        <v>759</v>
       </c>
       <c r="N303" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O303" s="2"/>
+        <v>760</v>
+      </c>
+      <c r="O303" t="s" s="2">
+        <v>761</v>
+      </c>
       <c r="P303" s="2"/>
       <c r="Q303" t="s" s="2">
         <v>73</v>
@@ -35967,13 +36002,13 @@
         <v>73</v>
       </c>
       <c r="Y303" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z303" t="s" s="2">
-        <v>73</v>
+        <v>762</v>
       </c>
       <c r="AA303" t="s" s="2">
-        <v>73</v>
+        <v>763</v>
       </c>
       <c r="AB303" t="s" s="2">
         <v>73</v>
@@ -35991,13 +36026,13 @@
         <v>73</v>
       </c>
       <c r="AG303" t="s" s="2">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="AH303" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI303" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ303" t="s" s="2">
         <v>73</v>
@@ -36011,14 +36046,14 @@
         <v>569</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" t="s" s="2">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="F304" s="2"/>
       <c r="G304" t="s" s="2">
@@ -36034,19 +36069,19 @@
         <v>73</v>
       </c>
       <c r="K304" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L304" t="s" s="2">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="N304" t="s" s="2">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="O304" t="s" s="2">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="P304" s="2"/>
       <c r="Q304" t="s" s="2">
@@ -36096,7 +36131,7 @@
         <v>73</v>
       </c>
       <c r="AG304" t="s" s="2">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="AH304" t="s" s="2">
         <v>74</v>
@@ -36116,10 +36151,10 @@
         <v>569</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" t="s" s="2">
@@ -36142,17 +36177,15 @@
         <v>82</v>
       </c>
       <c r="L305" t="s" s="2">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="N305" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="O305" t="s" s="2">
-        <v>786</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="O305" s="2"/>
       <c r="P305" s="2"/>
       <c r="Q305" t="s" s="2">
         <v>73</v>
@@ -36177,13 +36210,13 @@
         <v>73</v>
       </c>
       <c r="Y305" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z305" t="s" s="2">
-        <v>73</v>
+        <v>774</v>
       </c>
       <c r="AA305" t="s" s="2">
-        <v>73</v>
+        <v>775</v>
       </c>
       <c r="AB305" t="s" s="2">
         <v>73</v>
@@ -36201,7 +36234,7 @@
         <v>73</v>
       </c>
       <c r="AG305" t="s" s="2">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="AH305" t="s" s="2">
         <v>74</v>
@@ -36221,14 +36254,14 @@
         <v>569</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
-        <v>788</v>
+        <v>73</v>
       </c>
       <c r="F306" s="2"/>
       <c r="G306" t="s" s="2">
@@ -36247,20 +36280,18 @@
         <v>82</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>204</v>
+        <v>777</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="N306" t="s" s="2">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="O306" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="P306" t="s" s="2">
-        <v>792</v>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="P306" s="2"/>
       <c r="Q306" t="s" s="2">
         <v>73</v>
       </c>
@@ -36287,10 +36318,10 @@
         <v>265</v>
       </c>
       <c r="Z306" t="s" s="2">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="AA306" t="s" s="2">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="AB306" t="s" s="2">
         <v>73</v>
@@ -36308,7 +36339,7 @@
         <v>73</v>
       </c>
       <c r="AG306" t="s" s="2">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="AH306" t="s" s="2">
         <v>74</v>
@@ -36317,7 +36348,7 @@
         <v>75</v>
       </c>
       <c r="AJ306" t="s" s="2">
-        <v>795</v>
+        <v>73</v>
       </c>
       <c r="AK306" t="s" s="2">
         <v>93</v>
@@ -36328,21 +36359,21 @@
         <v>569</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
-        <v>797</v>
+        <v>73</v>
       </c>
       <c r="F307" s="2"/>
       <c r="G307" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H307" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I307" t="s" s="2">
         <v>73</v>
@@ -36351,21 +36382,19 @@
         <v>73</v>
       </c>
       <c r="K307" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L307" t="s" s="2">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="M307" t="s" s="2">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="N307" t="s" s="2">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="O307" s="2"/>
-      <c r="P307" t="s" s="2">
-        <v>792</v>
-      </c>
+      <c r="P307" s="2"/>
       <c r="Q307" t="s" s="2">
         <v>73</v>
       </c>
@@ -36413,16 +36442,16 @@
         <v>73</v>
       </c>
       <c r="AG307" t="s" s="2">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="AH307" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI307" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ307" t="s" s="2">
-        <v>795</v>
+        <v>73</v>
       </c>
       <c r="AK307" t="s" s="2">
         <v>93</v>
@@ -36433,14 +36462,14 @@
         <v>569</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" t="s" s="2">
-        <v>73</v>
+        <v>788</v>
       </c>
       <c r="F308" s="2"/>
       <c r="G308" t="s" s="2">
@@ -36450,7 +36479,7 @@
         <v>75</v>
       </c>
       <c r="I308" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J308" t="s" s="2">
         <v>73</v>
@@ -36459,15 +36488,17 @@
         <v>73</v>
       </c>
       <c r="L308" t="s" s="2">
-        <v>549</v>
+        <v>789</v>
       </c>
       <c r="M308" t="s" s="2">
-        <v>50</v>
+        <v>790</v>
       </c>
       <c r="N308" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="O308" s="2"/>
+        <v>791</v>
+      </c>
+      <c r="O308" t="s" s="2">
+        <v>792</v>
+      </c>
       <c r="P308" s="2"/>
       <c r="Q308" t="s" s="2">
         <v>73</v>
@@ -36516,7 +36547,7 @@
         <v>73</v>
       </c>
       <c r="AG308" t="s" s="2">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="AH308" t="s" s="2">
         <v>74</v>
@@ -36536,10 +36567,10 @@
         <v>569</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
@@ -36559,18 +36590,20 @@
         <v>73</v>
       </c>
       <c r="K309" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>347</v>
+        <v>794</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="N309" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="O309" s="2"/>
+        <v>796</v>
+      </c>
+      <c r="O309" t="s" s="2">
+        <v>797</v>
+      </c>
       <c r="P309" s="2"/>
       <c r="Q309" t="s" s="2">
         <v>73</v>
@@ -36619,7 +36652,7 @@
         <v>73</v>
       </c>
       <c r="AG309" t="s" s="2">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="AH309" t="s" s="2">
         <v>74</v>
@@ -36639,21 +36672,21 @@
         <v>569</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
-        <v>73</v>
+        <v>799</v>
       </c>
       <c r="F310" s="2"/>
       <c r="G310" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H310" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I310" t="s" s="2">
         <v>73</v>
@@ -36662,19 +36695,23 @@
         <v>73</v>
       </c>
       <c r="K310" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>162</v>
+        <v>800</v>
       </c>
       <c r="N310" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O310" s="2"/>
-      <c r="P310" s="2"/>
+        <v>801</v>
+      </c>
+      <c r="O310" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="P310" t="s" s="2">
+        <v>803</v>
+      </c>
       <c r="Q310" t="s" s="2">
         <v>73</v>
       </c>
@@ -36698,13 +36735,13 @@
         <v>73</v>
       </c>
       <c r="Y310" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z310" t="s" s="2">
-        <v>73</v>
+        <v>804</v>
       </c>
       <c r="AA310" t="s" s="2">
-        <v>73</v>
+        <v>805</v>
       </c>
       <c r="AB310" t="s" s="2">
         <v>73</v>
@@ -36722,19 +36759,19 @@
         <v>73</v>
       </c>
       <c r="AG310" t="s" s="2">
-        <v>164</v>
+        <v>798</v>
       </c>
       <c r="AH310" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI310" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ310" t="s" s="2">
-        <v>165</v>
+        <v>806</v>
       </c>
       <c r="AK310" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="311">
@@ -36742,21 +36779,21 @@
         <v>569</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
-        <v>126</v>
+        <v>808</v>
       </c>
       <c r="F311" s="2"/>
       <c r="G311" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H311" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I311" t="s" s="2">
         <v>73</v>
@@ -36765,21 +36802,21 @@
         <v>73</v>
       </c>
       <c r="K311" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>127</v>
+        <v>809</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>128</v>
+        <v>810</v>
       </c>
       <c r="N311" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O311" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P311" s="2"/>
+        <v>801</v>
+      </c>
+      <c r="O311" s="2"/>
+      <c r="P311" t="s" s="2">
+        <v>803</v>
+      </c>
       <c r="Q311" t="s" s="2">
         <v>73</v>
       </c>
@@ -36827,19 +36864,19 @@
         <v>73</v>
       </c>
       <c r="AG311" t="s" s="2">
-        <v>171</v>
+        <v>807</v>
       </c>
       <c r="AH311" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI311" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ311" t="s" s="2">
-        <v>73</v>
+        <v>806</v>
       </c>
       <c r="AK311" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="312">
@@ -36847,14 +36884,14 @@
         <v>569</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" t="s" s="2">
@@ -36864,29 +36901,25 @@
         <v>75</v>
       </c>
       <c r="I312" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J312" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K312" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>127</v>
+        <v>549</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>355</v>
+        <v>50</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O312" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P312" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>812</v>
+      </c>
+      <c r="O312" s="2"/>
+      <c r="P312" s="2"/>
       <c r="Q312" t="s" s="2">
         <v>73</v>
       </c>
@@ -36934,7 +36967,7 @@
         <v>73</v>
       </c>
       <c r="AG312" t="s" s="2">
-        <v>357</v>
+        <v>811</v>
       </c>
       <c r="AH312" t="s" s="2">
         <v>74</v>
@@ -36946,7 +36979,7 @@
         <v>73</v>
       </c>
       <c r="AK312" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="313">
@@ -36954,10 +36987,10 @@
         <v>569</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
@@ -36968,7 +37001,7 @@
         <v>74</v>
       </c>
       <c r="H313" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I313" t="s" s="2">
         <v>73</v>
@@ -36977,16 +37010,16 @@
         <v>73</v>
       </c>
       <c r="K313" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>809</v>
+        <v>347</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>803</v>
+        <v>814</v>
       </c>
       <c r="N313" t="s" s="2">
-        <v>804</v>
+        <v>815</v>
       </c>
       <c r="O313" s="2"/>
       <c r="P313" s="2"/>
@@ -37037,13 +37070,13 @@
         <v>73</v>
       </c>
       <c r="AG313" t="s" s="2">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="AH313" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI313" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ313" t="s" s="2">
         <v>73</v>
@@ -37057,10 +37090,10 @@
         <v>569</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -37071,7 +37104,7 @@
         <v>74</v>
       </c>
       <c r="H314" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I314" t="s" s="2">
         <v>73</v>
@@ -37083,17 +37116,15 @@
         <v>73</v>
       </c>
       <c r="L314" t="s" s="2">
-        <v>811</v>
+        <v>173</v>
       </c>
       <c r="M314" t="s" s="2">
-        <v>812</v>
+        <v>162</v>
       </c>
       <c r="N314" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="O314" t="s" s="2">
-        <v>814</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O314" s="2"/>
       <c r="P314" s="2"/>
       <c r="Q314" t="s" s="2">
         <v>73</v>
@@ -37142,34 +37173,34 @@
         <v>73</v>
       </c>
       <c r="AG314" t="s" s="2">
-        <v>810</v>
+        <v>164</v>
       </c>
       <c r="AH314" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI314" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ314" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK314" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>815</v>
+        <v>569</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F315" s="2"/>
       <c r="G315" t="s" s="2">
@@ -37188,15 +37219,17 @@
         <v>73</v>
       </c>
       <c r="L315" t="s" s="2">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="M315" t="s" s="2">
-        <v>821</v>
+        <v>128</v>
       </c>
       <c r="N315" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="O315" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O315" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P315" s="2"/>
       <c r="Q315" t="s" s="2">
         <v>73</v>
@@ -37245,7 +37278,7 @@
         <v>73</v>
       </c>
       <c r="AG315" t="s" s="2">
-        <v>819</v>
+        <v>171</v>
       </c>
       <c r="AH315" t="s" s="2">
         <v>74</v>
@@ -37257,52 +37290,54 @@
         <v>73</v>
       </c>
       <c r="AK315" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>815</v>
+        <v>569</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F316" s="2"/>
       <c r="G316" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H316" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I316" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J316" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K316" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L316" t="s" s="2">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="M316" t="s" s="2">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="N316" t="s" s="2">
-        <v>85</v>
+        <v>356</v>
       </c>
       <c r="O316" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="P316" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="P316" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q316" t="s" s="2">
         <v>73</v>
       </c>
@@ -37350,30 +37385,30 @@
         <v>73</v>
       </c>
       <c r="AG316" t="s" s="2">
-        <v>87</v>
+        <v>357</v>
       </c>
       <c r="AH316" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI316" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ316" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK316" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>815</v>
+        <v>569</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
@@ -37396,13 +37431,13 @@
         <v>82</v>
       </c>
       <c r="L317" t="s" s="2">
-        <v>89</v>
+        <v>820</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>90</v>
+        <v>814</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>91</v>
+        <v>815</v>
       </c>
       <c r="O317" s="2"/>
       <c r="P317" s="2"/>
@@ -37453,7 +37488,7 @@
         <v>73</v>
       </c>
       <c r="AG317" t="s" s="2">
-        <v>92</v>
+        <v>819</v>
       </c>
       <c r="AH317" t="s" s="2">
         <v>74</v>
@@ -37470,13 +37505,13 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>815</v>
+        <v>569</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
@@ -37487,28 +37522,28 @@
         <v>74</v>
       </c>
       <c r="H318" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I318" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J318" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K318" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L318" t="s" s="2">
-        <v>95</v>
+        <v>822</v>
       </c>
       <c r="M318" t="s" s="2">
-        <v>96</v>
+        <v>823</v>
       </c>
       <c r="N318" t="s" s="2">
-        <v>97</v>
+        <v>824</v>
       </c>
       <c r="O318" t="s" s="2">
-        <v>98</v>
+        <v>825</v>
       </c>
       <c r="P318" s="2"/>
       <c r="Q318" t="s" s="2">
@@ -37558,13 +37593,13 @@
         <v>73</v>
       </c>
       <c r="AG318" t="s" s="2">
-        <v>99</v>
+        <v>821</v>
       </c>
       <c r="AH318" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI318" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ318" t="s" s="2">
         <v>73</v>
@@ -37575,13 +37610,13 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -37592,7 +37627,7 @@
         <v>74</v>
       </c>
       <c r="H319" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I319" t="s" s="2">
         <v>73</v>
@@ -37604,17 +37639,15 @@
         <v>73</v>
       </c>
       <c r="L319" t="s" s="2">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="M319" t="s" s="2">
-        <v>102</v>
+        <v>832</v>
       </c>
       <c r="N319" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="O319" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>833</v>
+      </c>
+      <c r="O319" s="2"/>
       <c r="P319" s="2"/>
       <c r="Q319" t="s" s="2">
         <v>73</v>
@@ -37639,13 +37672,13 @@
         <v>73</v>
       </c>
       <c r="Y319" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="Z319" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AA319" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AB319" t="s" s="2">
         <v>73</v>
@@ -37663,34 +37696,34 @@
         <v>73</v>
       </c>
       <c r="AG319" t="s" s="2">
-        <v>108</v>
+        <v>830</v>
       </c>
       <c r="AH319" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI319" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ319" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK319" t="s" s="2">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="F320" s="2"/>
       <c r="G320" t="s" s="2">
@@ -37706,19 +37739,19 @@
         <v>73</v>
       </c>
       <c r="K320" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L320" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="M320" t="s" s="2">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="N320" t="s" s="2">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="O320" t="s" s="2">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="P320" s="2"/>
       <c r="Q320" t="s" s="2">
@@ -37768,7 +37801,7 @@
         <v>73</v>
       </c>
       <c r="AG320" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="AH320" t="s" s="2">
         <v>74</v>
@@ -37777,21 +37810,21 @@
         <v>81</v>
       </c>
       <c r="AJ320" t="s" s="2">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="AK320" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -37799,7 +37832,7 @@
       </c>
       <c r="F321" s="2"/>
       <c r="G321" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H321" t="s" s="2">
         <v>81</v>
@@ -37811,20 +37844,18 @@
         <v>73</v>
       </c>
       <c r="K321" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L321" t="s" s="2">
-        <v>829</v>
+        <v>89</v>
       </c>
       <c r="M321" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="N321" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="O321" t="s" s="2">
-        <v>122</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="O321" s="2"/>
       <c r="P321" s="2"/>
       <c r="Q321" t="s" s="2">
         <v>73</v>
@@ -37873,62 +37904,62 @@
         <v>73</v>
       </c>
       <c r="AG321" t="s" s="2">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="AH321" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI321" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ321" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK321" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H322" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I322" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J322" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K322" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L322" t="s" s="2">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="M322" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="N322" t="s" s="2">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="O322" t="s" s="2">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="P322" s="2"/>
       <c r="Q322" t="s" s="2">
@@ -37978,66 +38009,64 @@
         <v>73</v>
       </c>
       <c r="AG322" t="s" s="2">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="AH322" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI322" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ322" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK322" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F323" s="2"/>
       <c r="G323" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H323" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I323" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J323" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K323" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L323" t="s" s="2">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="O323" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P323" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="P323" s="2"/>
       <c r="Q323" t="s" s="2">
         <v>73</v>
       </c>
@@ -38061,13 +38090,13 @@
         <v>73</v>
       </c>
       <c r="Y323" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z323" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AA323" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AB323" t="s" s="2">
         <v>73</v>
@@ -38085,41 +38114,41 @@
         <v>73</v>
       </c>
       <c r="AG323" t="s" s="2">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="AH323" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI323" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ323" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK323" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="F324" s="2"/>
       <c r="G324" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H324" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I324" t="s" s="2">
         <v>73</v>
@@ -38128,18 +38157,20 @@
         <v>73</v>
       </c>
       <c r="K324" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>833</v>
+        <v>112</v>
       </c>
       <c r="N324" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="O324" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O324" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P324" s="2"/>
       <c r="Q324" t="s" s="2">
         <v>73</v>
@@ -38188,16 +38219,16 @@
         <v>73</v>
       </c>
       <c r="AG324" t="s" s="2">
-        <v>832</v>
+        <v>115</v>
       </c>
       <c r="AH324" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI324" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ324" t="s" s="2">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="AK324" t="s" s="2">
         <v>93</v>
@@ -38205,13 +38236,13 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -38219,10 +38250,10 @@
       </c>
       <c r="F325" s="2"/>
       <c r="G325" t="s" s="2">
-        <v>74</v>
+        <v>840</v>
       </c>
       <c r="H325" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I325" t="s" s="2">
         <v>73</v>
@@ -38234,15 +38265,17 @@
         <v>73</v>
       </c>
       <c r="L325" t="s" s="2">
-        <v>83</v>
+        <v>841</v>
       </c>
       <c r="M325" t="s" s="2">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="N325" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O325" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="O325" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="P325" s="2"/>
       <c r="Q325" t="s" s="2">
         <v>73</v>
@@ -38291,16 +38324,16 @@
         <v>73</v>
       </c>
       <c r="AG325" t="s" s="2">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AH325" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI325" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ325" t="s" s="2">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="AK325" t="s" s="2">
         <v>73</v>
@@ -38308,13 +38341,13 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -38343,7 +38376,7 @@
         <v>128</v>
       </c>
       <c r="N326" t="s" s="2">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="O326" t="s" s="2">
         <v>130</v>
@@ -38384,19 +38417,19 @@
         <v>73</v>
       </c>
       <c r="AC326" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD326" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AE326" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF326" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="AG326" t="s" s="2">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AH326" t="s" s="2">
         <v>74</v>
@@ -38413,24 +38446,24 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F327" s="2"/>
       <c r="G327" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H327" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I327" t="s" s="2">
         <v>73</v>
@@ -38442,19 +38475,19 @@
         <v>82</v>
       </c>
       <c r="L327" t="s" s="2">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="M327" t="s" s="2">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="N327" t="s" s="2">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="O327" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="P327" t="s" s="2">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="Q327" t="s" s="2">
         <v>73</v>
@@ -38479,13 +38512,13 @@
         <v>73</v>
       </c>
       <c r="Y327" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="Z327" t="s" s="2">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="AA327" t="s" s="2">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="AB327" t="s" s="2">
         <v>73</v>
@@ -38503,30 +38536,30 @@
         <v>73</v>
       </c>
       <c r="AG327" t="s" s="2">
-        <v>202</v>
+        <v>137</v>
       </c>
       <c r="AH327" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI327" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ327" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK327" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
@@ -38537,7 +38570,7 @@
         <v>74</v>
       </c>
       <c r="H328" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I328" t="s" s="2">
         <v>73</v>
@@ -38549,20 +38582,16 @@
         <v>82</v>
       </c>
       <c r="L328" t="s" s="2">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="M328" t="s" s="2">
-        <v>205</v>
+        <v>845</v>
       </c>
       <c r="N328" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O328" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="P328" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>846</v>
+      </c>
+      <c r="O328" s="2"/>
+      <c r="P328" s="2"/>
       <c r="Q328" t="s" s="2">
         <v>73</v>
       </c>
@@ -38586,13 +38615,13 @@
         <v>73</v>
       </c>
       <c r="Y328" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z328" t="s" s="2">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="AA328" t="s" s="2">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="AB328" t="s" s="2">
         <v>73</v>
@@ -38610,13 +38639,13 @@
         <v>73</v>
       </c>
       <c r="AG328" t="s" s="2">
-        <v>211</v>
+        <v>844</v>
       </c>
       <c r="AH328" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI328" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ328" t="s" s="2">
         <v>73</v>
@@ -38627,13 +38656,13 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -38641,7 +38670,7 @@
       </c>
       <c r="F329" s="2"/>
       <c r="G329" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H329" t="s" s="2">
         <v>81</v>
@@ -38653,23 +38682,19 @@
         <v>73</v>
       </c>
       <c r="K329" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L329" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="N329" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O329" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P329" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O329" s="2"/>
+      <c r="P329" s="2"/>
       <c r="Q329" t="s" s="2">
         <v>73</v>
       </c>
@@ -38681,7 +38706,7 @@
         <v>73</v>
       </c>
       <c r="U329" t="s" s="2">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="V329" t="s" s="2">
         <v>73</v>
@@ -38717,7 +38742,7 @@
         <v>73</v>
       </c>
       <c r="AG329" t="s" s="2">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="AH329" t="s" s="2">
         <v>74</v>
@@ -38726,32 +38751,32 @@
         <v>81</v>
       </c>
       <c r="AJ329" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK329" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F330" s="2"/>
       <c r="G330" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H330" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I330" t="s" s="2">
         <v>73</v>
@@ -38760,19 +38785,19 @@
         <v>73</v>
       </c>
       <c r="K330" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L330" t="s" s="2">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="O330" t="s" s="2">
-        <v>223</v>
+        <v>130</v>
       </c>
       <c r="P330" s="2"/>
       <c r="Q330" t="s" s="2">
@@ -38786,7 +38811,7 @@
         <v>73</v>
       </c>
       <c r="U330" t="s" s="2">
-        <v>224</v>
+        <v>73</v>
       </c>
       <c r="V330" t="s" s="2">
         <v>73</v>
@@ -38810,42 +38835,42 @@
         <v>73</v>
       </c>
       <c r="AC330" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD330" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE330" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF330" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="AH330" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI330" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ330" t="s" s="2">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="AK330" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -38862,22 +38887,26 @@
         <v>73</v>
       </c>
       <c r="J331" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K331" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L331" t="s" s="2">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="M331" t="s" s="2">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="N331" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O331" s="2"/>
-      <c r="P331" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O331" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="P331" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="Q331" t="s" s="2">
         <v>73</v>
       </c>
@@ -38901,13 +38930,13 @@
         <v>73</v>
       </c>
       <c r="Y331" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z331" t="s" s="2">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="AA331" t="s" s="2">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="AB331" t="s" s="2">
         <v>73</v>
@@ -38925,7 +38954,7 @@
         <v>73</v>
       </c>
       <c r="AG331" t="s" s="2">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="AH331" t="s" s="2">
         <v>74</v>
@@ -38942,13 +38971,13 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -38971,18 +39000,20 @@
         <v>82</v>
       </c>
       <c r="L332" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="M332" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="N332" t="s" s="2">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="O332" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="P332" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="P332" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="Q332" t="s" s="2">
         <v>73</v>
       </c>
@@ -39006,13 +39037,13 @@
         <v>73</v>
       </c>
       <c r="Y332" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="Z332" t="s" s="2">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="AA332" t="s" s="2">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="AB332" t="s" s="2">
         <v>73</v>
@@ -39030,7 +39061,7 @@
         <v>73</v>
       </c>
       <c r="AG332" t="s" s="2">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="AH332" t="s" s="2">
         <v>74</v>
@@ -39047,13 +39078,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -39061,7 +39092,7 @@
       </c>
       <c r="F333" s="2"/>
       <c r="G333" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H333" t="s" s="2">
         <v>81</v>
@@ -39076,16 +39107,20 @@
         <v>82</v>
       </c>
       <c r="L333" t="s" s="2">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="M333" t="s" s="2">
-        <v>844</v>
+        <v>213</v>
       </c>
       <c r="N333" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="O333" s="2"/>
-      <c r="P333" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="O333" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P333" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="Q333" t="s" s="2">
         <v>73</v>
       </c>
@@ -39097,7 +39132,7 @@
         <v>73</v>
       </c>
       <c r="U333" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="V333" t="s" s="2">
         <v>73</v>
@@ -39133,7 +39168,7 @@
         <v>73</v>
       </c>
       <c r="AG333" t="s" s="2">
-        <v>843</v>
+        <v>219</v>
       </c>
       <c r="AH333" t="s" s="2">
         <v>74</v>
@@ -39150,13 +39185,13 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -39164,7 +39199,7 @@
       </c>
       <c r="F334" s="2"/>
       <c r="G334" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H334" t="s" s="2">
         <v>81</v>
@@ -39173,22 +39208,22 @@
         <v>73</v>
       </c>
       <c r="J334" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K334" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L334" t="s" s="2">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="M334" t="s" s="2">
-        <v>847</v>
+        <v>221</v>
       </c>
       <c r="N334" t="s" s="2">
-        <v>848</v>
+        <v>222</v>
       </c>
       <c r="O334" t="s" s="2">
-        <v>849</v>
+        <v>223</v>
       </c>
       <c r="P334" s="2"/>
       <c r="Q334" t="s" s="2">
@@ -39202,7 +39237,7 @@
         <v>73</v>
       </c>
       <c r="U334" t="s" s="2">
-        <v>73</v>
+        <v>224</v>
       </c>
       <c r="V334" t="s" s="2">
         <v>73</v>
@@ -39214,13 +39249,13 @@
         <v>73</v>
       </c>
       <c r="Y334" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="Z334" t="s" s="2">
-        <v>850</v>
+        <v>73</v>
       </c>
       <c r="AA334" t="s" s="2">
-        <v>851</v>
+        <v>73</v>
       </c>
       <c r="AB334" t="s" s="2">
         <v>73</v>
@@ -39238,7 +39273,7 @@
         <v>73</v>
       </c>
       <c r="AG334" t="s" s="2">
-        <v>846</v>
+        <v>225</v>
       </c>
       <c r="AH334" t="s" s="2">
         <v>74</v>
@@ -39247,7 +39282,7 @@
         <v>81</v>
       </c>
       <c r="AJ334" t="s" s="2">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="AK334" t="s" s="2">
         <v>93</v>
@@ -39255,13 +39290,13 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -39269,7 +39304,7 @@
       </c>
       <c r="F335" s="2"/>
       <c r="G335" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H335" t="s" s="2">
         <v>81</v>
@@ -39284,17 +39319,15 @@
         <v>82</v>
       </c>
       <c r="L335" t="s" s="2">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="M335" t="s" s="2">
-        <v>853</v>
+        <v>228</v>
       </c>
       <c r="N335" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="O335" t="s" s="2">
-        <v>855</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="O335" s="2"/>
       <c r="P335" s="2"/>
       <c r="Q335" t="s" s="2">
         <v>73</v>
@@ -39319,11 +39352,13 @@
         <v>73</v>
       </c>
       <c r="Y335" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="Z335" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z335" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA335" t="s" s="2">
-        <v>856</v>
+        <v>73</v>
       </c>
       <c r="AB335" t="s" s="2">
         <v>73</v>
@@ -39341,7 +39376,7 @@
         <v>73</v>
       </c>
       <c r="AG335" t="s" s="2">
-        <v>852</v>
+        <v>230</v>
       </c>
       <c r="AH335" t="s" s="2">
         <v>74</v>
@@ -39358,13 +39393,13 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
@@ -39372,7 +39407,7 @@
       </c>
       <c r="F336" s="2"/>
       <c r="G336" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H336" t="s" s="2">
         <v>81</v>
@@ -39387,18 +39422,18 @@
         <v>82</v>
       </c>
       <c r="L336" t="s" s="2">
-        <v>699</v>
+        <v>232</v>
       </c>
       <c r="M336" t="s" s="2">
-        <v>858</v>
+        <v>233</v>
       </c>
       <c r="N336" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="O336" s="2"/>
-      <c r="P336" t="s" s="2">
-        <v>860</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="O336" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="P336" s="2"/>
       <c r="Q336" t="s" s="2">
         <v>73</v>
       </c>
@@ -39446,7 +39481,7 @@
         <v>73</v>
       </c>
       <c r="AG336" t="s" s="2">
-        <v>857</v>
+        <v>236</v>
       </c>
       <c r="AH336" t="s" s="2">
         <v>74</v>
@@ -39463,13 +39498,13 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -39489,16 +39524,16 @@
         <v>73</v>
       </c>
       <c r="K337" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L337" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="M337" t="s" s="2">
-        <v>162</v>
+        <v>856</v>
       </c>
       <c r="N337" t="s" s="2">
-        <v>163</v>
+        <v>857</v>
       </c>
       <c r="O337" s="2"/>
       <c r="P337" s="2"/>
@@ -39549,7 +39584,7 @@
         <v>73</v>
       </c>
       <c r="AG337" t="s" s="2">
-        <v>164</v>
+        <v>855</v>
       </c>
       <c r="AH337" t="s" s="2">
         <v>74</v>
@@ -39558,53 +39593,53 @@
         <v>81</v>
       </c>
       <c r="AJ337" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK337" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F338" s="2"/>
       <c r="G338" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H338" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I338" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J338" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K338" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L338" t="s" s="2">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>128</v>
+        <v>859</v>
       </c>
       <c r="N338" t="s" s="2">
-        <v>167</v>
+        <v>860</v>
       </c>
       <c r="O338" t="s" s="2">
-        <v>130</v>
+        <v>861</v>
       </c>
       <c r="P338" s="2"/>
       <c r="Q338" t="s" s="2">
@@ -39630,54 +39665,54 @@
         <v>73</v>
       </c>
       <c r="Y338" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z338" t="s" s="2">
-        <v>73</v>
+        <v>862</v>
       </c>
       <c r="AA338" t="s" s="2">
-        <v>73</v>
+        <v>863</v>
       </c>
       <c r="AB338" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AC338" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD338" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AE338" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF338" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>171</v>
+        <v>858</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI338" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ338" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK338" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -39685,7 +39720,7 @@
       </c>
       <c r="F339" s="2"/>
       <c r="G339" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H339" t="s" s="2">
         <v>81</v>
@@ -39700,16 +39735,16 @@
         <v>82</v>
       </c>
       <c r="L339" t="s" s="2">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>174</v>
+        <v>865</v>
       </c>
       <c r="N339" t="s" s="2">
-        <v>175</v>
+        <v>866</v>
       </c>
       <c r="O339" t="s" s="2">
-        <v>176</v>
+        <v>867</v>
       </c>
       <c r="P339" s="2"/>
       <c r="Q339" t="s" s="2">
@@ -39735,13 +39770,11 @@
         <v>73</v>
       </c>
       <c r="Y339" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z339" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="Z339" s="2"/>
       <c r="AA339" t="s" s="2">
-        <v>73</v>
+        <v>868</v>
       </c>
       <c r="AB339" t="s" s="2">
         <v>73</v>
@@ -39759,7 +39792,7 @@
         <v>73</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>177</v>
+        <v>864</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>74</v>
@@ -39768,7 +39801,7 @@
         <v>81</v>
       </c>
       <c r="AJ339" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="AK339" t="s" s="2">
         <v>93</v>
@@ -39776,13 +39809,13 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -39790,7 +39823,7 @@
       </c>
       <c r="F340" s="2"/>
       <c r="G340" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H340" t="s" s="2">
         <v>81</v>
@@ -39805,18 +39838,18 @@
         <v>82</v>
       </c>
       <c r="L340" t="s" s="2">
-        <v>95</v>
+        <v>710</v>
       </c>
       <c r="M340" t="s" s="2">
-        <v>180</v>
+        <v>870</v>
       </c>
       <c r="N340" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O340" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="P340" s="2"/>
+        <v>871</v>
+      </c>
+      <c r="O340" s="2"/>
+      <c r="P340" t="s" s="2">
+        <v>872</v>
+      </c>
       <c r="Q340" t="s" s="2">
         <v>73</v>
       </c>
@@ -39840,13 +39873,13 @@
         <v>73</v>
       </c>
       <c r="Y340" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z340" t="s" s="2">
-        <v>184</v>
+        <v>73</v>
       </c>
       <c r="AA340" t="s" s="2">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="AB340" t="s" s="2">
         <v>73</v>
@@ -39864,7 +39897,7 @@
         <v>73</v>
       </c>
       <c r="AG340" t="s" s="2">
-        <v>186</v>
+        <v>869</v>
       </c>
       <c r="AH340" t="s" s="2">
         <v>74</v>
@@ -39881,13 +39914,13 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -39895,7 +39928,7 @@
       </c>
       <c r="F341" s="2"/>
       <c r="G341" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H341" t="s" s="2">
         <v>81</v>
@@ -39907,20 +39940,18 @@
         <v>73</v>
       </c>
       <c r="K341" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L341" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="M341" t="s" s="2">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="N341" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O341" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O341" s="2"/>
       <c r="P341" s="2"/>
       <c r="Q341" t="s" s="2">
         <v>73</v>
@@ -39969,7 +40000,7 @@
         <v>73</v>
       </c>
       <c r="AG341" t="s" s="2">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="AH341" t="s" s="2">
         <v>74</v>
@@ -39978,32 +40009,32 @@
         <v>81</v>
       </c>
       <c r="AJ341" t="s" s="2">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="AK341" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H342" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I342" t="s" s="2">
         <v>73</v>
@@ -40015,15 +40046,17 @@
         <v>73</v>
       </c>
       <c r="L342" t="s" s="2">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="N342" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O342" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O342" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P342" s="2"/>
       <c r="Q342" t="s" s="2">
         <v>73</v>
@@ -40060,53 +40093,53 @@
         <v>73</v>
       </c>
       <c r="AC342" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD342" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE342" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF342" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG342" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AH342" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI342" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ342" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK342" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F343" s="2"/>
       <c r="G343" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H343" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I343" t="s" s="2">
         <v>73</v>
@@ -40115,19 +40148,19 @@
         <v>73</v>
       </c>
       <c r="K343" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="N343" t="s" s="2">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="O343" t="s" s="2">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="P343" s="2"/>
       <c r="Q343" t="s" s="2">
@@ -40165,42 +40198,42 @@
         <v>73</v>
       </c>
       <c r="AC343" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD343" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AE343" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF343" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="AG343" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AH343" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI343" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ343" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="AK343" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
@@ -40217,26 +40250,24 @@
         <v>73</v>
       </c>
       <c r="J344" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K344" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L344" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="M344" t="s" s="2">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="N344" t="s" s="2">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="O344" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="P344" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="P344" s="2"/>
       <c r="Q344" t="s" s="2">
         <v>73</v>
       </c>
@@ -40260,13 +40291,13 @@
         <v>73</v>
       </c>
       <c r="Y344" t="s" s="2">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="Z344" t="s" s="2">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="AA344" t="s" s="2">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="AB344" t="s" s="2">
         <v>73</v>
@@ -40284,7 +40315,7 @@
         <v>73</v>
       </c>
       <c r="AG344" t="s" s="2">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="AH344" t="s" s="2">
         <v>74</v>
@@ -40301,13 +40332,13 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -40315,7 +40346,7 @@
       </c>
       <c r="F345" s="2"/>
       <c r="G345" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H345" t="s" s="2">
         <v>81</v>
@@ -40330,20 +40361,18 @@
         <v>82</v>
       </c>
       <c r="L345" t="s" s="2">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="M345" t="s" s="2">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="N345" t="s" s="2">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="O345" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="P345" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="P345" s="2"/>
       <c r="Q345" t="s" s="2">
         <v>73</v>
       </c>
@@ -40367,13 +40396,13 @@
         <v>73</v>
       </c>
       <c r="Y345" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z345" t="s" s="2">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="AA345" t="s" s="2">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="AB345" t="s" s="2">
         <v>73</v>
@@ -40391,7 +40420,7 @@
         <v>73</v>
       </c>
       <c r="AG345" t="s" s="2">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="AH345" t="s" s="2">
         <v>74</v>
@@ -40400,7 +40429,7 @@
         <v>81</v>
       </c>
       <c r="AJ345" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="AK345" t="s" s="2">
         <v>93</v>
@@ -40408,13 +40437,13 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
@@ -40422,7 +40451,7 @@
       </c>
       <c r="F346" s="2"/>
       <c r="G346" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H346" t="s" s="2">
         <v>81</v>
@@ -40434,23 +40463,19 @@
         <v>73</v>
       </c>
       <c r="K346" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L346" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M346" t="s" s="2">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="N346" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O346" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P346" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O346" s="2"/>
+      <c r="P346" s="2"/>
       <c r="Q346" t="s" s="2">
         <v>73</v>
       </c>
@@ -40462,7 +40487,7 @@
         <v>73</v>
       </c>
       <c r="U346" t="s" s="2">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="V346" t="s" s="2">
         <v>73</v>
@@ -40474,11 +40499,13 @@
         <v>73</v>
       </c>
       <c r="Y346" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Z346" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z346" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA346" t="s" s="2">
-        <v>712</v>
+        <v>73</v>
       </c>
       <c r="AB346" t="s" s="2">
         <v>73</v>
@@ -40496,7 +40523,7 @@
         <v>73</v>
       </c>
       <c r="AG346" t="s" s="2">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="AH346" t="s" s="2">
         <v>74</v>
@@ -40505,32 +40532,32 @@
         <v>81</v>
       </c>
       <c r="AJ346" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK346" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F347" s="2"/>
       <c r="G347" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H347" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I347" t="s" s="2">
         <v>73</v>
@@ -40539,19 +40566,19 @@
         <v>73</v>
       </c>
       <c r="K347" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L347" t="s" s="2">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="M347" t="s" s="2">
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="N347" t="s" s="2">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="O347" t="s" s="2">
-        <v>223</v>
+        <v>130</v>
       </c>
       <c r="P347" s="2"/>
       <c r="Q347" t="s" s="2">
@@ -40565,7 +40592,7 @@
         <v>73</v>
       </c>
       <c r="U347" t="s" s="2">
-        <v>224</v>
+        <v>73</v>
       </c>
       <c r="V347" t="s" s="2">
         <v>73</v>
@@ -40589,42 +40616,42 @@
         <v>73</v>
       </c>
       <c r="AC347" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD347" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE347" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF347" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG347" t="s" s="2">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="AH347" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI347" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ347" t="s" s="2">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="AK347" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
@@ -40641,22 +40668,26 @@
         <v>73</v>
       </c>
       <c r="J348" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K348" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L348" t="s" s="2">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="M348" t="s" s="2">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="N348" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O348" s="2"/>
-      <c r="P348" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O348" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="P348" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="Q348" t="s" s="2">
         <v>73</v>
       </c>
@@ -40680,13 +40711,13 @@
         <v>73</v>
       </c>
       <c r="Y348" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z348" t="s" s="2">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="AA348" t="s" s="2">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="AB348" t="s" s="2">
         <v>73</v>
@@ -40704,7 +40735,7 @@
         <v>73</v>
       </c>
       <c r="AG348" t="s" s="2">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="AH348" t="s" s="2">
         <v>74</v>
@@ -40721,13 +40752,13 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
@@ -40750,18 +40781,20 @@
         <v>82</v>
       </c>
       <c r="L349" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="M349" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="N349" t="s" s="2">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="O349" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="P349" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="P349" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="Q349" t="s" s="2">
         <v>73</v>
       </c>
@@ -40785,13 +40818,13 @@
         <v>73</v>
       </c>
       <c r="Y349" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="Z349" t="s" s="2">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="AA349" t="s" s="2">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="AB349" t="s" s="2">
         <v>73</v>
@@ -40809,7 +40842,7 @@
         <v>73</v>
       </c>
       <c r="AG349" t="s" s="2">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="AH349" t="s" s="2">
         <v>74</v>
@@ -40826,13 +40859,13 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
@@ -40840,7 +40873,7 @@
       </c>
       <c r="F350" s="2"/>
       <c r="G350" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H350" t="s" s="2">
         <v>81</v>
@@ -40855,18 +40888,20 @@
         <v>82</v>
       </c>
       <c r="L350" t="s" s="2">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="M350" t="s" s="2">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="N350" t="s" s="2">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="O350" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="P350" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="P350" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="Q350" t="s" s="2">
         <v>73</v>
       </c>
@@ -40878,7 +40913,7 @@
         <v>73</v>
       </c>
       <c r="U350" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="V350" t="s" s="2">
         <v>73</v>
@@ -40890,13 +40925,11 @@
         <v>73</v>
       </c>
       <c r="Y350" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z350" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="Z350" s="2"/>
       <c r="AA350" t="s" s="2">
-        <v>73</v>
+        <v>723</v>
       </c>
       <c r="AB350" t="s" s="2">
         <v>73</v>
@@ -40914,7 +40947,7 @@
         <v>73</v>
       </c>
       <c r="AG350" t="s" s="2">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="AH350" t="s" s="2">
         <v>74</v>
@@ -40923,7 +40956,7 @@
         <v>81</v>
       </c>
       <c r="AJ350" t="s" s="2">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="AK350" t="s" s="2">
         <v>93</v>
@@ -40931,13 +40964,13 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -40945,7 +40978,7 @@
       </c>
       <c r="F351" s="2"/>
       <c r="G351" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H351" t="s" s="2">
         <v>81</v>
@@ -40960,15 +40993,17 @@
         <v>82</v>
       </c>
       <c r="L351" t="s" s="2">
-        <v>406</v>
+        <v>173</v>
       </c>
       <c r="M351" t="s" s="2">
-        <v>876</v>
+        <v>221</v>
       </c>
       <c r="N351" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="O351" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O351" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P351" s="2"/>
       <c r="Q351" t="s" s="2">
         <v>73</v>
@@ -40981,7 +41016,7 @@
         <v>73</v>
       </c>
       <c r="U351" t="s" s="2">
-        <v>73</v>
+        <v>224</v>
       </c>
       <c r="V351" t="s" s="2">
         <v>73</v>
@@ -41017,7 +41052,7 @@
         <v>73</v>
       </c>
       <c r="AG351" t="s" s="2">
-        <v>875</v>
+        <v>225</v>
       </c>
       <c r="AH351" t="s" s="2">
         <v>74</v>
@@ -41026,7 +41061,7 @@
         <v>81</v>
       </c>
       <c r="AJ351" t="s" s="2">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="AK351" t="s" s="2">
         <v>93</v>
@@ -41034,13 +41069,13 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
@@ -41051,7 +41086,7 @@
         <v>74</v>
       </c>
       <c r="H352" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I352" t="s" s="2">
         <v>73</v>
@@ -41060,20 +41095,18 @@
         <v>73</v>
       </c>
       <c r="K352" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L352" t="s" s="2">
-        <v>783</v>
+        <v>152</v>
       </c>
       <c r="M352" t="s" s="2">
-        <v>879</v>
+        <v>228</v>
       </c>
       <c r="N352" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="O352" t="s" s="2">
-        <v>881</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="O352" s="2"/>
       <c r="P352" s="2"/>
       <c r="Q352" t="s" s="2">
         <v>73</v>
@@ -41122,13 +41155,13 @@
         <v>73</v>
       </c>
       <c r="AG352" t="s" s="2">
-        <v>878</v>
+        <v>230</v>
       </c>
       <c r="AH352" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI352" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ352" t="s" s="2">
         <v>73</v>
@@ -41139,13 +41172,13 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
@@ -41153,7 +41186,7 @@
       </c>
       <c r="F353" s="2"/>
       <c r="G353" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H353" t="s" s="2">
         <v>81</v>
@@ -41165,19 +41198,19 @@
         <v>73</v>
       </c>
       <c r="K353" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L353" t="s" s="2">
-        <v>616</v>
+        <v>232</v>
       </c>
       <c r="M353" t="s" s="2">
-        <v>883</v>
+        <v>233</v>
       </c>
       <c r="N353" t="s" s="2">
-        <v>884</v>
+        <v>234</v>
       </c>
       <c r="O353" t="s" s="2">
-        <v>885</v>
+        <v>235</v>
       </c>
       <c r="P353" s="2"/>
       <c r="Q353" t="s" s="2">
@@ -41227,13 +41260,13 @@
         <v>73</v>
       </c>
       <c r="AG353" t="s" s="2">
-        <v>882</v>
+        <v>236</v>
       </c>
       <c r="AH353" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI353" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ353" t="s" s="2">
         <v>73</v>
@@ -41244,7 +41277,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>886</v>
@@ -41273,15 +41306,17 @@
         <v>82</v>
       </c>
       <c r="L354" t="s" s="2">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="M354" t="s" s="2">
-        <v>887</v>
+        <v>238</v>
       </c>
       <c r="N354" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="O354" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O354" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P354" s="2"/>
       <c r="Q354" t="s" s="2">
         <v>73</v>
@@ -41306,13 +41341,13 @@
         <v>73</v>
       </c>
       <c r="Y354" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="Z354" t="s" s="2">
-        <v>889</v>
+        <v>73</v>
       </c>
       <c r="AA354" t="s" s="2">
-        <v>890</v>
+        <v>73</v>
       </c>
       <c r="AB354" t="s" s="2">
         <v>73</v>
@@ -41330,7 +41365,7 @@
         <v>73</v>
       </c>
       <c r="AG354" t="s" s="2">
-        <v>886</v>
+        <v>241</v>
       </c>
       <c r="AH354" t="s" s="2">
         <v>74</v>
@@ -41339,7 +41374,7 @@
         <v>81</v>
       </c>
       <c r="AJ354" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="AK354" t="s" s="2">
         <v>93</v>
@@ -41347,13 +41382,13 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -41364,7 +41399,7 @@
         <v>74</v>
       </c>
       <c r="H355" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I355" t="s" s="2">
         <v>73</v>
@@ -41373,16 +41408,16 @@
         <v>73</v>
       </c>
       <c r="K355" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L355" t="s" s="2">
-        <v>204</v>
+        <v>406</v>
       </c>
       <c r="M355" t="s" s="2">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="N355" t="s" s="2">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="O355" s="2"/>
       <c r="P355" s="2"/>
@@ -41409,13 +41444,13 @@
         <v>73</v>
       </c>
       <c r="Y355" t="s" s="2">
-        <v>272</v>
+        <v>73</v>
       </c>
       <c r="Z355" t="s" s="2">
-        <v>894</v>
+        <v>73</v>
       </c>
       <c r="AA355" t="s" s="2">
-        <v>895</v>
+        <v>73</v>
       </c>
       <c r="AB355" t="s" s="2">
         <v>73</v>
@@ -41433,13 +41468,13 @@
         <v>73</v>
       </c>
       <c r="AG355" t="s" s="2">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="AH355" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI355" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ355" t="s" s="2">
         <v>73</v>
@@ -41450,13 +41485,13 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -41479,15 +41514,17 @@
         <v>73</v>
       </c>
       <c r="L356" t="s" s="2">
-        <v>347</v>
+        <v>794</v>
       </c>
       <c r="M356" t="s" s="2">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="N356" t="s" s="2">
-        <v>898</v>
-      </c>
-      <c r="O356" s="2"/>
+        <v>892</v>
+      </c>
+      <c r="O356" t="s" s="2">
+        <v>893</v>
+      </c>
       <c r="P356" s="2"/>
       <c r="Q356" t="s" s="2">
         <v>73</v>
@@ -41536,7 +41573,7 @@
         <v>73</v>
       </c>
       <c r="AG356" t="s" s="2">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="AH356" t="s" s="2">
         <v>74</v>
@@ -41553,13 +41590,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -41567,7 +41604,7 @@
       </c>
       <c r="F357" s="2"/>
       <c r="G357" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H357" t="s" s="2">
         <v>81</v>
@@ -41582,15 +41619,17 @@
         <v>73</v>
       </c>
       <c r="L357" t="s" s="2">
-        <v>173</v>
+        <v>616</v>
       </c>
       <c r="M357" t="s" s="2">
-        <v>162</v>
+        <v>895</v>
       </c>
       <c r="N357" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O357" s="2"/>
+        <v>896</v>
+      </c>
+      <c r="O357" t="s" s="2">
+        <v>897</v>
+      </c>
       <c r="P357" s="2"/>
       <c r="Q357" t="s" s="2">
         <v>73</v>
@@ -41639,41 +41678,41 @@
         <v>73</v>
       </c>
       <c r="AG357" t="s" s="2">
-        <v>164</v>
+        <v>894</v>
       </c>
       <c r="AH357" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI357" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ357" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK357" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H358" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I358" t="s" s="2">
         <v>73</v>
@@ -41682,20 +41721,18 @@
         <v>73</v>
       </c>
       <c r="K358" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L358" t="s" s="2">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="M358" t="s" s="2">
-        <v>128</v>
+        <v>899</v>
       </c>
       <c r="N358" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O358" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="O358" s="2"/>
       <c r="P358" s="2"/>
       <c r="Q358" t="s" s="2">
         <v>73</v>
@@ -41720,13 +41757,13 @@
         <v>73</v>
       </c>
       <c r="Y358" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z358" t="s" s="2">
-        <v>73</v>
+        <v>901</v>
       </c>
       <c r="AA358" t="s" s="2">
-        <v>73</v>
+        <v>902</v>
       </c>
       <c r="AB358" t="s" s="2">
         <v>73</v>
@@ -41744,34 +41781,34 @@
         <v>73</v>
       </c>
       <c r="AG358" t="s" s="2">
-        <v>171</v>
+        <v>898</v>
       </c>
       <c r="AH358" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI358" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ358" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK358" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F359" s="2"/>
       <c r="G359" t="s" s="2">
@@ -41784,26 +41821,22 @@
         <v>73</v>
       </c>
       <c r="J359" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K359" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L359" t="s" s="2">
-        <v>127</v>
+        <v>204</v>
       </c>
       <c r="M359" t="s" s="2">
-        <v>355</v>
+        <v>904</v>
       </c>
       <c r="N359" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O359" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P359" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>905</v>
+      </c>
+      <c r="O359" s="2"/>
+      <c r="P359" s="2"/>
       <c r="Q359" t="s" s="2">
         <v>73</v>
       </c>
@@ -41827,13 +41860,13 @@
         <v>73</v>
       </c>
       <c r="Y359" t="s" s="2">
-        <v>73</v>
+        <v>272</v>
       </c>
       <c r="Z359" t="s" s="2">
-        <v>73</v>
+        <v>906</v>
       </c>
       <c r="AA359" t="s" s="2">
-        <v>73</v>
+        <v>907</v>
       </c>
       <c r="AB359" t="s" s="2">
         <v>73</v>
@@ -41851,7 +41884,7 @@
         <v>73</v>
       </c>
       <c r="AG359" t="s" s="2">
-        <v>357</v>
+        <v>903</v>
       </c>
       <c r="AH359" t="s" s="2">
         <v>74</v>
@@ -41863,18 +41896,18 @@
         <v>73</v>
       </c>
       <c r="AK359" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -41882,10 +41915,10 @@
       </c>
       <c r="F360" s="2"/>
       <c r="G360" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H360" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I360" t="s" s="2">
         <v>73</v>
@@ -41897,13 +41930,13 @@
         <v>73</v>
       </c>
       <c r="L360" t="s" s="2">
-        <v>204</v>
+        <v>347</v>
       </c>
       <c r="M360" t="s" s="2">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="N360" t="s" s="2">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="O360" s="2"/>
       <c r="P360" s="2"/>
@@ -41930,13 +41963,13 @@
         <v>73</v>
       </c>
       <c r="Y360" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z360" t="s" s="2">
-        <v>793</v>
+        <v>73</v>
       </c>
       <c r="AA360" t="s" s="2">
-        <v>794</v>
+        <v>73</v>
       </c>
       <c r="AB360" t="s" s="2">
         <v>73</v>
@@ -41954,13 +41987,13 @@
         <v>73</v>
       </c>
       <c r="AG360" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="AH360" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI360" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ360" t="s" s="2">
         <v>73</v>
@@ -41971,13 +42004,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -41985,7 +42018,7 @@
       </c>
       <c r="F361" s="2"/>
       <c r="G361" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H361" t="s" s="2">
         <v>81</v>
@@ -42003,10 +42036,10 @@
         <v>173</v>
       </c>
       <c r="M361" t="s" s="2">
-        <v>906</v>
+        <v>162</v>
       </c>
       <c r="N361" t="s" s="2">
-        <v>907</v>
+        <v>163</v>
       </c>
       <c r="O361" s="2"/>
       <c r="P361" s="2"/>
@@ -42057,41 +42090,41 @@
         <v>73</v>
       </c>
       <c r="AG361" t="s" s="2">
-        <v>905</v>
+        <v>164</v>
       </c>
       <c r="AH361" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI361" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ361" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK361" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F362" s="2"/>
       <c r="G362" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H362" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I362" t="s" s="2">
         <v>73</v>
@@ -42103,15 +42136,17 @@
         <v>73</v>
       </c>
       <c r="L362" t="s" s="2">
-        <v>347</v>
+        <v>127</v>
       </c>
       <c r="M362" t="s" s="2">
-        <v>909</v>
+        <v>128</v>
       </c>
       <c r="N362" t="s" s="2">
-        <v>910</v>
-      </c>
-      <c r="O362" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O362" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P362" s="2"/>
       <c r="Q362" t="s" s="2">
         <v>73</v>
@@ -42160,62 +42195,66 @@
         <v>73</v>
       </c>
       <c r="AG362" t="s" s="2">
-        <v>908</v>
+        <v>171</v>
       </c>
       <c r="AH362" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI362" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ362" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK362" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F363" s="2"/>
       <c r="G363" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H363" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I363" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J363" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K363" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L363" t="s" s="2">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="M363" t="s" s="2">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="N363" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O363" s="2"/>
-      <c r="P363" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O363" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P363" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q363" t="s" s="2">
         <v>73</v>
       </c>
@@ -42263,41 +42302,41 @@
         <v>73</v>
       </c>
       <c r="AG363" t="s" s="2">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="AH363" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI363" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ363" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK363" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F364" s="2"/>
       <c r="G364" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H364" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I364" t="s" s="2">
         <v>73</v>
@@ -42309,17 +42348,15 @@
         <v>73</v>
       </c>
       <c r="L364" t="s" s="2">
-        <v>127</v>
+        <v>204</v>
       </c>
       <c r="M364" t="s" s="2">
-        <v>128</v>
+        <v>915</v>
       </c>
       <c r="N364" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O364" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>916</v>
+      </c>
+      <c r="O364" s="2"/>
       <c r="P364" s="2"/>
       <c r="Q364" t="s" s="2">
         <v>73</v>
@@ -42344,13 +42381,13 @@
         <v>73</v>
       </c>
       <c r="Y364" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z364" t="s" s="2">
-        <v>73</v>
+        <v>804</v>
       </c>
       <c r="AA364" t="s" s="2">
-        <v>73</v>
+        <v>805</v>
       </c>
       <c r="AB364" t="s" s="2">
         <v>73</v>
@@ -42368,66 +42405,62 @@
         <v>73</v>
       </c>
       <c r="AG364" t="s" s="2">
-        <v>171</v>
+        <v>914</v>
       </c>
       <c r="AH364" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AI364" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ364" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK364" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F365" s="2"/>
       <c r="G365" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H365" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I365" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J365" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K365" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L365" t="s" s="2">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="M365" t="s" s="2">
-        <v>355</v>
+        <v>918</v>
       </c>
       <c r="N365" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O365" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P365" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>919</v>
+      </c>
+      <c r="O365" s="2"/>
+      <c r="P365" s="2"/>
       <c r="Q365" t="s" s="2">
         <v>73</v>
       </c>
@@ -42475,30 +42508,30 @@
         <v>73</v>
       </c>
       <c r="AG365" t="s" s="2">
-        <v>357</v>
+        <v>917</v>
       </c>
       <c r="AH365" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AI365" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ365" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK365" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
@@ -42506,7 +42539,7 @@
       </c>
       <c r="F366" s="2"/>
       <c r="G366" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H366" t="s" s="2">
         <v>81</v>
@@ -42518,16 +42551,16 @@
         <v>73</v>
       </c>
       <c r="K366" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L366" t="s" s="2">
-        <v>915</v>
+        <v>347</v>
       </c>
       <c r="M366" t="s" s="2">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="N366" t="s" s="2">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="O366" s="2"/>
       <c r="P366" s="2"/>
@@ -42578,7 +42611,7 @@
         <v>73</v>
       </c>
       <c r="AG366" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="AH366" t="s" s="2">
         <v>74</v>
@@ -42595,13 +42628,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -42609,7 +42642,7 @@
       </c>
       <c r="F367" s="2"/>
       <c r="G367" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H367" t="s" s="2">
         <v>81</v>
@@ -42621,16 +42654,16 @@
         <v>73</v>
       </c>
       <c r="K367" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L367" t="s" s="2">
-        <v>406</v>
+        <v>173</v>
       </c>
       <c r="M367" t="s" s="2">
-        <v>919</v>
+        <v>162</v>
       </c>
       <c r="N367" t="s" s="2">
-        <v>920</v>
+        <v>163</v>
       </c>
       <c r="O367" s="2"/>
       <c r="P367" s="2"/>
@@ -42681,7 +42714,7 @@
         <v>73</v>
       </c>
       <c r="AG367" t="s" s="2">
-        <v>918</v>
+        <v>164</v>
       </c>
       <c r="AH367" t="s" s="2">
         <v>74</v>
@@ -42690,32 +42723,32 @@
         <v>81</v>
       </c>
       <c r="AJ367" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK367" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F368" s="2"/>
       <c r="G368" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H368" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I368" t="s" s="2">
         <v>73</v>
@@ -42724,18 +42757,20 @@
         <v>73</v>
       </c>
       <c r="K368" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L368" t="s" s="2">
-        <v>521</v>
+        <v>127</v>
       </c>
       <c r="M368" t="s" s="2">
-        <v>922</v>
+        <v>128</v>
       </c>
       <c r="N368" t="s" s="2">
-        <v>923</v>
-      </c>
-      <c r="O368" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O368" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P368" s="2"/>
       <c r="Q368" t="s" s="2">
         <v>73</v>
@@ -42784,62 +42819,66 @@
         <v>73</v>
       </c>
       <c r="AG368" t="s" s="2">
-        <v>921</v>
+        <v>171</v>
       </c>
       <c r="AH368" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI368" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ368" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK368" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F369" s="2"/>
       <c r="G369" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H369" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I369" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J369" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K369" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L369" t="s" s="2">
-        <v>925</v>
+        <v>127</v>
       </c>
       <c r="M369" t="s" s="2">
-        <v>926</v>
+        <v>355</v>
       </c>
       <c r="N369" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="O369" s="2"/>
-      <c r="P369" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O369" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P369" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q369" t="s" s="2">
         <v>73</v>
       </c>
@@ -42887,30 +42926,30 @@
         <v>73</v>
       </c>
       <c r="AG369" t="s" s="2">
-        <v>924</v>
+        <v>357</v>
       </c>
       <c r="AH369" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI369" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ369" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK369" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
@@ -42930,16 +42969,16 @@
         <v>73</v>
       </c>
       <c r="K370" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L370" t="s" s="2">
-        <v>204</v>
+        <v>927</v>
       </c>
       <c r="M370" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="N370" t="s" s="2">
         <v>929</v>
-      </c>
-      <c r="N370" t="s" s="2">
-        <v>930</v>
       </c>
       <c r="O370" s="2"/>
       <c r="P370" s="2"/>
@@ -42966,13 +43005,13 @@
         <v>73</v>
       </c>
       <c r="Y370" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z370" t="s" s="2">
-        <v>931</v>
+        <v>73</v>
       </c>
       <c r="AA370" t="s" s="2">
-        <v>932</v>
+        <v>73</v>
       </c>
       <c r="AB370" t="s" s="2">
         <v>73</v>
@@ -42990,7 +43029,7 @@
         <v>73</v>
       </c>
       <c r="AG370" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="AH370" t="s" s="2">
         <v>74</v>
@@ -43007,13 +43046,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -43021,7 +43060,7 @@
       </c>
       <c r="F371" s="2"/>
       <c r="G371" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H371" t="s" s="2">
         <v>81</v>
@@ -43033,16 +43072,16 @@
         <v>73</v>
       </c>
       <c r="K371" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L371" t="s" s="2">
-        <v>544</v>
+        <v>406</v>
       </c>
       <c r="M371" t="s" s="2">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="N371" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="O371" s="2"/>
       <c r="P371" s="2"/>
@@ -43069,10 +43108,10 @@
         <v>73</v>
       </c>
       <c r="Y371" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z371" t="s" s="2">
-        <v>935</v>
+        <v>73</v>
       </c>
       <c r="AA371" t="s" s="2">
         <v>73</v>
@@ -43093,7 +43132,7 @@
         <v>73</v>
       </c>
       <c r="AG371" t="s" s="2">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="AH371" t="s" s="2">
         <v>74</v>
@@ -43110,13 +43149,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -43136,16 +43175,16 @@
         <v>73</v>
       </c>
       <c r="K372" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L372" t="s" s="2">
-        <v>937</v>
+        <v>521</v>
       </c>
       <c r="M372" t="s" s="2">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="N372" t="s" s="2">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="O372" s="2"/>
       <c r="P372" s="2"/>
@@ -43196,7 +43235,7 @@
         <v>73</v>
       </c>
       <c r="AG372" t="s" s="2">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="AH372" t="s" s="2">
         <v>74</v>
@@ -43213,13 +43252,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="D373" s="2"/>
       <c r="E373" t="s" s="2">
@@ -43242,17 +43281,15 @@
         <v>73</v>
       </c>
       <c r="L373" t="s" s="2">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="M373" t="s" s="2">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="N373" t="s" s="2">
-        <v>943</v>
-      </c>
-      <c r="O373" t="s" s="2">
-        <v>944</v>
-      </c>
+        <v>939</v>
+      </c>
+      <c r="O373" s="2"/>
       <c r="P373" s="2"/>
       <c r="Q373" t="s" s="2">
         <v>73</v>
@@ -43277,13 +43314,13 @@
         <v>73</v>
       </c>
       <c r="Y373" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z373" t="s" s="2">
-        <v>793</v>
+        <v>73</v>
       </c>
       <c r="AA373" t="s" s="2">
-        <v>794</v>
+        <v>73</v>
       </c>
       <c r="AB373" t="s" s="2">
         <v>73</v>
@@ -43301,7 +43338,7 @@
         <v>73</v>
       </c>
       <c r="AG373" t="s" s="2">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="AH373" t="s" s="2">
         <v>74</v>
@@ -43318,13 +43355,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
@@ -43344,23 +43381,19 @@
         <v>73</v>
       </c>
       <c r="K374" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L374" t="s" s="2">
-        <v>946</v>
+        <v>204</v>
       </c>
       <c r="M374" t="s" s="2">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="N374" t="s" s="2">
-        <v>948</v>
-      </c>
-      <c r="O374" t="s" s="2">
-        <v>949</v>
-      </c>
-      <c r="P374" t="s" s="2">
-        <v>950</v>
-      </c>
+        <v>942</v>
+      </c>
+      <c r="O374" s="2"/>
+      <c r="P374" s="2"/>
       <c r="Q374" t="s" s="2">
         <v>73</v>
       </c>
@@ -43384,13 +43417,13 @@
         <v>73</v>
       </c>
       <c r="Y374" t="s" s="2">
-        <v>183</v>
+        <v>265</v>
       </c>
       <c r="Z374" t="s" s="2">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="AA374" t="s" s="2">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="AB374" t="s" s="2">
         <v>73</v>
@@ -43408,7 +43441,7 @@
         <v>73</v>
       </c>
       <c r="AG374" t="s" s="2">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="AH374" t="s" s="2">
         <v>74</v>
@@ -43425,13 +43458,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -43442,7 +43475,7 @@
         <v>74</v>
       </c>
       <c r="H375" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I375" t="s" s="2">
         <v>73</v>
@@ -43454,13 +43487,13 @@
         <v>73</v>
       </c>
       <c r="L375" t="s" s="2">
-        <v>347</v>
+        <v>544</v>
       </c>
       <c r="M375" t="s" s="2">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="N375" t="s" s="2">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="O375" s="2"/>
       <c r="P375" s="2"/>
@@ -43487,10 +43520,10 @@
         <v>73</v>
       </c>
       <c r="Y375" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z375" t="s" s="2">
-        <v>73</v>
+        <v>947</v>
       </c>
       <c r="AA375" t="s" s="2">
         <v>73</v>
@@ -43511,13 +43544,13 @@
         <v>73</v>
       </c>
       <c r="AG375" t="s" s="2">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="AH375" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI375" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ375" t="s" s="2">
         <v>73</v>
@@ -43528,13 +43561,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -43557,13 +43590,13 @@
         <v>73</v>
       </c>
       <c r="L376" t="s" s="2">
-        <v>173</v>
+        <v>949</v>
       </c>
       <c r="M376" t="s" s="2">
-        <v>162</v>
+        <v>950</v>
       </c>
       <c r="N376" t="s" s="2">
-        <v>163</v>
+        <v>951</v>
       </c>
       <c r="O376" s="2"/>
       <c r="P376" s="2"/>
@@ -43614,7 +43647,7 @@
         <v>73</v>
       </c>
       <c r="AG376" t="s" s="2">
-        <v>164</v>
+        <v>948</v>
       </c>
       <c r="AH376" t="s" s="2">
         <v>74</v>
@@ -43623,32 +43656,32 @@
         <v>81</v>
       </c>
       <c r="AJ376" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK376" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F377" s="2"/>
       <c r="G377" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H377" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I377" t="s" s="2">
         <v>73</v>
@@ -43660,16 +43693,16 @@
         <v>73</v>
       </c>
       <c r="L377" t="s" s="2">
-        <v>127</v>
+        <v>953</v>
       </c>
       <c r="M377" t="s" s="2">
-        <v>128</v>
+        <v>954</v>
       </c>
       <c r="N377" t="s" s="2">
-        <v>167</v>
+        <v>955</v>
       </c>
       <c r="O377" t="s" s="2">
-        <v>130</v>
+        <v>956</v>
       </c>
       <c r="P377" s="2"/>
       <c r="Q377" t="s" s="2">
@@ -43695,13 +43728,13 @@
         <v>73</v>
       </c>
       <c r="Y377" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z377" t="s" s="2">
-        <v>73</v>
+        <v>804</v>
       </c>
       <c r="AA377" t="s" s="2">
-        <v>73</v>
+        <v>805</v>
       </c>
       <c r="AB377" t="s" s="2">
         <v>73</v>
@@ -43719,65 +43752,65 @@
         <v>73</v>
       </c>
       <c r="AG377" t="s" s="2">
-        <v>171</v>
+        <v>952</v>
       </c>
       <c r="AH377" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI377" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ377" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK377" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F378" s="2"/>
       <c r="G378" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H378" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I378" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J378" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K378" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L378" t="s" s="2">
-        <v>127</v>
+        <v>958</v>
       </c>
       <c r="M378" t="s" s="2">
-        <v>355</v>
+        <v>959</v>
       </c>
       <c r="N378" t="s" s="2">
-        <v>356</v>
+        <v>960</v>
       </c>
       <c r="O378" t="s" s="2">
-        <v>130</v>
+        <v>961</v>
       </c>
       <c r="P378" t="s" s="2">
-        <v>136</v>
+        <v>962</v>
       </c>
       <c r="Q378" t="s" s="2">
         <v>73</v>
@@ -43802,13 +43835,13 @@
         <v>73</v>
       </c>
       <c r="Y378" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="Z378" t="s" s="2">
-        <v>73</v>
+        <v>963</v>
       </c>
       <c r="AA378" t="s" s="2">
-        <v>73</v>
+        <v>964</v>
       </c>
       <c r="AB378" t="s" s="2">
         <v>73</v>
@@ -43826,30 +43859,30 @@
         <v>73</v>
       </c>
       <c r="AG378" t="s" s="2">
-        <v>357</v>
+        <v>957</v>
       </c>
       <c r="AH378" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI378" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ378" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK378" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -43860,7 +43893,7 @@
         <v>74</v>
       </c>
       <c r="H379" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I379" t="s" s="2">
         <v>73</v>
@@ -43872,13 +43905,13 @@
         <v>73</v>
       </c>
       <c r="L379" t="s" s="2">
-        <v>173</v>
+        <v>347</v>
       </c>
       <c r="M379" t="s" s="2">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="N379" t="s" s="2">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="O379" s="2"/>
       <c r="P379" s="2"/>
@@ -43929,13 +43962,13 @@
         <v>73</v>
       </c>
       <c r="AG379" t="s" s="2">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="AH379" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI379" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ379" t="s" s="2">
         <v>73</v>
@@ -43946,13 +43979,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -43975,13 +44008,13 @@
         <v>73</v>
       </c>
       <c r="L380" t="s" s="2">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="M380" t="s" s="2">
-        <v>963</v>
+        <v>162</v>
       </c>
       <c r="N380" t="s" s="2">
-        <v>964</v>
+        <v>163</v>
       </c>
       <c r="O380" s="2"/>
       <c r="P380" s="2"/>
@@ -44008,13 +44041,13 @@
         <v>73</v>
       </c>
       <c r="Y380" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z380" t="s" s="2">
-        <v>965</v>
+        <v>73</v>
       </c>
       <c r="AA380" t="s" s="2">
-        <v>966</v>
+        <v>73</v>
       </c>
       <c r="AB380" t="s" s="2">
         <v>73</v>
@@ -44032,7 +44065,7 @@
         <v>73</v>
       </c>
       <c r="AG380" t="s" s="2">
-        <v>962</v>
+        <v>164</v>
       </c>
       <c r="AH380" t="s" s="2">
         <v>74</v>
@@ -44041,25 +44074,25 @@
         <v>81</v>
       </c>
       <c r="AJ380" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK380" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F381" s="2"/>
       <c r="G381" t="s" s="2">
@@ -44078,15 +44111,17 @@
         <v>73</v>
       </c>
       <c r="L381" t="s" s="2">
-        <v>968</v>
+        <v>127</v>
       </c>
       <c r="M381" t="s" s="2">
-        <v>969</v>
+        <v>128</v>
       </c>
       <c r="N381" t="s" s="2">
-        <v>970</v>
-      </c>
-      <c r="O381" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O381" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P381" s="2"/>
       <c r="Q381" t="s" s="2">
         <v>73</v>
@@ -44135,7 +44170,7 @@
         <v>73</v>
       </c>
       <c r="AG381" t="s" s="2">
-        <v>967</v>
+        <v>171</v>
       </c>
       <c r="AH381" t="s" s="2">
         <v>74</v>
@@ -44147,50 +44182,54 @@
         <v>73</v>
       </c>
       <c r="AK381" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F382" s="2"/>
       <c r="G382" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H382" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I382" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J382" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K382" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L382" t="s" s="2">
-        <v>972</v>
+        <v>127</v>
       </c>
       <c r="M382" t="s" s="2">
-        <v>973</v>
+        <v>355</v>
       </c>
       <c r="N382" t="s" s="2">
-        <v>974</v>
-      </c>
-      <c r="O382" s="2"/>
-      <c r="P382" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O382" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P382" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q382" t="s" s="2">
         <v>73</v>
       </c>
@@ -44238,30 +44277,30 @@
         <v>73</v>
       </c>
       <c r="AG382" t="s" s="2">
-        <v>971</v>
+        <v>357</v>
       </c>
       <c r="AH382" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI382" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ382" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK382" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -44269,10 +44308,10 @@
       </c>
       <c r="F383" s="2"/>
       <c r="G383" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H383" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I383" t="s" s="2">
         <v>73</v>
@@ -44284,13 +44323,13 @@
         <v>73</v>
       </c>
       <c r="L383" t="s" s="2">
-        <v>347</v>
+        <v>173</v>
       </c>
       <c r="M383" t="s" s="2">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="N383" t="s" s="2">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="O383" s="2"/>
       <c r="P383" s="2"/>
@@ -44341,13 +44380,13 @@
         <v>73</v>
       </c>
       <c r="AG383" t="s" s="2">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="AH383" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI383" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ383" t="s" s="2">
         <v>73</v>
@@ -44358,13 +44397,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -44387,13 +44426,13 @@
         <v>73</v>
       </c>
       <c r="L384" t="s" s="2">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="M384" t="s" s="2">
-        <v>162</v>
+        <v>975</v>
       </c>
       <c r="N384" t="s" s="2">
-        <v>163</v>
+        <v>976</v>
       </c>
       <c r="O384" s="2"/>
       <c r="P384" s="2"/>
@@ -44420,13 +44459,13 @@
         <v>73</v>
       </c>
       <c r="Y384" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z384" t="s" s="2">
-        <v>73</v>
+        <v>977</v>
       </c>
       <c r="AA384" t="s" s="2">
-        <v>73</v>
+        <v>978</v>
       </c>
       <c r="AB384" t="s" s="2">
         <v>73</v>
@@ -44444,7 +44483,7 @@
         <v>73</v>
       </c>
       <c r="AG384" t="s" s="2">
-        <v>164</v>
+        <v>974</v>
       </c>
       <c r="AH384" t="s" s="2">
         <v>74</v>
@@ -44453,15 +44492,15 @@
         <v>81</v>
       </c>
       <c r="AJ384" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK384" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>979</v>
@@ -44471,7 +44510,7 @@
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F385" s="2"/>
       <c r="G385" t="s" s="2">
@@ -44490,17 +44529,15 @@
         <v>73</v>
       </c>
       <c r="L385" t="s" s="2">
-        <v>127</v>
+        <v>980</v>
       </c>
       <c r="M385" t="s" s="2">
-        <v>128</v>
+        <v>981</v>
       </c>
       <c r="N385" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O385" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>982</v>
+      </c>
+      <c r="O385" s="2"/>
       <c r="P385" s="2"/>
       <c r="Q385" t="s" s="2">
         <v>73</v>
@@ -44549,7 +44586,7 @@
         <v>73</v>
       </c>
       <c r="AG385" t="s" s="2">
-        <v>171</v>
+        <v>979</v>
       </c>
       <c r="AH385" t="s" s="2">
         <v>74</v>
@@ -44561,54 +44598,50 @@
         <v>73</v>
       </c>
       <c r="AK385" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F386" s="2"/>
       <c r="G386" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H386" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I386" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J386" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K386" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L386" t="s" s="2">
-        <v>127</v>
+        <v>984</v>
       </c>
       <c r="M386" t="s" s="2">
-        <v>355</v>
+        <v>985</v>
       </c>
       <c r="N386" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O386" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P386" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>986</v>
+      </c>
+      <c r="O386" s="2"/>
+      <c r="P386" s="2"/>
       <c r="Q386" t="s" s="2">
         <v>73</v>
       </c>
@@ -44656,30 +44689,30 @@
         <v>73</v>
       </c>
       <c r="AG386" t="s" s="2">
-        <v>357</v>
+        <v>983</v>
       </c>
       <c r="AH386" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI386" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ386" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK386" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -44690,7 +44723,7 @@
         <v>81</v>
       </c>
       <c r="H387" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I387" t="s" s="2">
         <v>73</v>
@@ -44702,13 +44735,13 @@
         <v>73</v>
       </c>
       <c r="L387" t="s" s="2">
-        <v>557</v>
+        <v>347</v>
       </c>
       <c r="M387" t="s" s="2">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="N387" t="s" s="2">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="O387" s="2"/>
       <c r="P387" s="2"/>
@@ -44759,13 +44792,13 @@
         <v>73</v>
       </c>
       <c r="AG387" t="s" s="2">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="AH387" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI387" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ387" t="s" s="2">
         <v>73</v>
@@ -44776,13 +44809,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
@@ -44805,13 +44838,13 @@
         <v>73</v>
       </c>
       <c r="L388" t="s" s="2">
-        <v>276</v>
+        <v>173</v>
       </c>
       <c r="M388" t="s" s="2">
-        <v>985</v>
+        <v>162</v>
       </c>
       <c r="N388" t="s" s="2">
-        <v>986</v>
+        <v>163</v>
       </c>
       <c r="O388" s="2"/>
       <c r="P388" s="2"/>
@@ -44862,7 +44895,7 @@
         <v>73</v>
       </c>
       <c r="AG388" t="s" s="2">
-        <v>984</v>
+        <v>164</v>
       </c>
       <c r="AH388" t="s" s="2">
         <v>74</v>
@@ -44871,32 +44904,32 @@
         <v>81</v>
       </c>
       <c r="AJ388" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK388" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F389" s="2"/>
       <c r="G389" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H389" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I389" t="s" s="2">
         <v>73</v>
@@ -44908,15 +44941,17 @@
         <v>73</v>
       </c>
       <c r="L389" t="s" s="2">
-        <v>925</v>
+        <v>127</v>
       </c>
       <c r="M389" t="s" s="2">
-        <v>988</v>
+        <v>128</v>
       </c>
       <c r="N389" t="s" s="2">
-        <v>989</v>
-      </c>
-      <c r="O389" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O389" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P389" s="2"/>
       <c r="Q389" t="s" s="2">
         <v>73</v>
@@ -44965,34 +45000,34 @@
         <v>73</v>
       </c>
       <c r="AG389" t="s" s="2">
-        <v>987</v>
+        <v>171</v>
       </c>
       <c r="AH389" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI389" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ389" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK389" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F390" s="2"/>
       <c r="G390" t="s" s="2">
@@ -45005,25 +45040,25 @@
         <v>73</v>
       </c>
       <c r="J390" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K390" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L390" t="s" s="2">
-        <v>204</v>
+        <v>127</v>
       </c>
       <c r="M390" t="s" s="2">
-        <v>991</v>
+        <v>355</v>
       </c>
       <c r="N390" t="s" s="2">
-        <v>992</v>
+        <v>356</v>
       </c>
       <c r="O390" t="s" s="2">
-        <v>993</v>
+        <v>130</v>
       </c>
       <c r="P390" t="s" s="2">
-        <v>994</v>
+        <v>136</v>
       </c>
       <c r="Q390" t="s" s="2">
         <v>73</v>
@@ -45048,13 +45083,13 @@
         <v>73</v>
       </c>
       <c r="Y390" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z390" t="s" s="2">
-        <v>995</v>
+        <v>73</v>
       </c>
       <c r="AA390" t="s" s="2">
-        <v>996</v>
+        <v>73</v>
       </c>
       <c r="AB390" t="s" s="2">
         <v>73</v>
@@ -45072,7 +45107,7 @@
         <v>73</v>
       </c>
       <c r="AG390" t="s" s="2">
-        <v>990</v>
+        <v>357</v>
       </c>
       <c r="AH390" t="s" s="2">
         <v>74</v>
@@ -45084,18 +45119,18 @@
         <v>73</v>
       </c>
       <c r="AK390" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
@@ -45103,10 +45138,10 @@
       </c>
       <c r="F391" s="2"/>
       <c r="G391" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H391" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I391" t="s" s="2">
         <v>73</v>
@@ -45118,13 +45153,13 @@
         <v>73</v>
       </c>
       <c r="L391" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="M391" t="s" s="2">
-        <v>50</v>
+        <v>994</v>
       </c>
       <c r="N391" t="s" s="2">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="O391" s="2"/>
       <c r="P391" s="2"/>
@@ -45175,18 +45210,434 @@
         <v>73</v>
       </c>
       <c r="AG391" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="AH391" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI391" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ391" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK391" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B392" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="C392" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="D392" s="2"/>
+      <c r="E392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F392" s="2"/>
+      <c r="G392" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H392" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L392" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M392" t="s" s="2">
         <v>997</v>
       </c>
-      <c r="AH391" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI391" t="s" s="2">
+      <c r="N392" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="O392" s="2"/>
+      <c r="P392" s="2"/>
+      <c r="Q392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R392" s="2"/>
+      <c r="S392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG392" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="AH392" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI392" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ392" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK392" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B393" t="s" s="2">
+        <v>999</v>
+      </c>
+      <c r="C393" t="s" s="2">
+        <v>999</v>
+      </c>
+      <c r="D393" s="2"/>
+      <c r="E393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F393" s="2"/>
+      <c r="G393" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H393" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L393" t="s" s="2">
+        <v>937</v>
+      </c>
+      <c r="M393" t="s" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N393" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="O393" s="2"/>
+      <c r="P393" s="2"/>
+      <c r="Q393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R393" s="2"/>
+      <c r="S393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG393" t="s" s="2">
+        <v>999</v>
+      </c>
+      <c r="AH393" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI393" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ393" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK393" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B394" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C394" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D394" s="2"/>
+      <c r="E394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F394" s="2"/>
+      <c r="G394" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H394" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AJ391" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK391" t="s" s="2">
+      <c r="I394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K394" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L394" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M394" t="s" s="2">
+        <v>1003</v>
+      </c>
+      <c r="N394" t="s" s="2">
+        <v>1004</v>
+      </c>
+      <c r="O394" t="s" s="2">
+        <v>1005</v>
+      </c>
+      <c r="P394" t="s" s="2">
+        <v>1006</v>
+      </c>
+      <c r="Q394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R394" s="2"/>
+      <c r="S394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y394" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z394" t="s" s="2">
+        <v>1007</v>
+      </c>
+      <c r="AA394" t="s" s="2">
+        <v>1008</v>
+      </c>
+      <c r="AB394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG394" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="AH394" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI394" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ394" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK394" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B395" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="C395" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="D395" s="2"/>
+      <c r="E395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F395" s="2"/>
+      <c r="G395" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H395" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L395" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M395" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="N395" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="O395" s="2"/>
+      <c r="P395" s="2"/>
+      <c r="Q395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R395" s="2"/>
+      <c r="S395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG395" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="AH395" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI395" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ395" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK395" t="s" s="2">
         <v>93</v>
       </c>
     </row>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T07:57:25+00:00</t>
+    <t>2026-03-19T11:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T11:47:55+00:00</t>
+    <t>2026-03-20T10:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T10:04:21+00:00</t>
+    <t>2026-03-20T11:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:14:53+00:00</t>
+    <t>2026-03-20T11:25:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:25:24+00:00</t>
+    <t>2026-03-20T11:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:48:45+00:00</t>
+    <t>2026-03-20T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:42:40+00:00</t>
+    <t>2026-03-20T12:57:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:57:31+00:00</t>
+    <t>2026-03-20T13:17:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -814,7 +814,7 @@
     <t>PractitionerRole.organization.identifier.system</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/organization-it-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/organization-id-type-vs</t>
   </si>
   <si>
     <t>PractitionerRole.organization.identifier.value</t>
@@ -2272,7 +2272,7 @@
     <t>ServiceRequest.subject.identifier.system</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/public-it-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/public-id-type-vs</t>
   </si>
   <si>
     <t>ServiceRequest.subject.identifier.value</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:25:48+00:00</t>
+    <t>2026-04-10T11:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:43:13+00:00</t>
+    <t>2026-04-10T11:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:51:44+00:00</t>
+    <t>2026-04-10T12:03:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:03:27+00:00</t>
+    <t>2026-04-10T12:17:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:17:42+00:00</t>
+    <t>2026-04-10T12:43:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:43:41+00:00</t>
+    <t>2026-04-10T12:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:51:31+00:00</t>
+    <t>2026-04-10T13:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:11:24+00:00</t>
+    <t>2026-04-13T12:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T12:24:04+00:00</t>
+    <t>2026-04-13T13:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13291" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13291" uniqueCount="1028">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.5</t>
+    <t>0.1.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T13:08:41+00:00</t>
+    <t>2026-04-15T12:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -701,7 +701,7 @@
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/person-id-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/healthcare-person-id-type-vs</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -2321,7 +2321,7 @@
     <t>ServiceRequest.subject.identifier.system</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/public-id-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/person-public-id-type-vs</t>
   </si>
   <si>
     <t>ServiceRequest.subject.identifier.value</t>
@@ -2429,6 +2429,10 @@
   </si>
   <si>
     <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+local-reference-only:Referansen må være lokal (starte med #) og peke til en inneholdt ressurs. {reference.startsWith('#')}</t>
   </si>
   <si>
     <t>ServiceRequest.performerType</t>
@@ -4167,7 +4171,7 @@
         <v>2</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="108">
@@ -4175,7 +4179,7 @@
         <v>4</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="109">
@@ -4191,7 +4195,7 @@
         <v>8</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="111">
@@ -4251,7 +4255,7 @@
         <v>22</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="119">
@@ -4287,7 +4291,7 @@
         <v>29</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="124">
@@ -4295,7 +4299,7 @@
         <v>31</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="125">
@@ -32249,13 +32253,13 @@
       </c>
       <c r="F267" s="2"/>
       <c r="G267" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H267" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I267" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J267" t="s" s="2">
         <v>73</v>
@@ -36194,7 +36198,7 @@
         <v>73</v>
       </c>
       <c r="AK304" t="s" s="2">
-        <v>93</v>
+        <v>773</v>
       </c>
     </row>
     <row r="305">
@@ -36202,14 +36206,14 @@
         <v>569</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F305" s="2"/>
       <c r="G305" t="s" s="2">
@@ -36231,13 +36235,13 @@
         <v>204</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N305" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O305" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="P305" s="2"/>
       <c r="Q305" t="s" s="2">
@@ -36266,10 +36270,10 @@
         <v>265</v>
       </c>
       <c r="Z305" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AA305" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AB305" t="s" s="2">
         <v>73</v>
@@ -36287,7 +36291,7 @@
         <v>73</v>
       </c>
       <c r="AG305" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AH305" t="s" s="2">
         <v>74</v>
@@ -36307,14 +36311,14 @@
         <v>569</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F306" s="2"/>
       <c r="G306" t="s" s="2">
@@ -36333,16 +36337,16 @@
         <v>82</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N306" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="O306" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P306" s="2"/>
       <c r="Q306" t="s" s="2">
@@ -36392,7 +36396,7 @@
         <v>73</v>
       </c>
       <c r="AG306" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AH306" t="s" s="2">
         <v>74</v>
@@ -36412,10 +36416,10 @@
         <v>569</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
@@ -36438,13 +36442,13 @@
         <v>82</v>
       </c>
       <c r="L307" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M307" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N307" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="O307" s="2"/>
       <c r="P307" s="2"/>
@@ -36474,10 +36478,10 @@
         <v>265</v>
       </c>
       <c r="Z307" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AA307" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AB307" t="s" s="2">
         <v>73</v>
@@ -36495,7 +36499,7 @@
         <v>73</v>
       </c>
       <c r="AG307" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AH307" t="s" s="2">
         <v>74</v>
@@ -36515,10 +36519,10 @@
         <v>569</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" t="s" s="2">
@@ -36541,16 +36545,16 @@
         <v>82</v>
       </c>
       <c r="L308" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="M308" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N308" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="O308" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="P308" s="2"/>
       <c r="Q308" t="s" s="2">
@@ -36579,10 +36583,10 @@
         <v>265</v>
       </c>
       <c r="Z308" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AA308" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AB308" t="s" s="2">
         <v>73</v>
@@ -36600,7 +36604,7 @@
         <v>73</v>
       </c>
       <c r="AG308" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AH308" t="s" s="2">
         <v>74</v>
@@ -36620,10 +36624,10 @@
         <v>569</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
@@ -36646,13 +36650,13 @@
         <v>73</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N309" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="O309" s="2"/>
       <c r="P309" s="2"/>
@@ -36703,7 +36707,7 @@
         <v>73</v>
       </c>
       <c r="AG309" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AH309" t="s" s="2">
         <v>74</v>
@@ -36723,14 +36727,14 @@
         <v>569</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F310" s="2"/>
       <c r="G310" t="s" s="2">
@@ -36749,16 +36753,16 @@
         <v>73</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N310" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="O310" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="P310" s="2"/>
       <c r="Q310" t="s" s="2">
@@ -36808,7 +36812,7 @@
         <v>73</v>
       </c>
       <c r="AG310" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AH310" t="s" s="2">
         <v>74</v>
@@ -36828,10 +36832,10 @@
         <v>569</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -36854,16 +36858,16 @@
         <v>82</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="N311" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="O311" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="P311" s="2"/>
       <c r="Q311" t="s" s="2">
@@ -36913,7 +36917,7 @@
         <v>73</v>
       </c>
       <c r="AG311" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AH311" t="s" s="2">
         <v>74</v>
@@ -36933,14 +36937,14 @@
         <v>569</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" t="s" s="2">
@@ -36962,16 +36966,16 @@
         <v>204</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O312" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="P312" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="Q312" t="s" s="2">
         <v>73</v>
@@ -36999,10 +37003,10 @@
         <v>265</v>
       </c>
       <c r="Z312" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AA312" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AB312" t="s" s="2">
         <v>73</v>
@@ -37020,7 +37024,7 @@
         <v>73</v>
       </c>
       <c r="AG312" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AH312" t="s" s="2">
         <v>74</v>
@@ -37029,7 +37033,7 @@
         <v>75</v>
       </c>
       <c r="AJ312" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AK312" t="s" s="2">
         <v>93</v>
@@ -37040,14 +37044,14 @@
         <v>569</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F313" s="2"/>
       <c r="G313" t="s" s="2">
@@ -37066,17 +37070,17 @@
         <v>82</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="N313" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O313" s="2"/>
       <c r="P313" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="Q313" t="s" s="2">
         <v>73</v>
@@ -37125,16 +37129,16 @@
         <v>73</v>
       </c>
       <c r="AG313" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="AH313" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI313" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ313" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="AH313" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ313" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="AK313" t="s" s="2">
         <v>93</v>
@@ -37145,10 +37149,10 @@
         <v>569</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -37177,7 +37181,7 @@
         <v>50</v>
       </c>
       <c r="N314" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="O314" s="2"/>
       <c r="P314" s="2"/>
@@ -37228,7 +37232,7 @@
         <v>73</v>
       </c>
       <c r="AG314" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AH314" t="s" s="2">
         <v>74</v>
@@ -37248,10 +37252,10 @@
         <v>569</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -37277,10 +37281,10 @@
         <v>347</v>
       </c>
       <c r="M315" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="N315" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="O315" s="2"/>
       <c r="P315" s="2"/>
@@ -37331,7 +37335,7 @@
         <v>73</v>
       </c>
       <c r="AG315" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AH315" t="s" s="2">
         <v>74</v>
@@ -37351,10 +37355,10 @@
         <v>569</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
@@ -37454,10 +37458,10 @@
         <v>569</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
@@ -37559,10 +37563,10 @@
         <v>569</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
@@ -37666,10 +37670,10 @@
         <v>569</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -37692,13 +37696,13 @@
         <v>82</v>
       </c>
       <c r="L319" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M319" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="N319" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="O319" s="2"/>
       <c r="P319" s="2"/>
@@ -37749,7 +37753,7 @@
         <v>73</v>
       </c>
       <c r="AG319" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AH319" t="s" s="2">
         <v>74</v>
@@ -37769,10 +37773,10 @@
         <v>569</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
@@ -37795,16 +37799,16 @@
         <v>73</v>
       </c>
       <c r="L320" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="M320" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="N320" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="O320" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="P320" s="2"/>
       <c r="Q320" t="s" s="2">
@@ -37854,7 +37858,7 @@
         <v>73</v>
       </c>
       <c r="AG320" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AH320" t="s" s="2">
         <v>74</v>
@@ -37871,13 +37875,13 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -37903,10 +37907,10 @@
         <v>76</v>
       </c>
       <c r="M321" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N321" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="O321" s="2"/>
       <c r="P321" s="2"/>
@@ -37957,7 +37961,7 @@
         <v>73</v>
       </c>
       <c r="AG321" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AH321" t="s" s="2">
         <v>74</v>
@@ -37974,13 +37978,13 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
@@ -38079,13 +38083,13 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
@@ -38182,13 +38186,13 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
@@ -38287,13 +38291,13 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -38392,13 +38396,13 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -38497,13 +38501,13 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -38511,7 +38515,7 @@
       </c>
       <c r="F327" s="2"/>
       <c r="G327" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H327" t="s" s="2">
         <v>75</v>
@@ -38526,7 +38530,7 @@
         <v>73</v>
       </c>
       <c r="L327" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M327" t="s" s="2">
         <v>77</v>
@@ -38602,13 +38606,13 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
@@ -38707,13 +38711,13 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -38814,13 +38818,13 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
@@ -38846,10 +38850,10 @@
         <v>139</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="O330" s="2"/>
       <c r="P330" s="2"/>
@@ -38900,7 +38904,7 @@
         <v>73</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AH330" t="s" s="2">
         <v>74</v>
@@ -38917,13 +38921,13 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -39020,13 +39024,13 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -39125,13 +39129,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -39232,13 +39236,13 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -39339,13 +39343,13 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -39446,13 +39450,13 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
@@ -39551,13 +39555,13 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -39654,13 +39658,13 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
@@ -39759,13 +39763,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -39791,10 +39795,10 @@
         <v>139</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="N339" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="O339" s="2"/>
       <c r="P339" s="2"/>
@@ -39845,7 +39849,7 @@
         <v>73</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>74</v>
@@ -39862,13 +39866,13 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -39894,13 +39898,13 @@
         <v>101</v>
       </c>
       <c r="M340" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="N340" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="O340" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="P340" s="2"/>
       <c r="Q340" t="s" s="2">
@@ -39929,10 +39933,10 @@
         <v>105</v>
       </c>
       <c r="Z340" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AA340" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AB340" t="s" s="2">
         <v>73</v>
@@ -39950,7 +39954,7 @@
         <v>73</v>
       </c>
       <c r="AG340" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AH340" t="s" s="2">
         <v>74</v>
@@ -39967,13 +39971,13 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -39999,13 +40003,13 @@
         <v>204</v>
       </c>
       <c r="M341" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="N341" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="O341" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="P341" s="2"/>
       <c r="Q341" t="s" s="2">
@@ -40035,7 +40039,7 @@
       </c>
       <c r="Z341" s="2"/>
       <c r="AA341" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="AB341" t="s" s="2">
         <v>73</v>
@@ -40053,7 +40057,7 @@
         <v>73</v>
       </c>
       <c r="AG341" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AH341" t="s" s="2">
         <v>74</v>
@@ -40070,13 +40074,13 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" t="s" s="2">
@@ -40102,14 +40106,14 @@
         <v>726</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="N342" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="O342" s="2"/>
       <c r="P342" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="Q342" t="s" s="2">
         <v>73</v>
@@ -40158,7 +40162,7 @@
         <v>73</v>
       </c>
       <c r="AG342" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AH342" t="s" s="2">
         <v>74</v>
@@ -40175,13 +40179,13 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
@@ -40278,13 +40282,13 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
@@ -40383,13 +40387,13 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -40488,13 +40492,13 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
@@ -40593,13 +40597,13 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
@@ -40698,13 +40702,13 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
@@ -40801,13 +40805,13 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
@@ -40906,13 +40910,13 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
@@ -41013,13 +41017,13 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -41120,13 +41124,13 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
@@ -41225,13 +41229,13 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
@@ -41330,13 +41334,13 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" t="s" s="2">
@@ -41433,13 +41437,13 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -41538,13 +41542,13 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -41643,13 +41647,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -41675,10 +41679,10 @@
         <v>406</v>
       </c>
       <c r="M357" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="N357" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="O357" s="2"/>
       <c r="P357" s="2"/>
@@ -41729,7 +41733,7 @@
         <v>73</v>
       </c>
       <c r="AG357" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AH357" t="s" s="2">
         <v>74</v>
@@ -41746,13 +41750,13 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
@@ -41775,16 +41779,16 @@
         <v>73</v>
       </c>
       <c r="L358" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M358" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="N358" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="O358" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="P358" s="2"/>
       <c r="Q358" t="s" s="2">
@@ -41834,7 +41838,7 @@
         <v>73</v>
       </c>
       <c r="AG358" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AH358" t="s" s="2">
         <v>74</v>
@@ -41851,13 +41855,13 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -41883,13 +41887,13 @@
         <v>632</v>
       </c>
       <c r="M359" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="N359" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="O359" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="P359" s="2"/>
       <c r="Q359" t="s" s="2">
@@ -41939,7 +41943,7 @@
         <v>73</v>
       </c>
       <c r="AG359" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AH359" t="s" s="2">
         <v>74</v>
@@ -41956,13 +41960,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -41988,10 +41992,10 @@
         <v>101</v>
       </c>
       <c r="M360" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="N360" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="O360" s="2"/>
       <c r="P360" s="2"/>
@@ -42021,10 +42025,10 @@
         <v>105</v>
       </c>
       <c r="Z360" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="AA360" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="AB360" t="s" s="2">
         <v>73</v>
@@ -42042,7 +42046,7 @@
         <v>73</v>
       </c>
       <c r="AG360" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AH360" t="s" s="2">
         <v>74</v>
@@ -42059,13 +42063,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -42091,10 +42095,10 @@
         <v>204</v>
       </c>
       <c r="M361" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="N361" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="O361" s="2"/>
       <c r="P361" s="2"/>
@@ -42124,10 +42128,10 @@
         <v>272</v>
       </c>
       <c r="Z361" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="AA361" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="AB361" t="s" s="2">
         <v>73</v>
@@ -42145,7 +42149,7 @@
         <v>73</v>
       </c>
       <c r="AG361" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AH361" t="s" s="2">
         <v>74</v>
@@ -42162,13 +42166,13 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -42194,10 +42198,10 @@
         <v>347</v>
       </c>
       <c r="M362" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="N362" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="O362" s="2"/>
       <c r="P362" s="2"/>
@@ -42248,7 +42252,7 @@
         <v>73</v>
       </c>
       <c r="AG362" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AH362" t="s" s="2">
         <v>74</v>
@@ -42265,13 +42269,13 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
@@ -42368,13 +42372,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
@@ -42473,13 +42477,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
@@ -42580,13 +42584,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
@@ -42612,10 +42616,10 @@
         <v>204</v>
       </c>
       <c r="M366" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="N366" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="O366" s="2"/>
       <c r="P366" s="2"/>
@@ -42645,10 +42649,10 @@
         <v>265</v>
       </c>
       <c r="Z366" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AA366" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AB366" t="s" s="2">
         <v>73</v>
@@ -42666,7 +42670,7 @@
         <v>73</v>
       </c>
       <c r="AG366" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AH366" t="s" s="2">
         <v>81</v>
@@ -42683,13 +42687,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -42715,10 +42719,10 @@
         <v>173</v>
       </c>
       <c r="M367" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="N367" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="O367" s="2"/>
       <c r="P367" s="2"/>
@@ -42769,7 +42773,7 @@
         <v>73</v>
       </c>
       <c r="AG367" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="AH367" t="s" s="2">
         <v>81</v>
@@ -42786,13 +42790,13 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
@@ -42818,10 +42822,10 @@
         <v>347</v>
       </c>
       <c r="M368" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="N368" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="O368" s="2"/>
       <c r="P368" s="2"/>
@@ -42872,7 +42876,7 @@
         <v>73</v>
       </c>
       <c r="AG368" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AH368" t="s" s="2">
         <v>74</v>
@@ -42889,13 +42893,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
@@ -42992,13 +42996,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
@@ -43097,13 +43101,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -43204,13 +43208,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -43233,13 +43237,13 @@
         <v>82</v>
       </c>
       <c r="L372" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="M372" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="N372" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="O372" s="2"/>
       <c r="P372" s="2"/>
@@ -43290,7 +43294,7 @@
         <v>73</v>
       </c>
       <c r="AG372" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="AH372" t="s" s="2">
         <v>74</v>
@@ -43307,13 +43311,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D373" s="2"/>
       <c r="E373" t="s" s="2">
@@ -43339,10 +43343,10 @@
         <v>406</v>
       </c>
       <c r="M373" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="N373" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="O373" s="2"/>
       <c r="P373" s="2"/>
@@ -43393,7 +43397,7 @@
         <v>73</v>
       </c>
       <c r="AG373" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="AH373" t="s" s="2">
         <v>74</v>
@@ -43410,13 +43414,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
@@ -43442,10 +43446,10 @@
         <v>521</v>
       </c>
       <c r="M374" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="N374" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="O374" s="2"/>
       <c r="P374" s="2"/>
@@ -43496,7 +43500,7 @@
         <v>73</v>
       </c>
       <c r="AG374" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AH374" t="s" s="2">
         <v>74</v>
@@ -43513,13 +43517,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -43542,13 +43546,13 @@
         <v>73</v>
       </c>
       <c r="L375" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M375" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="N375" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="O375" s="2"/>
       <c r="P375" s="2"/>
@@ -43599,7 +43603,7 @@
         <v>73</v>
       </c>
       <c r="AG375" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="AH375" t="s" s="2">
         <v>74</v>
@@ -43616,13 +43620,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -43648,10 +43652,10 @@
         <v>204</v>
       </c>
       <c r="M376" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="N376" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="O376" s="2"/>
       <c r="P376" s="2"/>
@@ -43681,10 +43685,10 @@
         <v>265</v>
       </c>
       <c r="Z376" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="AA376" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="AB376" t="s" s="2">
         <v>73</v>
@@ -43702,7 +43706,7 @@
         <v>73</v>
       </c>
       <c r="AG376" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="AH376" t="s" s="2">
         <v>74</v>
@@ -43719,13 +43723,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -43751,10 +43755,10 @@
         <v>544</v>
       </c>
       <c r="M377" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="N377" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="O377" s="2"/>
       <c r="P377" s="2"/>
@@ -43784,7 +43788,7 @@
         <v>265</v>
       </c>
       <c r="Z377" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AA377" t="s" s="2">
         <v>73</v>
@@ -43805,7 +43809,7 @@
         <v>73</v>
       </c>
       <c r="AG377" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AH377" t="s" s="2">
         <v>74</v>
@@ -43822,13 +43826,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -43851,13 +43855,13 @@
         <v>73</v>
       </c>
       <c r="L378" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="M378" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="N378" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="O378" s="2"/>
       <c r="P378" s="2"/>
@@ -43908,7 +43912,7 @@
         <v>73</v>
       </c>
       <c r="AG378" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AH378" t="s" s="2">
         <v>74</v>
@@ -43925,13 +43929,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -43954,16 +43958,16 @@
         <v>73</v>
       </c>
       <c r="L379" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M379" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="N379" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="O379" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="P379" s="2"/>
       <c r="Q379" t="s" s="2">
@@ -43992,10 +43996,10 @@
         <v>265</v>
       </c>
       <c r="Z379" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AA379" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AB379" t="s" s="2">
         <v>73</v>
@@ -44013,7 +44017,7 @@
         <v>73</v>
       </c>
       <c r="AG379" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AH379" t="s" s="2">
         <v>74</v>
@@ -44030,13 +44034,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -44059,19 +44063,19 @@
         <v>82</v>
       </c>
       <c r="L380" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="M380" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="N380" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="O380" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="P380" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="Q380" t="s" s="2">
         <v>73</v>
@@ -44099,10 +44103,10 @@
         <v>183</v>
       </c>
       <c r="Z380" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AA380" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AB380" t="s" s="2">
         <v>73</v>
@@ -44120,7 +44124,7 @@
         <v>73</v>
       </c>
       <c r="AG380" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="AH380" t="s" s="2">
         <v>74</v>
@@ -44137,13 +44141,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -44169,10 +44173,10 @@
         <v>347</v>
       </c>
       <c r="M381" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="N381" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="O381" s="2"/>
       <c r="P381" s="2"/>
@@ -44223,7 +44227,7 @@
         <v>73</v>
       </c>
       <c r="AG381" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AH381" t="s" s="2">
         <v>74</v>
@@ -44240,13 +44244,13 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" t="s" s="2">
@@ -44343,13 +44347,13 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -44448,13 +44452,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -44555,13 +44559,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -44587,10 +44591,10 @@
         <v>173</v>
       </c>
       <c r="M385" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="N385" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="O385" s="2"/>
       <c r="P385" s="2"/>
@@ -44641,7 +44645,7 @@
         <v>73</v>
       </c>
       <c r="AG385" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="AH385" t="s" s="2">
         <v>74</v>
@@ -44658,13 +44662,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" t="s" s="2">
@@ -44690,10 +44694,10 @@
         <v>204</v>
       </c>
       <c r="M386" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="N386" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="O386" s="2"/>
       <c r="P386" s="2"/>
@@ -44723,10 +44727,10 @@
         <v>265</v>
       </c>
       <c r="Z386" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AA386" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="AB386" t="s" s="2">
         <v>73</v>
@@ -44744,7 +44748,7 @@
         <v>73</v>
       </c>
       <c r="AG386" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="AH386" t="s" s="2">
         <v>74</v>
@@ -44761,13 +44765,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -44790,13 +44794,13 @@
         <v>73</v>
       </c>
       <c r="L387" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="M387" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="N387" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="O387" s="2"/>
       <c r="P387" s="2"/>
@@ -44847,7 +44851,7 @@
         <v>73</v>
       </c>
       <c r="AG387" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="AH387" t="s" s="2">
         <v>74</v>
@@ -44864,13 +44868,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
@@ -44893,13 +44897,13 @@
         <v>73</v>
       </c>
       <c r="L388" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M388" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="N388" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="O388" s="2"/>
       <c r="P388" s="2"/>
@@ -44950,7 +44954,7 @@
         <v>73</v>
       </c>
       <c r="AG388" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="AH388" t="s" s="2">
         <v>74</v>
@@ -44967,13 +44971,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -44999,10 +45003,10 @@
         <v>347</v>
       </c>
       <c r="M389" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="N389" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="O389" s="2"/>
       <c r="P389" s="2"/>
@@ -45053,7 +45057,7 @@
         <v>73</v>
       </c>
       <c r="AG389" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="AH389" t="s" s="2">
         <v>74</v>
@@ -45070,13 +45074,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
@@ -45173,13 +45177,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
@@ -45278,13 +45282,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" t="s" s="2">
@@ -45385,13 +45389,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" t="s" s="2">
@@ -45417,10 +45421,10 @@
         <v>557</v>
       </c>
       <c r="M393" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="N393" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="O393" s="2"/>
       <c r="P393" s="2"/>
@@ -45471,7 +45475,7 @@
         <v>73</v>
       </c>
       <c r="AG393" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="AH393" t="s" s="2">
         <v>81</v>
@@ -45488,13 +45492,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" t="s" s="2">
@@ -45520,10 +45524,10 @@
         <v>276</v>
       </c>
       <c r="M394" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="N394" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="O394" s="2"/>
       <c r="P394" s="2"/>
@@ -45574,7 +45578,7 @@
         <v>73</v>
       </c>
       <c r="AG394" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="AH394" t="s" s="2">
         <v>74</v>
@@ -45591,13 +45595,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
@@ -45620,13 +45624,13 @@
         <v>73</v>
       </c>
       <c r="L395" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M395" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="N395" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="O395" s="2"/>
       <c r="P395" s="2"/>
@@ -45677,7 +45681,7 @@
         <v>73</v>
       </c>
       <c r="AG395" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="AH395" t="s" s="2">
         <v>74</v>
@@ -45694,13 +45698,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
@@ -45726,16 +45730,16 @@
         <v>204</v>
       </c>
       <c r="M396" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="N396" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="O396" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="P396" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="Q396" t="s" s="2">
         <v>73</v>
@@ -45763,10 +45767,10 @@
         <v>183</v>
       </c>
       <c r="Z396" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="AA396" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="AB396" t="s" s="2">
         <v>73</v>
@@ -45784,7 +45788,7 @@
         <v>73</v>
       </c>
       <c r="AG396" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AH396" t="s" s="2">
         <v>74</v>
@@ -45801,13 +45805,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" t="s" s="2">
@@ -45836,7 +45840,7 @@
         <v>50</v>
       </c>
       <c r="N397" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="O397" s="2"/>
       <c r="P397" s="2"/>
@@ -45887,7 +45891,7 @@
         <v>73</v>
       </c>
       <c r="AG397" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="AH397" t="s" s="2">
         <v>74</v>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13291" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13423" uniqueCount="1042">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.6</t>
+    <t>0.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:03:39+00:00</t>
+    <t>2026-04-16T08:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2377,6 +2377,49 @@
   </si>
   <si>
     <t>The date/time at which the requested service should occur.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x].id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x].extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x].start</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x].end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The end value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
   </si>
   <si>
     <t>ServiceRequest.asNeeded[x]</t>
@@ -4171,7 +4214,7 @@
         <v>2</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
     </row>
     <row r="108">
@@ -4179,7 +4222,7 @@
         <v>4</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>844</v>
+        <v>858</v>
       </c>
     </row>
     <row r="109">
@@ -4195,7 +4238,7 @@
         <v>8</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>845</v>
+        <v>859</v>
       </c>
     </row>
     <row r="111">
@@ -4255,7 +4298,7 @@
         <v>22</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>846</v>
+        <v>860</v>
       </c>
     </row>
     <row r="119">
@@ -4291,7 +4334,7 @@
         <v>29</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>847</v>
+        <v>861</v>
       </c>
     </row>
     <row r="124">
@@ -4299,7 +4342,7 @@
         <v>31</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>848</v>
+        <v>862</v>
       </c>
     </row>
     <row r="125">
@@ -4325,7 +4368,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK397"/>
+  <dimension ref="A1:AK401"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.671875" customWidth="true" bestFit="true"/>
@@ -35918,16 +35961,16 @@
         <v>73</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L302" t="s" s="2">
-        <v>758</v>
+        <v>83</v>
       </c>
       <c r="M302" t="s" s="2">
-        <v>759</v>
+        <v>162</v>
       </c>
       <c r="N302" t="s" s="2">
-        <v>760</v>
+        <v>163</v>
       </c>
       <c r="O302" s="2"/>
       <c r="P302" s="2"/>
@@ -35954,13 +35997,13 @@
         <v>73</v>
       </c>
       <c r="Y302" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z302" t="s" s="2">
-        <v>761</v>
+        <v>73</v>
       </c>
       <c r="AA302" t="s" s="2">
-        <v>762</v>
+        <v>73</v>
       </c>
       <c r="AB302" t="s" s="2">
         <v>73</v>
@@ -35978,7 +36021,7 @@
         <v>73</v>
       </c>
       <c r="AG302" t="s" s="2">
-        <v>757</v>
+        <v>164</v>
       </c>
       <c r="AH302" t="s" s="2">
         <v>74</v>
@@ -35987,10 +36030,10 @@
         <v>81</v>
       </c>
       <c r="AJ302" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK302" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="303">
@@ -35998,21 +36041,21 @@
         <v>569</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" t="s" s="2">
-        <v>764</v>
+        <v>126</v>
       </c>
       <c r="F303" s="2"/>
       <c r="G303" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H303" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I303" t="s" s="2">
         <v>73</v>
@@ -36021,18 +36064,20 @@
         <v>73</v>
       </c>
       <c r="K303" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L303" t="s" s="2">
-        <v>406</v>
+        <v>127</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>765</v>
+        <v>128</v>
       </c>
       <c r="N303" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="O303" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O303" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P303" s="2"/>
       <c r="Q303" t="s" s="2">
         <v>73</v>
@@ -36069,31 +36114,31 @@
         <v>73</v>
       </c>
       <c r="AC303" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD303" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE303" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF303" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG303" t="s" s="2">
-        <v>763</v>
+        <v>171</v>
       </c>
       <c r="AH303" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI303" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ303" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK303" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="304">
@@ -36101,18 +36146,18 @@
         <v>569</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" t="s" s="2">
-        <v>768</v>
+        <v>73</v>
       </c>
       <c r="F304" s="2"/>
       <c r="G304" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H304" t="s" s="2">
         <v>81</v>
@@ -36127,16 +36172,16 @@
         <v>82</v>
       </c>
       <c r="L304" t="s" s="2">
-        <v>769</v>
+        <v>406</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="N304" t="s" s="2">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="O304" t="s" s="2">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="P304" s="2"/>
       <c r="Q304" t="s" s="2">
@@ -36186,7 +36231,7 @@
         <v>73</v>
       </c>
       <c r="AG304" t="s" s="2">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="AH304" t="s" s="2">
         <v>74</v>
@@ -36195,10 +36240,10 @@
         <v>81</v>
       </c>
       <c r="AJ304" t="s" s="2">
-        <v>73</v>
+        <v>764</v>
       </c>
       <c r="AK304" t="s" s="2">
-        <v>773</v>
+        <v>93</v>
       </c>
     </row>
     <row r="305">
@@ -36206,18 +36251,18 @@
         <v>569</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" t="s" s="2">
-        <v>775</v>
+        <v>73</v>
       </c>
       <c r="F305" s="2"/>
       <c r="G305" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H305" t="s" s="2">
         <v>81</v>
@@ -36232,22 +36277,24 @@
         <v>82</v>
       </c>
       <c r="L305" t="s" s="2">
-        <v>204</v>
+        <v>406</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="N305" t="s" s="2">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="O305" t="s" s="2">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="P305" s="2"/>
       <c r="Q305" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="R305" s="2"/>
+      <c r="R305" t="s" s="2">
+        <v>769</v>
+      </c>
       <c r="S305" t="s" s="2">
         <v>73</v>
       </c>
@@ -36267,13 +36314,13 @@
         <v>73</v>
       </c>
       <c r="Y305" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z305" t="s" s="2">
-        <v>779</v>
+        <v>73</v>
       </c>
       <c r="AA305" t="s" s="2">
-        <v>780</v>
+        <v>73</v>
       </c>
       <c r="AB305" t="s" s="2">
         <v>73</v>
@@ -36291,7 +36338,7 @@
         <v>73</v>
       </c>
       <c r="AG305" t="s" s="2">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="AH305" t="s" s="2">
         <v>74</v>
@@ -36300,7 +36347,7 @@
         <v>81</v>
       </c>
       <c r="AJ305" t="s" s="2">
-        <v>73</v>
+        <v>764</v>
       </c>
       <c r="AK305" t="s" s="2">
         <v>93</v>
@@ -36311,21 +36358,21 @@
         <v>569</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
-        <v>782</v>
+        <v>73</v>
       </c>
       <c r="F306" s="2"/>
       <c r="G306" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H306" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I306" t="s" s="2">
         <v>73</v>
@@ -36337,17 +36384,15 @@
         <v>82</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="N306" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="O306" t="s" s="2">
-        <v>786</v>
-      </c>
+        <v>774</v>
+      </c>
+      <c r="O306" s="2"/>
       <c r="P306" s="2"/>
       <c r="Q306" t="s" s="2">
         <v>73</v>
@@ -36372,13 +36417,13 @@
         <v>73</v>
       </c>
       <c r="Y306" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z306" t="s" s="2">
-        <v>73</v>
+        <v>775</v>
       </c>
       <c r="AA306" t="s" s="2">
-        <v>73</v>
+        <v>776</v>
       </c>
       <c r="AB306" t="s" s="2">
         <v>73</v>
@@ -36396,13 +36441,13 @@
         <v>73</v>
       </c>
       <c r="AG306" t="s" s="2">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="AH306" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI306" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ306" t="s" s="2">
         <v>73</v>
@@ -36416,21 +36461,21 @@
         <v>569</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
-        <v>73</v>
+        <v>778</v>
       </c>
       <c r="F307" s="2"/>
       <c r="G307" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H307" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I307" t="s" s="2">
         <v>73</v>
@@ -36442,13 +36487,13 @@
         <v>82</v>
       </c>
       <c r="L307" t="s" s="2">
-        <v>788</v>
+        <v>406</v>
       </c>
       <c r="M307" t="s" s="2">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="N307" t="s" s="2">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="O307" s="2"/>
       <c r="P307" s="2"/>
@@ -36475,13 +36520,13 @@
         <v>73</v>
       </c>
       <c r="Y307" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z307" t="s" s="2">
-        <v>791</v>
+        <v>73</v>
       </c>
       <c r="AA307" t="s" s="2">
-        <v>792</v>
+        <v>73</v>
       </c>
       <c r="AB307" t="s" s="2">
         <v>73</v>
@@ -36499,13 +36544,13 @@
         <v>73</v>
       </c>
       <c r="AG307" t="s" s="2">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="AH307" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI307" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ307" t="s" s="2">
         <v>73</v>
@@ -36519,21 +36564,21 @@
         <v>569</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" t="s" s="2">
-        <v>73</v>
+        <v>782</v>
       </c>
       <c r="F308" s="2"/>
       <c r="G308" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H308" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I308" t="s" s="2">
         <v>73</v>
@@ -36545,16 +36590,16 @@
         <v>82</v>
       </c>
       <c r="L308" t="s" s="2">
-        <v>794</v>
+        <v>783</v>
       </c>
       <c r="M308" t="s" s="2">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="N308" t="s" s="2">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="O308" t="s" s="2">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="P308" s="2"/>
       <c r="Q308" t="s" s="2">
@@ -36580,13 +36625,13 @@
         <v>73</v>
       </c>
       <c r="Y308" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z308" t="s" s="2">
-        <v>798</v>
+        <v>73</v>
       </c>
       <c r="AA308" t="s" s="2">
-        <v>799</v>
+        <v>73</v>
       </c>
       <c r="AB308" t="s" s="2">
         <v>73</v>
@@ -36604,19 +36649,19 @@
         <v>73</v>
       </c>
       <c r="AG308" t="s" s="2">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="AH308" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI308" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ308" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK308" t="s" s="2">
-        <v>93</v>
+        <v>787</v>
       </c>
     </row>
     <row r="309">
@@ -36624,21 +36669,21 @@
         <v>569</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
-        <v>73</v>
+        <v>789</v>
       </c>
       <c r="F309" s="2"/>
       <c r="G309" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H309" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I309" t="s" s="2">
         <v>73</v>
@@ -36647,18 +36692,20 @@
         <v>73</v>
       </c>
       <c r="K309" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>801</v>
+        <v>204</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="N309" t="s" s="2">
-        <v>803</v>
-      </c>
-      <c r="O309" s="2"/>
+        <v>791</v>
+      </c>
+      <c r="O309" t="s" s="2">
+        <v>792</v>
+      </c>
       <c r="P309" s="2"/>
       <c r="Q309" t="s" s="2">
         <v>73</v>
@@ -36683,13 +36730,13 @@
         <v>73</v>
       </c>
       <c r="Y309" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z309" t="s" s="2">
-        <v>73</v>
+        <v>793</v>
       </c>
       <c r="AA309" t="s" s="2">
-        <v>73</v>
+        <v>794</v>
       </c>
       <c r="AB309" t="s" s="2">
         <v>73</v>
@@ -36707,13 +36754,13 @@
         <v>73</v>
       </c>
       <c r="AG309" t="s" s="2">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="AH309" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI309" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ309" t="s" s="2">
         <v>73</v>
@@ -36727,14 +36774,14 @@
         <v>569</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="F310" s="2"/>
       <c r="G310" t="s" s="2">
@@ -36750,19 +36797,19 @@
         <v>73</v>
       </c>
       <c r="K310" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="N310" t="s" s="2">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="O310" t="s" s="2">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="P310" s="2"/>
       <c r="Q310" t="s" s="2">
@@ -36812,7 +36859,7 @@
         <v>73</v>
       </c>
       <c r="AG310" t="s" s="2">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="AH310" t="s" s="2">
         <v>74</v>
@@ -36832,10 +36879,10 @@
         <v>569</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -36858,17 +36905,15 @@
         <v>82</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="N311" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="O311" t="s" s="2">
-        <v>814</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="O311" s="2"/>
       <c r="P311" s="2"/>
       <c r="Q311" t="s" s="2">
         <v>73</v>
@@ -36893,13 +36938,13 @@
         <v>73</v>
       </c>
       <c r="Y311" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z311" t="s" s="2">
-        <v>73</v>
+        <v>805</v>
       </c>
       <c r="AA311" t="s" s="2">
-        <v>73</v>
+        <v>806</v>
       </c>
       <c r="AB311" t="s" s="2">
         <v>73</v>
@@ -36917,7 +36962,7 @@
         <v>73</v>
       </c>
       <c r="AG311" t="s" s="2">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="AH311" t="s" s="2">
         <v>74</v>
@@ -36937,14 +36982,14 @@
         <v>569</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
-        <v>816</v>
+        <v>73</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" t="s" s="2">
@@ -36963,20 +37008,18 @@
         <v>82</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>204</v>
+        <v>808</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="O312" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="P312" t="s" s="2">
-        <v>820</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="P312" s="2"/>
       <c r="Q312" t="s" s="2">
         <v>73</v>
       </c>
@@ -37003,10 +37046,10 @@
         <v>265</v>
       </c>
       <c r="Z312" t="s" s="2">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="AA312" t="s" s="2">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="AB312" t="s" s="2">
         <v>73</v>
@@ -37024,7 +37067,7 @@
         <v>73</v>
       </c>
       <c r="AG312" t="s" s="2">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="AH312" t="s" s="2">
         <v>74</v>
@@ -37033,7 +37076,7 @@
         <v>75</v>
       </c>
       <c r="AJ312" t="s" s="2">
-        <v>823</v>
+        <v>73</v>
       </c>
       <c r="AK312" t="s" s="2">
         <v>93</v>
@@ -37044,21 +37087,21 @@
         <v>569</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
-        <v>825</v>
+        <v>73</v>
       </c>
       <c r="F313" s="2"/>
       <c r="G313" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H313" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I313" t="s" s="2">
         <v>73</v>
@@ -37067,21 +37110,19 @@
         <v>73</v>
       </c>
       <c r="K313" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>826</v>
+        <v>815</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>827</v>
+        <v>816</v>
       </c>
       <c r="N313" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="O313" s="2"/>
-      <c r="P313" t="s" s="2">
-        <v>820</v>
-      </c>
+      <c r="P313" s="2"/>
       <c r="Q313" t="s" s="2">
         <v>73</v>
       </c>
@@ -37129,16 +37170,16 @@
         <v>73</v>
       </c>
       <c r="AG313" t="s" s="2">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="AH313" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI313" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ313" t="s" s="2">
-        <v>823</v>
+        <v>73</v>
       </c>
       <c r="AK313" t="s" s="2">
         <v>93</v>
@@ -37149,14 +37190,14 @@
         <v>569</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
-        <v>73</v>
+        <v>819</v>
       </c>
       <c r="F314" s="2"/>
       <c r="G314" t="s" s="2">
@@ -37166,7 +37207,7 @@
         <v>75</v>
       </c>
       <c r="I314" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J314" t="s" s="2">
         <v>73</v>
@@ -37175,15 +37216,17 @@
         <v>73</v>
       </c>
       <c r="L314" t="s" s="2">
-        <v>549</v>
+        <v>820</v>
       </c>
       <c r="M314" t="s" s="2">
-        <v>50</v>
+        <v>821</v>
       </c>
       <c r="N314" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="O314" s="2"/>
+        <v>822</v>
+      </c>
+      <c r="O314" t="s" s="2">
+        <v>823</v>
+      </c>
       <c r="P314" s="2"/>
       <c r="Q314" t="s" s="2">
         <v>73</v>
@@ -37232,7 +37275,7 @@
         <v>73</v>
       </c>
       <c r="AG314" t="s" s="2">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="AH314" t="s" s="2">
         <v>74</v>
@@ -37252,10 +37295,10 @@
         <v>569</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -37275,18 +37318,20 @@
         <v>73</v>
       </c>
       <c r="K315" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L315" t="s" s="2">
-        <v>347</v>
+        <v>825</v>
       </c>
       <c r="M315" t="s" s="2">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="N315" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="O315" s="2"/>
+        <v>827</v>
+      </c>
+      <c r="O315" t="s" s="2">
+        <v>828</v>
+      </c>
       <c r="P315" s="2"/>
       <c r="Q315" t="s" s="2">
         <v>73</v>
@@ -37335,7 +37380,7 @@
         <v>73</v>
       </c>
       <c r="AG315" t="s" s="2">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="AH315" t="s" s="2">
         <v>74</v>
@@ -37355,21 +37400,21 @@
         <v>569</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
-        <v>73</v>
+        <v>830</v>
       </c>
       <c r="F316" s="2"/>
       <c r="G316" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H316" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I316" t="s" s="2">
         <v>73</v>
@@ -37378,19 +37423,23 @@
         <v>73</v>
       </c>
       <c r="K316" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L316" t="s" s="2">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="M316" t="s" s="2">
-        <v>162</v>
+        <v>831</v>
       </c>
       <c r="N316" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O316" s="2"/>
-      <c r="P316" s="2"/>
+        <v>832</v>
+      </c>
+      <c r="O316" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="P316" t="s" s="2">
+        <v>834</v>
+      </c>
       <c r="Q316" t="s" s="2">
         <v>73</v>
       </c>
@@ -37414,13 +37463,13 @@
         <v>73</v>
       </c>
       <c r="Y316" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z316" t="s" s="2">
-        <v>73</v>
+        <v>835</v>
       </c>
       <c r="AA316" t="s" s="2">
-        <v>73</v>
+        <v>836</v>
       </c>
       <c r="AB316" t="s" s="2">
         <v>73</v>
@@ -37438,19 +37487,19 @@
         <v>73</v>
       </c>
       <c r="AG316" t="s" s="2">
-        <v>164</v>
+        <v>829</v>
       </c>
       <c r="AH316" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI316" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ316" t="s" s="2">
-        <v>165</v>
+        <v>837</v>
       </c>
       <c r="AK316" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="317">
@@ -37458,21 +37507,21 @@
         <v>569</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
-        <v>126</v>
+        <v>839</v>
       </c>
       <c r="F317" s="2"/>
       <c r="G317" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H317" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I317" t="s" s="2">
         <v>73</v>
@@ -37481,21 +37530,21 @@
         <v>73</v>
       </c>
       <c r="K317" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L317" t="s" s="2">
-        <v>127</v>
+        <v>840</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>128</v>
+        <v>841</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O317" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P317" s="2"/>
+        <v>832</v>
+      </c>
+      <c r="O317" s="2"/>
+      <c r="P317" t="s" s="2">
+        <v>834</v>
+      </c>
       <c r="Q317" t="s" s="2">
         <v>73</v>
       </c>
@@ -37543,19 +37592,19 @@
         <v>73</v>
       </c>
       <c r="AG317" t="s" s="2">
-        <v>171</v>
+        <v>838</v>
       </c>
       <c r="AH317" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI317" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ317" t="s" s="2">
-        <v>73</v>
+        <v>837</v>
       </c>
       <c r="AK317" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="318">
@@ -37563,14 +37612,14 @@
         <v>569</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F318" s="2"/>
       <c r="G318" t="s" s="2">
@@ -37580,29 +37629,25 @@
         <v>75</v>
       </c>
       <c r="I318" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J318" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K318" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L318" t="s" s="2">
-        <v>127</v>
+        <v>549</v>
       </c>
       <c r="M318" t="s" s="2">
-        <v>355</v>
+        <v>50</v>
       </c>
       <c r="N318" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O318" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P318" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>843</v>
+      </c>
+      <c r="O318" s="2"/>
+      <c r="P318" s="2"/>
       <c r="Q318" t="s" s="2">
         <v>73</v>
       </c>
@@ -37650,7 +37695,7 @@
         <v>73</v>
       </c>
       <c r="AG318" t="s" s="2">
-        <v>357</v>
+        <v>842</v>
       </c>
       <c r="AH318" t="s" s="2">
         <v>74</v>
@@ -37662,7 +37707,7 @@
         <v>73</v>
       </c>
       <c r="AK318" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="319">
@@ -37670,10 +37715,10 @@
         <v>569</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -37684,7 +37729,7 @@
         <v>74</v>
       </c>
       <c r="H319" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I319" t="s" s="2">
         <v>73</v>
@@ -37693,16 +37738,16 @@
         <v>73</v>
       </c>
       <c r="K319" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L319" t="s" s="2">
-        <v>837</v>
+        <v>347</v>
       </c>
       <c r="M319" t="s" s="2">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="N319" t="s" s="2">
-        <v>832</v>
+        <v>846</v>
       </c>
       <c r="O319" s="2"/>
       <c r="P319" s="2"/>
@@ -37753,13 +37798,13 @@
         <v>73</v>
       </c>
       <c r="AG319" t="s" s="2">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="AH319" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI319" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ319" t="s" s="2">
         <v>73</v>
@@ -37773,10 +37818,10 @@
         <v>569</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
@@ -37787,7 +37832,7 @@
         <v>74</v>
       </c>
       <c r="H320" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I320" t="s" s="2">
         <v>73</v>
@@ -37799,17 +37844,15 @@
         <v>73</v>
       </c>
       <c r="L320" t="s" s="2">
-        <v>839</v>
+        <v>173</v>
       </c>
       <c r="M320" t="s" s="2">
-        <v>840</v>
+        <v>162</v>
       </c>
       <c r="N320" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="O320" t="s" s="2">
-        <v>842</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O320" s="2"/>
       <c r="P320" s="2"/>
       <c r="Q320" t="s" s="2">
         <v>73</v>
@@ -37858,34 +37901,34 @@
         <v>73</v>
       </c>
       <c r="AG320" t="s" s="2">
-        <v>838</v>
+        <v>164</v>
       </c>
       <c r="AH320" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI320" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ320" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK320" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>843</v>
+        <v>569</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F321" s="2"/>
       <c r="G321" t="s" s="2">
@@ -37904,15 +37947,17 @@
         <v>73</v>
       </c>
       <c r="L321" t="s" s="2">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="M321" t="s" s="2">
-        <v>849</v>
+        <v>128</v>
       </c>
       <c r="N321" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="O321" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O321" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P321" s="2"/>
       <c r="Q321" t="s" s="2">
         <v>73</v>
@@ -37961,7 +38006,7 @@
         <v>73</v>
       </c>
       <c r="AG321" t="s" s="2">
-        <v>847</v>
+        <v>171</v>
       </c>
       <c r="AH321" t="s" s="2">
         <v>74</v>
@@ -37973,52 +38018,54 @@
         <v>73</v>
       </c>
       <c r="AK321" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>843</v>
+        <v>569</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H322" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I322" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J322" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K322" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L322" t="s" s="2">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="M322" t="s" s="2">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="N322" t="s" s="2">
-        <v>85</v>
+        <v>356</v>
       </c>
       <c r="O322" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="P322" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="P322" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q322" t="s" s="2">
         <v>73</v>
       </c>
@@ -38066,30 +38113,30 @@
         <v>73</v>
       </c>
       <c r="AG322" t="s" s="2">
-        <v>87</v>
+        <v>357</v>
       </c>
       <c r="AH322" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI322" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ322" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK322" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>843</v>
+        <v>569</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
@@ -38112,13 +38159,13 @@
         <v>82</v>
       </c>
       <c r="L323" t="s" s="2">
-        <v>89</v>
+        <v>851</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>90</v>
+        <v>845</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>91</v>
+        <v>846</v>
       </c>
       <c r="O323" s="2"/>
       <c r="P323" s="2"/>
@@ -38169,7 +38216,7 @@
         <v>73</v>
       </c>
       <c r="AG323" t="s" s="2">
-        <v>92</v>
+        <v>850</v>
       </c>
       <c r="AH323" t="s" s="2">
         <v>74</v>
@@ -38186,13 +38233,13 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>843</v>
+        <v>569</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
@@ -38203,28 +38250,28 @@
         <v>74</v>
       </c>
       <c r="H324" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I324" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J324" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K324" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>95</v>
+        <v>853</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>96</v>
+        <v>854</v>
       </c>
       <c r="N324" t="s" s="2">
-        <v>97</v>
+        <v>855</v>
       </c>
       <c r="O324" t="s" s="2">
-        <v>98</v>
+        <v>856</v>
       </c>
       <c r="P324" s="2"/>
       <c r="Q324" t="s" s="2">
@@ -38274,13 +38321,13 @@
         <v>73</v>
       </c>
       <c r="AG324" t="s" s="2">
-        <v>99</v>
+        <v>852</v>
       </c>
       <c r="AH324" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI324" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ324" t="s" s="2">
         <v>73</v>
@@ -38291,13 +38338,13 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -38308,7 +38355,7 @@
         <v>74</v>
       </c>
       <c r="H325" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I325" t="s" s="2">
         <v>73</v>
@@ -38320,17 +38367,15 @@
         <v>73</v>
       </c>
       <c r="L325" t="s" s="2">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="M325" t="s" s="2">
-        <v>102</v>
+        <v>863</v>
       </c>
       <c r="N325" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="O325" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>864</v>
+      </c>
+      <c r="O325" s="2"/>
       <c r="P325" s="2"/>
       <c r="Q325" t="s" s="2">
         <v>73</v>
@@ -38355,13 +38400,13 @@
         <v>73</v>
       </c>
       <c r="Y325" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="Z325" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AA325" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AB325" t="s" s="2">
         <v>73</v>
@@ -38379,34 +38424,34 @@
         <v>73</v>
       </c>
       <c r="AG325" t="s" s="2">
-        <v>108</v>
+        <v>861</v>
       </c>
       <c r="AH325" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI325" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ325" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK325" t="s" s="2">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="F326" s="2"/>
       <c r="G326" t="s" s="2">
@@ -38422,19 +38467,19 @@
         <v>73</v>
       </c>
       <c r="K326" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L326" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="M326" t="s" s="2">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="N326" t="s" s="2">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="O326" t="s" s="2">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="P326" s="2"/>
       <c r="Q326" t="s" s="2">
@@ -38484,7 +38529,7 @@
         <v>73</v>
       </c>
       <c r="AG326" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="AH326" t="s" s="2">
         <v>74</v>
@@ -38493,21 +38538,21 @@
         <v>81</v>
       </c>
       <c r="AJ326" t="s" s="2">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="AK326" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -38515,10 +38560,10 @@
       </c>
       <c r="F327" s="2"/>
       <c r="G327" t="s" s="2">
-        <v>857</v>
+        <v>74</v>
       </c>
       <c r="H327" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I327" t="s" s="2">
         <v>73</v>
@@ -38527,20 +38572,18 @@
         <v>73</v>
       </c>
       <c r="K327" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L327" t="s" s="2">
-        <v>858</v>
+        <v>89</v>
       </c>
       <c r="M327" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="N327" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="O327" t="s" s="2">
-        <v>122</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="O327" s="2"/>
       <c r="P327" s="2"/>
       <c r="Q327" t="s" s="2">
         <v>73</v>
@@ -38589,62 +38632,62 @@
         <v>73</v>
       </c>
       <c r="AG327" t="s" s="2">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="AH327" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI327" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ327" t="s" s="2">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="AK327" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F328" s="2"/>
       <c r="G328" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H328" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I328" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J328" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K328" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L328" t="s" s="2">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="M328" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="N328" t="s" s="2">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="O328" t="s" s="2">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="P328" s="2"/>
       <c r="Q328" t="s" s="2">
@@ -38694,66 +38737,64 @@
         <v>73</v>
       </c>
       <c r="AG328" t="s" s="2">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="AH328" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI328" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ328" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK328" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F329" s="2"/>
       <c r="G329" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H329" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I329" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J329" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K329" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L329" t="s" s="2">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="N329" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="O329" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P329" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="P329" s="2"/>
       <c r="Q329" t="s" s="2">
         <v>73</v>
       </c>
@@ -38777,13 +38818,13 @@
         <v>73</v>
       </c>
       <c r="Y329" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z329" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AA329" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AB329" t="s" s="2">
         <v>73</v>
@@ -38801,41 +38842,41 @@
         <v>73</v>
       </c>
       <c r="AG329" t="s" s="2">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="AH329" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI329" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ329" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK329" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="F330" s="2"/>
       <c r="G330" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H330" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I330" t="s" s="2">
         <v>73</v>
@@ -38844,18 +38885,20 @@
         <v>73</v>
       </c>
       <c r="K330" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L330" t="s" s="2">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>862</v>
+        <v>112</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="O330" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O330" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P330" s="2"/>
       <c r="Q330" t="s" s="2">
         <v>73</v>
@@ -38904,16 +38947,16 @@
         <v>73</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>861</v>
+        <v>115</v>
       </c>
       <c r="AH330" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI330" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ330" t="s" s="2">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="AK330" t="s" s="2">
         <v>93</v>
@@ -38921,13 +38964,13 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -38935,10 +38978,10 @@
       </c>
       <c r="F331" s="2"/>
       <c r="G331" t="s" s="2">
-        <v>74</v>
+        <v>871</v>
       </c>
       <c r="H331" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I331" t="s" s="2">
         <v>73</v>
@@ -38950,15 +38993,17 @@
         <v>73</v>
       </c>
       <c r="L331" t="s" s="2">
-        <v>83</v>
+        <v>872</v>
       </c>
       <c r="M331" t="s" s="2">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="N331" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O331" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="O331" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="P331" s="2"/>
       <c r="Q331" t="s" s="2">
         <v>73</v>
@@ -39007,16 +39052,16 @@
         <v>73</v>
       </c>
       <c r="AG331" t="s" s="2">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AH331" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI331" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ331" t="s" s="2">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="AK331" t="s" s="2">
         <v>73</v>
@@ -39024,13 +39069,13 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -39059,7 +39104,7 @@
         <v>128</v>
       </c>
       <c r="N332" t="s" s="2">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="O332" t="s" s="2">
         <v>130</v>
@@ -39100,19 +39145,19 @@
         <v>73</v>
       </c>
       <c r="AC332" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD332" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AE332" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF332" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="AG332" t="s" s="2">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AH332" t="s" s="2">
         <v>74</v>
@@ -39129,24 +39174,24 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F333" s="2"/>
       <c r="G333" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H333" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I333" t="s" s="2">
         <v>73</v>
@@ -39158,19 +39203,19 @@
         <v>82</v>
       </c>
       <c r="L333" t="s" s="2">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="M333" t="s" s="2">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="N333" t="s" s="2">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="O333" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="P333" t="s" s="2">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="Q333" t="s" s="2">
         <v>73</v>
@@ -39195,13 +39240,13 @@
         <v>73</v>
       </c>
       <c r="Y333" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="Z333" t="s" s="2">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="AA333" t="s" s="2">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="AB333" t="s" s="2">
         <v>73</v>
@@ -39219,30 +39264,30 @@
         <v>73</v>
       </c>
       <c r="AG333" t="s" s="2">
-        <v>202</v>
+        <v>137</v>
       </c>
       <c r="AH333" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI333" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ333" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK333" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -39253,7 +39298,7 @@
         <v>74</v>
       </c>
       <c r="H334" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I334" t="s" s="2">
         <v>73</v>
@@ -39265,20 +39310,16 @@
         <v>82</v>
       </c>
       <c r="L334" t="s" s="2">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="M334" t="s" s="2">
-        <v>205</v>
+        <v>876</v>
       </c>
       <c r="N334" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O334" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="P334" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="O334" s="2"/>
+      <c r="P334" s="2"/>
       <c r="Q334" t="s" s="2">
         <v>73</v>
       </c>
@@ -39302,13 +39343,13 @@
         <v>73</v>
       </c>
       <c r="Y334" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z334" t="s" s="2">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="AA334" t="s" s="2">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="AB334" t="s" s="2">
         <v>73</v>
@@ -39326,13 +39367,13 @@
         <v>73</v>
       </c>
       <c r="AG334" t="s" s="2">
-        <v>211</v>
+        <v>875</v>
       </c>
       <c r="AH334" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI334" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ334" t="s" s="2">
         <v>73</v>
@@ -39343,13 +39384,13 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -39357,7 +39398,7 @@
       </c>
       <c r="F335" s="2"/>
       <c r="G335" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H335" t="s" s="2">
         <v>81</v>
@@ -39369,23 +39410,19 @@
         <v>73</v>
       </c>
       <c r="K335" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L335" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M335" t="s" s="2">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="N335" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O335" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P335" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O335" s="2"/>
+      <c r="P335" s="2"/>
       <c r="Q335" t="s" s="2">
         <v>73</v>
       </c>
@@ -39397,7 +39434,7 @@
         <v>73</v>
       </c>
       <c r="U335" t="s" s="2">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="V335" t="s" s="2">
         <v>73</v>
@@ -39433,7 +39470,7 @@
         <v>73</v>
       </c>
       <c r="AG335" t="s" s="2">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="AH335" t="s" s="2">
         <v>74</v>
@@ -39442,32 +39479,32 @@
         <v>81</v>
       </c>
       <c r="AJ335" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK335" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F336" s="2"/>
       <c r="G336" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H336" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I336" t="s" s="2">
         <v>73</v>
@@ -39476,19 +39513,19 @@
         <v>73</v>
       </c>
       <c r="K336" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L336" t="s" s="2">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="M336" t="s" s="2">
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="N336" t="s" s="2">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="O336" t="s" s="2">
-        <v>223</v>
+        <v>130</v>
       </c>
       <c r="P336" s="2"/>
       <c r="Q336" t="s" s="2">
@@ -39502,7 +39539,7 @@
         <v>73</v>
       </c>
       <c r="U336" t="s" s="2">
-        <v>224</v>
+        <v>73</v>
       </c>
       <c r="V336" t="s" s="2">
         <v>73</v>
@@ -39526,42 +39563,42 @@
         <v>73</v>
       </c>
       <c r="AC336" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD336" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE336" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF336" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG336" t="s" s="2">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="AH336" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI336" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ336" t="s" s="2">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="AK336" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -39578,22 +39615,26 @@
         <v>73</v>
       </c>
       <c r="J337" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K337" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L337" t="s" s="2">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="M337" t="s" s="2">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="N337" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O337" s="2"/>
-      <c r="P337" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O337" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="P337" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="Q337" t="s" s="2">
         <v>73</v>
       </c>
@@ -39617,13 +39658,13 @@
         <v>73</v>
       </c>
       <c r="Y337" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z337" t="s" s="2">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="AA337" t="s" s="2">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="AB337" t="s" s="2">
         <v>73</v>
@@ -39641,7 +39682,7 @@
         <v>73</v>
       </c>
       <c r="AG337" t="s" s="2">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="AH337" t="s" s="2">
         <v>74</v>
@@ -39658,13 +39699,13 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
@@ -39687,18 +39728,20 @@
         <v>82</v>
       </c>
       <c r="L338" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="N338" t="s" s="2">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="O338" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="P338" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="P338" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="Q338" t="s" s="2">
         <v>73</v>
       </c>
@@ -39722,13 +39765,13 @@
         <v>73</v>
       </c>
       <c r="Y338" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="Z338" t="s" s="2">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="AA338" t="s" s="2">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="AB338" t="s" s="2">
         <v>73</v>
@@ -39746,7 +39789,7 @@
         <v>73</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>74</v>
@@ -39763,13 +39806,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>872</v>
+        <v>882</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>872</v>
+        <v>882</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -39777,7 +39820,7 @@
       </c>
       <c r="F339" s="2"/>
       <c r="G339" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H339" t="s" s="2">
         <v>81</v>
@@ -39792,16 +39835,20 @@
         <v>82</v>
       </c>
       <c r="L339" t="s" s="2">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>873</v>
+        <v>213</v>
       </c>
       <c r="N339" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="O339" s="2"/>
-      <c r="P339" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="O339" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P339" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="Q339" t="s" s="2">
         <v>73</v>
       </c>
@@ -39813,7 +39860,7 @@
         <v>73</v>
       </c>
       <c r="U339" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="V339" t="s" s="2">
         <v>73</v>
@@ -39849,7 +39896,7 @@
         <v>73</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>872</v>
+        <v>219</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>74</v>
@@ -39866,13 +39913,13 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -39880,7 +39927,7 @@
       </c>
       <c r="F340" s="2"/>
       <c r="G340" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H340" t="s" s="2">
         <v>81</v>
@@ -39889,22 +39936,22 @@
         <v>73</v>
       </c>
       <c r="J340" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K340" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L340" t="s" s="2">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="M340" t="s" s="2">
-        <v>876</v>
+        <v>221</v>
       </c>
       <c r="N340" t="s" s="2">
-        <v>877</v>
+        <v>222</v>
       </c>
       <c r="O340" t="s" s="2">
-        <v>878</v>
+        <v>223</v>
       </c>
       <c r="P340" s="2"/>
       <c r="Q340" t="s" s="2">
@@ -39918,7 +39965,7 @@
         <v>73</v>
       </c>
       <c r="U340" t="s" s="2">
-        <v>73</v>
+        <v>224</v>
       </c>
       <c r="V340" t="s" s="2">
         <v>73</v>
@@ -39930,13 +39977,13 @@
         <v>73</v>
       </c>
       <c r="Y340" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="Z340" t="s" s="2">
-        <v>879</v>
+        <v>73</v>
       </c>
       <c r="AA340" t="s" s="2">
-        <v>880</v>
+        <v>73</v>
       </c>
       <c r="AB340" t="s" s="2">
         <v>73</v>
@@ -39954,7 +40001,7 @@
         <v>73</v>
       </c>
       <c r="AG340" t="s" s="2">
-        <v>875</v>
+        <v>225</v>
       </c>
       <c r="AH340" t="s" s="2">
         <v>74</v>
@@ -39963,7 +40010,7 @@
         <v>81</v>
       </c>
       <c r="AJ340" t="s" s="2">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="AK340" t="s" s="2">
         <v>93</v>
@@ -39971,13 +40018,13 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -39985,7 +40032,7 @@
       </c>
       <c r="F341" s="2"/>
       <c r="G341" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H341" t="s" s="2">
         <v>81</v>
@@ -40000,17 +40047,15 @@
         <v>82</v>
       </c>
       <c r="L341" t="s" s="2">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="M341" t="s" s="2">
-        <v>882</v>
+        <v>228</v>
       </c>
       <c r="N341" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="O341" t="s" s="2">
-        <v>884</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="O341" s="2"/>
       <c r="P341" s="2"/>
       <c r="Q341" t="s" s="2">
         <v>73</v>
@@ -40035,11 +40080,13 @@
         <v>73</v>
       </c>
       <c r="Y341" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="Z341" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z341" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA341" t="s" s="2">
-        <v>885</v>
+        <v>73</v>
       </c>
       <c r="AB341" t="s" s="2">
         <v>73</v>
@@ -40057,7 +40104,7 @@
         <v>73</v>
       </c>
       <c r="AG341" t="s" s="2">
-        <v>881</v>
+        <v>230</v>
       </c>
       <c r="AH341" t="s" s="2">
         <v>74</v>
@@ -40074,13 +40121,13 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" t="s" s="2">
@@ -40088,7 +40135,7 @@
       </c>
       <c r="F342" s="2"/>
       <c r="G342" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H342" t="s" s="2">
         <v>81</v>
@@ -40103,18 +40150,18 @@
         <v>82</v>
       </c>
       <c r="L342" t="s" s="2">
-        <v>726</v>
+        <v>232</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>887</v>
+        <v>233</v>
       </c>
       <c r="N342" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="O342" s="2"/>
-      <c r="P342" t="s" s="2">
-        <v>889</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="O342" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="P342" s="2"/>
       <c r="Q342" t="s" s="2">
         <v>73</v>
       </c>
@@ -40162,7 +40209,7 @@
         <v>73</v>
       </c>
       <c r="AG342" t="s" s="2">
-        <v>886</v>
+        <v>236</v>
       </c>
       <c r="AH342" t="s" s="2">
         <v>74</v>
@@ -40179,13 +40226,13 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
@@ -40205,16 +40252,16 @@
         <v>73</v>
       </c>
       <c r="K343" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>162</v>
+        <v>887</v>
       </c>
       <c r="N343" t="s" s="2">
-        <v>163</v>
+        <v>888</v>
       </c>
       <c r="O343" s="2"/>
       <c r="P343" s="2"/>
@@ -40265,7 +40312,7 @@
         <v>73</v>
       </c>
       <c r="AG343" t="s" s="2">
-        <v>164</v>
+        <v>886</v>
       </c>
       <c r="AH343" t="s" s="2">
         <v>74</v>
@@ -40274,53 +40321,53 @@
         <v>81</v>
       </c>
       <c r="AJ343" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK343" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F344" s="2"/>
       <c r="G344" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H344" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I344" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J344" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K344" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L344" t="s" s="2">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="M344" t="s" s="2">
-        <v>128</v>
+        <v>890</v>
       </c>
       <c r="N344" t="s" s="2">
-        <v>167</v>
+        <v>891</v>
       </c>
       <c r="O344" t="s" s="2">
-        <v>130</v>
+        <v>892</v>
       </c>
       <c r="P344" s="2"/>
       <c r="Q344" t="s" s="2">
@@ -40346,54 +40393,54 @@
         <v>73</v>
       </c>
       <c r="Y344" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z344" t="s" s="2">
-        <v>73</v>
+        <v>893</v>
       </c>
       <c r="AA344" t="s" s="2">
-        <v>73</v>
+        <v>894</v>
       </c>
       <c r="AB344" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AC344" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD344" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AE344" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF344" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="AG344" t="s" s="2">
-        <v>171</v>
+        <v>889</v>
       </c>
       <c r="AH344" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI344" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ344" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK344" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -40401,7 +40448,7 @@
       </c>
       <c r="F345" s="2"/>
       <c r="G345" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H345" t="s" s="2">
         <v>81</v>
@@ -40416,16 +40463,16 @@
         <v>82</v>
       </c>
       <c r="L345" t="s" s="2">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="M345" t="s" s="2">
-        <v>174</v>
+        <v>896</v>
       </c>
       <c r="N345" t="s" s="2">
-        <v>175</v>
+        <v>897</v>
       </c>
       <c r="O345" t="s" s="2">
-        <v>176</v>
+        <v>898</v>
       </c>
       <c r="P345" s="2"/>
       <c r="Q345" t="s" s="2">
@@ -40451,13 +40498,11 @@
         <v>73</v>
       </c>
       <c r="Y345" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z345" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="Z345" s="2"/>
       <c r="AA345" t="s" s="2">
-        <v>73</v>
+        <v>899</v>
       </c>
       <c r="AB345" t="s" s="2">
         <v>73</v>
@@ -40475,7 +40520,7 @@
         <v>73</v>
       </c>
       <c r="AG345" t="s" s="2">
-        <v>177</v>
+        <v>895</v>
       </c>
       <c r="AH345" t="s" s="2">
         <v>74</v>
@@ -40484,7 +40529,7 @@
         <v>81</v>
       </c>
       <c r="AJ345" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="AK345" t="s" s="2">
         <v>93</v>
@@ -40492,13 +40537,13 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
@@ -40506,7 +40551,7 @@
       </c>
       <c r="F346" s="2"/>
       <c r="G346" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H346" t="s" s="2">
         <v>81</v>
@@ -40521,18 +40566,18 @@
         <v>82</v>
       </c>
       <c r="L346" t="s" s="2">
-        <v>95</v>
+        <v>726</v>
       </c>
       <c r="M346" t="s" s="2">
-        <v>180</v>
+        <v>901</v>
       </c>
       <c r="N346" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O346" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="P346" s="2"/>
+        <v>902</v>
+      </c>
+      <c r="O346" s="2"/>
+      <c r="P346" t="s" s="2">
+        <v>903</v>
+      </c>
       <c r="Q346" t="s" s="2">
         <v>73</v>
       </c>
@@ -40556,13 +40601,13 @@
         <v>73</v>
       </c>
       <c r="Y346" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z346" t="s" s="2">
-        <v>184</v>
+        <v>73</v>
       </c>
       <c r="AA346" t="s" s="2">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="AB346" t="s" s="2">
         <v>73</v>
@@ -40580,7 +40625,7 @@
         <v>73</v>
       </c>
       <c r="AG346" t="s" s="2">
-        <v>186</v>
+        <v>900</v>
       </c>
       <c r="AH346" t="s" s="2">
         <v>74</v>
@@ -40597,13 +40642,13 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>894</v>
+        <v>904</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>894</v>
+        <v>904</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
@@ -40611,7 +40656,7 @@
       </c>
       <c r="F347" s="2"/>
       <c r="G347" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H347" t="s" s="2">
         <v>81</v>
@@ -40623,20 +40668,18 @@
         <v>73</v>
       </c>
       <c r="K347" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L347" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="M347" t="s" s="2">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="N347" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O347" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O347" s="2"/>
       <c r="P347" s="2"/>
       <c r="Q347" t="s" s="2">
         <v>73</v>
@@ -40685,7 +40728,7 @@
         <v>73</v>
       </c>
       <c r="AG347" t="s" s="2">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="AH347" t="s" s="2">
         <v>74</v>
@@ -40694,32 +40737,32 @@
         <v>81</v>
       </c>
       <c r="AJ347" t="s" s="2">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="AK347" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F348" s="2"/>
       <c r="G348" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H348" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I348" t="s" s="2">
         <v>73</v>
@@ -40731,15 +40774,17 @@
         <v>73</v>
       </c>
       <c r="L348" t="s" s="2">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="M348" t="s" s="2">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="N348" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O348" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O348" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P348" s="2"/>
       <c r="Q348" t="s" s="2">
         <v>73</v>
@@ -40776,53 +40821,53 @@
         <v>73</v>
       </c>
       <c r="AC348" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD348" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE348" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF348" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG348" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AH348" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI348" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ348" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK348" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F349" s="2"/>
       <c r="G349" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H349" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I349" t="s" s="2">
         <v>73</v>
@@ -40831,19 +40876,19 @@
         <v>73</v>
       </c>
       <c r="K349" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L349" t="s" s="2">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="M349" t="s" s="2">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="N349" t="s" s="2">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="O349" t="s" s="2">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="P349" s="2"/>
       <c r="Q349" t="s" s="2">
@@ -40881,42 +40926,42 @@
         <v>73</v>
       </c>
       <c r="AC349" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD349" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AE349" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF349" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="AG349" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AH349" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI349" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ349" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="AK349" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>897</v>
+        <v>907</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>897</v>
+        <v>907</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
@@ -40933,26 +40978,24 @@
         <v>73</v>
       </c>
       <c r="J350" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K350" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L350" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="M350" t="s" s="2">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="N350" t="s" s="2">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="O350" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="P350" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="P350" s="2"/>
       <c r="Q350" t="s" s="2">
         <v>73</v>
       </c>
@@ -40976,13 +41019,13 @@
         <v>73</v>
       </c>
       <c r="Y350" t="s" s="2">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="Z350" t="s" s="2">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="AA350" t="s" s="2">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="AB350" t="s" s="2">
         <v>73</v>
@@ -41000,7 +41043,7 @@
         <v>73</v>
       </c>
       <c r="AG350" t="s" s="2">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="AH350" t="s" s="2">
         <v>74</v>
@@ -41017,13 +41060,13 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -41031,7 +41074,7 @@
       </c>
       <c r="F351" s="2"/>
       <c r="G351" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H351" t="s" s="2">
         <v>81</v>
@@ -41046,20 +41089,18 @@
         <v>82</v>
       </c>
       <c r="L351" t="s" s="2">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="M351" t="s" s="2">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="N351" t="s" s="2">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="O351" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="P351" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="P351" s="2"/>
       <c r="Q351" t="s" s="2">
         <v>73</v>
       </c>
@@ -41083,13 +41124,13 @@
         <v>73</v>
       </c>
       <c r="Y351" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z351" t="s" s="2">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="AA351" t="s" s="2">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="AB351" t="s" s="2">
         <v>73</v>
@@ -41107,7 +41148,7 @@
         <v>73</v>
       </c>
       <c r="AG351" t="s" s="2">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="AH351" t="s" s="2">
         <v>74</v>
@@ -41116,7 +41157,7 @@
         <v>81</v>
       </c>
       <c r="AJ351" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="AK351" t="s" s="2">
         <v>93</v>
@@ -41124,13 +41165,13 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
@@ -41138,7 +41179,7 @@
       </c>
       <c r="F352" s="2"/>
       <c r="G352" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H352" t="s" s="2">
         <v>81</v>
@@ -41150,23 +41191,19 @@
         <v>73</v>
       </c>
       <c r="K352" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L352" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M352" t="s" s="2">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="N352" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O352" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="P352" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O352" s="2"/>
+      <c r="P352" s="2"/>
       <c r="Q352" t="s" s="2">
         <v>73</v>
       </c>
@@ -41178,7 +41215,7 @@
         <v>73</v>
       </c>
       <c r="U352" t="s" s="2">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="V352" t="s" s="2">
         <v>73</v>
@@ -41190,11 +41227,13 @@
         <v>73</v>
       </c>
       <c r="Y352" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Z352" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z352" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA352" t="s" s="2">
-        <v>739</v>
+        <v>73</v>
       </c>
       <c r="AB352" t="s" s="2">
         <v>73</v>
@@ -41212,7 +41251,7 @@
         <v>73</v>
       </c>
       <c r="AG352" t="s" s="2">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="AH352" t="s" s="2">
         <v>74</v>
@@ -41221,32 +41260,32 @@
         <v>81</v>
       </c>
       <c r="AJ352" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK352" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F353" s="2"/>
       <c r="G353" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H353" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I353" t="s" s="2">
         <v>73</v>
@@ -41255,19 +41294,19 @@
         <v>73</v>
       </c>
       <c r="K353" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L353" t="s" s="2">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="M353" t="s" s="2">
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="N353" t="s" s="2">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="O353" t="s" s="2">
-        <v>223</v>
+        <v>130</v>
       </c>
       <c r="P353" s="2"/>
       <c r="Q353" t="s" s="2">
@@ -41281,7 +41320,7 @@
         <v>73</v>
       </c>
       <c r="U353" t="s" s="2">
-        <v>224</v>
+        <v>73</v>
       </c>
       <c r="V353" t="s" s="2">
         <v>73</v>
@@ -41305,42 +41344,42 @@
         <v>73</v>
       </c>
       <c r="AC353" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD353" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AE353" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF353" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="AG353" t="s" s="2">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="AH353" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI353" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ353" t="s" s="2">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="AK353" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" t="s" s="2">
@@ -41357,22 +41396,26 @@
         <v>73</v>
       </c>
       <c r="J354" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K354" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L354" t="s" s="2">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="M354" t="s" s="2">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="N354" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O354" s="2"/>
-      <c r="P354" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O354" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="P354" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="Q354" t="s" s="2">
         <v>73</v>
       </c>
@@ -41396,13 +41439,13 @@
         <v>73</v>
       </c>
       <c r="Y354" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z354" t="s" s="2">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="AA354" t="s" s="2">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="AB354" t="s" s="2">
         <v>73</v>
@@ -41420,7 +41463,7 @@
         <v>73</v>
       </c>
       <c r="AG354" t="s" s="2">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="AH354" t="s" s="2">
         <v>74</v>
@@ -41437,13 +41480,13 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -41466,18 +41509,20 @@
         <v>82</v>
       </c>
       <c r="L355" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="M355" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="N355" t="s" s="2">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="O355" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="P355" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="P355" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="Q355" t="s" s="2">
         <v>73</v>
       </c>
@@ -41501,13 +41546,13 @@
         <v>73</v>
       </c>
       <c r="Y355" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="Z355" t="s" s="2">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="AA355" t="s" s="2">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="AB355" t="s" s="2">
         <v>73</v>
@@ -41525,7 +41570,7 @@
         <v>73</v>
       </c>
       <c r="AG355" t="s" s="2">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="AH355" t="s" s="2">
         <v>74</v>
@@ -41542,13 +41587,13 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -41556,7 +41601,7 @@
       </c>
       <c r="F356" s="2"/>
       <c r="G356" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H356" t="s" s="2">
         <v>81</v>
@@ -41571,18 +41616,20 @@
         <v>82</v>
       </c>
       <c r="L356" t="s" s="2">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="M356" t="s" s="2">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="N356" t="s" s="2">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="O356" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="P356" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="P356" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="Q356" t="s" s="2">
         <v>73</v>
       </c>
@@ -41594,7 +41641,7 @@
         <v>73</v>
       </c>
       <c r="U356" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="V356" t="s" s="2">
         <v>73</v>
@@ -41606,13 +41653,11 @@
         <v>73</v>
       </c>
       <c r="Y356" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z356" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="Z356" s="2"/>
       <c r="AA356" t="s" s="2">
-        <v>73</v>
+        <v>739</v>
       </c>
       <c r="AB356" t="s" s="2">
         <v>73</v>
@@ -41630,7 +41675,7 @@
         <v>73</v>
       </c>
       <c r="AG356" t="s" s="2">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="AH356" t="s" s="2">
         <v>74</v>
@@ -41639,7 +41684,7 @@
         <v>81</v>
       </c>
       <c r="AJ356" t="s" s="2">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="AK356" t="s" s="2">
         <v>93</v>
@@ -41647,13 +41692,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -41661,7 +41706,7 @@
       </c>
       <c r="F357" s="2"/>
       <c r="G357" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H357" t="s" s="2">
         <v>81</v>
@@ -41676,15 +41721,17 @@
         <v>82</v>
       </c>
       <c r="L357" t="s" s="2">
-        <v>406</v>
+        <v>173</v>
       </c>
       <c r="M357" t="s" s="2">
-        <v>905</v>
+        <v>221</v>
       </c>
       <c r="N357" t="s" s="2">
-        <v>906</v>
-      </c>
-      <c r="O357" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O357" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P357" s="2"/>
       <c r="Q357" t="s" s="2">
         <v>73</v>
@@ -41697,7 +41744,7 @@
         <v>73</v>
       </c>
       <c r="U357" t="s" s="2">
-        <v>73</v>
+        <v>224</v>
       </c>
       <c r="V357" t="s" s="2">
         <v>73</v>
@@ -41733,7 +41780,7 @@
         <v>73</v>
       </c>
       <c r="AG357" t="s" s="2">
-        <v>904</v>
+        <v>225</v>
       </c>
       <c r="AH357" t="s" s="2">
         <v>74</v>
@@ -41742,7 +41789,7 @@
         <v>81</v>
       </c>
       <c r="AJ357" t="s" s="2">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="AK357" t="s" s="2">
         <v>93</v>
@@ -41750,13 +41797,13 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
@@ -41767,7 +41814,7 @@
         <v>74</v>
       </c>
       <c r="H358" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I358" t="s" s="2">
         <v>73</v>
@@ -41776,20 +41823,18 @@
         <v>73</v>
       </c>
       <c r="K358" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L358" t="s" s="2">
-        <v>811</v>
+        <v>152</v>
       </c>
       <c r="M358" t="s" s="2">
-        <v>908</v>
+        <v>228</v>
       </c>
       <c r="N358" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="O358" t="s" s="2">
-        <v>910</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="O358" s="2"/>
       <c r="P358" s="2"/>
       <c r="Q358" t="s" s="2">
         <v>73</v>
@@ -41838,13 +41883,13 @@
         <v>73</v>
       </c>
       <c r="AG358" t="s" s="2">
-        <v>907</v>
+        <v>230</v>
       </c>
       <c r="AH358" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI358" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ358" t="s" s="2">
         <v>73</v>
@@ -41855,13 +41900,13 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -41869,7 +41914,7 @@
       </c>
       <c r="F359" s="2"/>
       <c r="G359" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H359" t="s" s="2">
         <v>81</v>
@@ -41881,19 +41926,19 @@
         <v>73</v>
       </c>
       <c r="K359" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L359" t="s" s="2">
-        <v>632</v>
+        <v>232</v>
       </c>
       <c r="M359" t="s" s="2">
-        <v>912</v>
+        <v>233</v>
       </c>
       <c r="N359" t="s" s="2">
-        <v>913</v>
+        <v>234</v>
       </c>
       <c r="O359" t="s" s="2">
-        <v>914</v>
+        <v>235</v>
       </c>
       <c r="P359" s="2"/>
       <c r="Q359" t="s" s="2">
@@ -41943,13 +41988,13 @@
         <v>73</v>
       </c>
       <c r="AG359" t="s" s="2">
-        <v>911</v>
+        <v>236</v>
       </c>
       <c r="AH359" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI359" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ359" t="s" s="2">
         <v>73</v>
@@ -41960,13 +42005,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -41989,15 +42034,17 @@
         <v>82</v>
       </c>
       <c r="L360" t="s" s="2">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="M360" t="s" s="2">
-        <v>916</v>
+        <v>238</v>
       </c>
       <c r="N360" t="s" s="2">
-        <v>917</v>
-      </c>
-      <c r="O360" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O360" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P360" s="2"/>
       <c r="Q360" t="s" s="2">
         <v>73</v>
@@ -42022,13 +42069,13 @@
         <v>73</v>
       </c>
       <c r="Y360" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="Z360" t="s" s="2">
-        <v>918</v>
+        <v>73</v>
       </c>
       <c r="AA360" t="s" s="2">
-        <v>919</v>
+        <v>73</v>
       </c>
       <c r="AB360" t="s" s="2">
         <v>73</v>
@@ -42046,7 +42093,7 @@
         <v>73</v>
       </c>
       <c r="AG360" t="s" s="2">
-        <v>915</v>
+        <v>241</v>
       </c>
       <c r="AH360" t="s" s="2">
         <v>74</v>
@@ -42055,7 +42102,7 @@
         <v>81</v>
       </c>
       <c r="AJ360" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="AK360" t="s" s="2">
         <v>93</v>
@@ -42063,13 +42110,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -42080,7 +42127,7 @@
         <v>74</v>
       </c>
       <c r="H361" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I361" t="s" s="2">
         <v>73</v>
@@ -42089,16 +42136,16 @@
         <v>73</v>
       </c>
       <c r="K361" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L361" t="s" s="2">
-        <v>204</v>
+        <v>406</v>
       </c>
       <c r="M361" t="s" s="2">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="N361" t="s" s="2">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="O361" s="2"/>
       <c r="P361" s="2"/>
@@ -42125,13 +42172,13 @@
         <v>73</v>
       </c>
       <c r="Y361" t="s" s="2">
-        <v>272</v>
+        <v>73</v>
       </c>
       <c r="Z361" t="s" s="2">
-        <v>923</v>
+        <v>73</v>
       </c>
       <c r="AA361" t="s" s="2">
-        <v>924</v>
+        <v>73</v>
       </c>
       <c r="AB361" t="s" s="2">
         <v>73</v>
@@ -42149,13 +42196,13 @@
         <v>73</v>
       </c>
       <c r="AG361" t="s" s="2">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="AH361" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI361" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ361" t="s" s="2">
         <v>73</v>
@@ -42166,13 +42213,13 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -42195,15 +42242,17 @@
         <v>73</v>
       </c>
       <c r="L362" t="s" s="2">
-        <v>347</v>
+        <v>825</v>
       </c>
       <c r="M362" t="s" s="2">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="N362" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="O362" s="2"/>
+        <v>923</v>
+      </c>
+      <c r="O362" t="s" s="2">
+        <v>924</v>
+      </c>
       <c r="P362" s="2"/>
       <c r="Q362" t="s" s="2">
         <v>73</v>
@@ -42252,7 +42301,7 @@
         <v>73</v>
       </c>
       <c r="AG362" t="s" s="2">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="AH362" t="s" s="2">
         <v>74</v>
@@ -42269,13 +42318,13 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
@@ -42283,7 +42332,7 @@
       </c>
       <c r="F363" s="2"/>
       <c r="G363" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H363" t="s" s="2">
         <v>81</v>
@@ -42298,15 +42347,17 @@
         <v>73</v>
       </c>
       <c r="L363" t="s" s="2">
-        <v>173</v>
+        <v>632</v>
       </c>
       <c r="M363" t="s" s="2">
-        <v>162</v>
+        <v>926</v>
       </c>
       <c r="N363" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O363" s="2"/>
+        <v>927</v>
+      </c>
+      <c r="O363" t="s" s="2">
+        <v>928</v>
+      </c>
       <c r="P363" s="2"/>
       <c r="Q363" t="s" s="2">
         <v>73</v>
@@ -42355,24 +42406,24 @@
         <v>73</v>
       </c>
       <c r="AG363" t="s" s="2">
-        <v>164</v>
+        <v>925</v>
       </c>
       <c r="AH363" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI363" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ363" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK363" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B364" t="s" s="2">
         <v>929</v>
@@ -42382,14 +42433,14 @@
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F364" s="2"/>
       <c r="G364" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H364" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I364" t="s" s="2">
         <v>73</v>
@@ -42398,20 +42449,18 @@
         <v>73</v>
       </c>
       <c r="K364" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L364" t="s" s="2">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="M364" t="s" s="2">
-        <v>128</v>
+        <v>930</v>
       </c>
       <c r="N364" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O364" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>931</v>
+      </c>
+      <c r="O364" s="2"/>
       <c r="P364" s="2"/>
       <c r="Q364" t="s" s="2">
         <v>73</v>
@@ -42436,13 +42485,13 @@
         <v>73</v>
       </c>
       <c r="Y364" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="Z364" t="s" s="2">
-        <v>73</v>
+        <v>932</v>
       </c>
       <c r="AA364" t="s" s="2">
-        <v>73</v>
+        <v>933</v>
       </c>
       <c r="AB364" t="s" s="2">
         <v>73</v>
@@ -42460,34 +42509,34 @@
         <v>73</v>
       </c>
       <c r="AG364" t="s" s="2">
-        <v>171</v>
+        <v>929</v>
       </c>
       <c r="AH364" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI364" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ364" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK364" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F365" s="2"/>
       <c r="G365" t="s" s="2">
@@ -42500,26 +42549,22 @@
         <v>73</v>
       </c>
       <c r="J365" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K365" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L365" t="s" s="2">
-        <v>127</v>
+        <v>204</v>
       </c>
       <c r="M365" t="s" s="2">
-        <v>355</v>
+        <v>935</v>
       </c>
       <c r="N365" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O365" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P365" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>936</v>
+      </c>
+      <c r="O365" s="2"/>
+      <c r="P365" s="2"/>
       <c r="Q365" t="s" s="2">
         <v>73</v>
       </c>
@@ -42543,13 +42588,13 @@
         <v>73</v>
       </c>
       <c r="Y365" t="s" s="2">
-        <v>73</v>
+        <v>272</v>
       </c>
       <c r="Z365" t="s" s="2">
-        <v>73</v>
+        <v>937</v>
       </c>
       <c r="AA365" t="s" s="2">
-        <v>73</v>
+        <v>938</v>
       </c>
       <c r="AB365" t="s" s="2">
         <v>73</v>
@@ -42567,7 +42612,7 @@
         <v>73</v>
       </c>
       <c r="AG365" t="s" s="2">
-        <v>357</v>
+        <v>934</v>
       </c>
       <c r="AH365" t="s" s="2">
         <v>74</v>
@@ -42579,18 +42624,18 @@
         <v>73</v>
       </c>
       <c r="AK365" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
@@ -42598,10 +42643,10 @@
       </c>
       <c r="F366" s="2"/>
       <c r="G366" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H366" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I366" t="s" s="2">
         <v>73</v>
@@ -42613,13 +42658,13 @@
         <v>73</v>
       </c>
       <c r="L366" t="s" s="2">
-        <v>204</v>
+        <v>347</v>
       </c>
       <c r="M366" t="s" s="2">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="N366" t="s" s="2">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="O366" s="2"/>
       <c r="P366" s="2"/>
@@ -42646,13 +42691,13 @@
         <v>73</v>
       </c>
       <c r="Y366" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z366" t="s" s="2">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AA366" t="s" s="2">
-        <v>822</v>
+        <v>73</v>
       </c>
       <c r="AB366" t="s" s="2">
         <v>73</v>
@@ -42670,13 +42715,13 @@
         <v>73</v>
       </c>
       <c r="AG366" t="s" s="2">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="AH366" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI366" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ366" t="s" s="2">
         <v>73</v>
@@ -42687,13 +42732,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -42701,7 +42746,7 @@
       </c>
       <c r="F367" s="2"/>
       <c r="G367" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H367" t="s" s="2">
         <v>81</v>
@@ -42719,10 +42764,10 @@
         <v>173</v>
       </c>
       <c r="M367" t="s" s="2">
-        <v>935</v>
+        <v>162</v>
       </c>
       <c r="N367" t="s" s="2">
-        <v>936</v>
+        <v>163</v>
       </c>
       <c r="O367" s="2"/>
       <c r="P367" s="2"/>
@@ -42773,41 +42818,41 @@
         <v>73</v>
       </c>
       <c r="AG367" t="s" s="2">
-        <v>934</v>
+        <v>164</v>
       </c>
       <c r="AH367" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI367" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ367" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK367" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F368" s="2"/>
       <c r="G368" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H368" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I368" t="s" s="2">
         <v>73</v>
@@ -42819,15 +42864,17 @@
         <v>73</v>
       </c>
       <c r="L368" t="s" s="2">
-        <v>347</v>
+        <v>127</v>
       </c>
       <c r="M368" t="s" s="2">
-        <v>938</v>
+        <v>128</v>
       </c>
       <c r="N368" t="s" s="2">
-        <v>939</v>
-      </c>
-      <c r="O368" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O368" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P368" s="2"/>
       <c r="Q368" t="s" s="2">
         <v>73</v>
@@ -42876,62 +42923,66 @@
         <v>73</v>
       </c>
       <c r="AG368" t="s" s="2">
-        <v>937</v>
+        <v>171</v>
       </c>
       <c r="AH368" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI368" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ368" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK368" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F369" s="2"/>
       <c r="G369" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H369" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I369" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J369" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K369" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L369" t="s" s="2">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="M369" t="s" s="2">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="N369" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O369" s="2"/>
-      <c r="P369" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O369" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P369" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q369" t="s" s="2">
         <v>73</v>
       </c>
@@ -42979,41 +43030,41 @@
         <v>73</v>
       </c>
       <c r="AG369" t="s" s="2">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="AH369" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI369" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ369" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK369" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F370" s="2"/>
       <c r="G370" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H370" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I370" t="s" s="2">
         <v>73</v>
@@ -43025,17 +43076,15 @@
         <v>73</v>
       </c>
       <c r="L370" t="s" s="2">
-        <v>127</v>
+        <v>204</v>
       </c>
       <c r="M370" t="s" s="2">
-        <v>128</v>
+        <v>946</v>
       </c>
       <c r="N370" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O370" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>947</v>
+      </c>
+      <c r="O370" s="2"/>
       <c r="P370" s="2"/>
       <c r="Q370" t="s" s="2">
         <v>73</v>
@@ -43060,13 +43109,13 @@
         <v>73</v>
       </c>
       <c r="Y370" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z370" t="s" s="2">
-        <v>73</v>
+        <v>835</v>
       </c>
       <c r="AA370" t="s" s="2">
-        <v>73</v>
+        <v>836</v>
       </c>
       <c r="AB370" t="s" s="2">
         <v>73</v>
@@ -43084,66 +43133,62 @@
         <v>73</v>
       </c>
       <c r="AG370" t="s" s="2">
-        <v>171</v>
+        <v>945</v>
       </c>
       <c r="AH370" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AI370" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ370" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK370" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F371" s="2"/>
       <c r="G371" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H371" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I371" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J371" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K371" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L371" t="s" s="2">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="M371" t="s" s="2">
-        <v>355</v>
+        <v>949</v>
       </c>
       <c r="N371" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O371" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P371" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>950</v>
+      </c>
+      <c r="O371" s="2"/>
+      <c r="P371" s="2"/>
       <c r="Q371" t="s" s="2">
         <v>73</v>
       </c>
@@ -43191,30 +43236,30 @@
         <v>73</v>
       </c>
       <c r="AG371" t="s" s="2">
-        <v>357</v>
+        <v>948</v>
       </c>
       <c r="AH371" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AI371" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ371" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK371" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -43222,7 +43267,7 @@
       </c>
       <c r="F372" s="2"/>
       <c r="G372" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H372" t="s" s="2">
         <v>81</v>
@@ -43234,16 +43279,16 @@
         <v>73</v>
       </c>
       <c r="K372" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L372" t="s" s="2">
-        <v>944</v>
+        <v>347</v>
       </c>
       <c r="M372" t="s" s="2">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="N372" t="s" s="2">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="O372" s="2"/>
       <c r="P372" s="2"/>
@@ -43294,7 +43339,7 @@
         <v>73</v>
       </c>
       <c r="AG372" t="s" s="2">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="AH372" t="s" s="2">
         <v>74</v>
@@ -43311,13 +43356,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="D373" s="2"/>
       <c r="E373" t="s" s="2">
@@ -43325,7 +43370,7 @@
       </c>
       <c r="F373" s="2"/>
       <c r="G373" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H373" t="s" s="2">
         <v>81</v>
@@ -43337,16 +43382,16 @@
         <v>73</v>
       </c>
       <c r="K373" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L373" t="s" s="2">
-        <v>406</v>
+        <v>173</v>
       </c>
       <c r="M373" t="s" s="2">
-        <v>948</v>
+        <v>162</v>
       </c>
       <c r="N373" t="s" s="2">
-        <v>949</v>
+        <v>163</v>
       </c>
       <c r="O373" s="2"/>
       <c r="P373" s="2"/>
@@ -43397,7 +43442,7 @@
         <v>73</v>
       </c>
       <c r="AG373" t="s" s="2">
-        <v>947</v>
+        <v>164</v>
       </c>
       <c r="AH373" t="s" s="2">
         <v>74</v>
@@ -43406,32 +43451,32 @@
         <v>81</v>
       </c>
       <c r="AJ373" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK373" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F374" s="2"/>
       <c r="G374" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H374" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I374" t="s" s="2">
         <v>73</v>
@@ -43440,18 +43485,20 @@
         <v>73</v>
       </c>
       <c r="K374" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L374" t="s" s="2">
-        <v>521</v>
+        <v>127</v>
       </c>
       <c r="M374" t="s" s="2">
-        <v>951</v>
+        <v>128</v>
       </c>
       <c r="N374" t="s" s="2">
-        <v>952</v>
-      </c>
-      <c r="O374" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O374" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P374" s="2"/>
       <c r="Q374" t="s" s="2">
         <v>73</v>
@@ -43500,62 +43547,66 @@
         <v>73</v>
       </c>
       <c r="AG374" t="s" s="2">
-        <v>950</v>
+        <v>171</v>
       </c>
       <c r="AH374" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI374" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ374" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK374" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F375" s="2"/>
       <c r="G375" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H375" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I375" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J375" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K375" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L375" t="s" s="2">
-        <v>954</v>
+        <v>127</v>
       </c>
       <c r="M375" t="s" s="2">
-        <v>955</v>
+        <v>355</v>
       </c>
       <c r="N375" t="s" s="2">
-        <v>956</v>
-      </c>
-      <c r="O375" s="2"/>
-      <c r="P375" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O375" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P375" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q375" t="s" s="2">
         <v>73</v>
       </c>
@@ -43603,24 +43654,24 @@
         <v>73</v>
       </c>
       <c r="AG375" t="s" s="2">
-        <v>953</v>
+        <v>357</v>
       </c>
       <c r="AH375" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI375" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ375" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK375" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B376" t="s" s="2">
         <v>957</v>
@@ -43646,16 +43697,16 @@
         <v>73</v>
       </c>
       <c r="K376" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L376" t="s" s="2">
-        <v>204</v>
+        <v>958</v>
       </c>
       <c r="M376" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="N376" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="O376" s="2"/>
       <c r="P376" s="2"/>
@@ -43682,13 +43733,13 @@
         <v>73</v>
       </c>
       <c r="Y376" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z376" t="s" s="2">
-        <v>960</v>
+        <v>73</v>
       </c>
       <c r="AA376" t="s" s="2">
-        <v>961</v>
+        <v>73</v>
       </c>
       <c r="AB376" t="s" s="2">
         <v>73</v>
@@ -43723,13 +43774,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -43737,7 +43788,7 @@
       </c>
       <c r="F377" s="2"/>
       <c r="G377" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H377" t="s" s="2">
         <v>81</v>
@@ -43749,16 +43800,16 @@
         <v>73</v>
       </c>
       <c r="K377" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L377" t="s" s="2">
-        <v>544</v>
+        <v>406</v>
       </c>
       <c r="M377" t="s" s="2">
+        <v>962</v>
+      </c>
+      <c r="N377" t="s" s="2">
         <v>963</v>
-      </c>
-      <c r="N377" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="O377" s="2"/>
       <c r="P377" s="2"/>
@@ -43785,10 +43836,10 @@
         <v>73</v>
       </c>
       <c r="Y377" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z377" t="s" s="2">
-        <v>964</v>
+        <v>73</v>
       </c>
       <c r="AA377" t="s" s="2">
         <v>73</v>
@@ -43809,7 +43860,7 @@
         <v>73</v>
       </c>
       <c r="AG377" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="AH377" t="s" s="2">
         <v>74</v>
@@ -43826,13 +43877,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -43852,16 +43903,16 @@
         <v>73</v>
       </c>
       <c r="K378" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L378" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M378" t="s" s="2">
+        <v>965</v>
+      </c>
+      <c r="N378" t="s" s="2">
         <v>966</v>
-      </c>
-      <c r="M378" t="s" s="2">
-        <v>967</v>
-      </c>
-      <c r="N378" t="s" s="2">
-        <v>968</v>
       </c>
       <c r="O378" s="2"/>
       <c r="P378" s="2"/>
@@ -43912,7 +43963,7 @@
         <v>73</v>
       </c>
       <c r="AG378" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="AH378" t="s" s="2">
         <v>74</v>
@@ -43929,13 +43980,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -43958,17 +44009,15 @@
         <v>73</v>
       </c>
       <c r="L379" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="M379" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="N379" t="s" s="2">
         <v>970</v>
       </c>
-      <c r="M379" t="s" s="2">
-        <v>971</v>
-      </c>
-      <c r="N379" t="s" s="2">
-        <v>972</v>
-      </c>
-      <c r="O379" t="s" s="2">
-        <v>973</v>
-      </c>
+      <c r="O379" s="2"/>
       <c r="P379" s="2"/>
       <c r="Q379" t="s" s="2">
         <v>73</v>
@@ -43993,13 +44042,13 @@
         <v>73</v>
       </c>
       <c r="Y379" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z379" t="s" s="2">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AA379" t="s" s="2">
-        <v>822</v>
+        <v>73</v>
       </c>
       <c r="AB379" t="s" s="2">
         <v>73</v>
@@ -44017,7 +44066,7 @@
         <v>73</v>
       </c>
       <c r="AG379" t="s" s="2">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="AH379" t="s" s="2">
         <v>74</v>
@@ -44034,13 +44083,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -44060,23 +44109,19 @@
         <v>73</v>
       </c>
       <c r="K380" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L380" t="s" s="2">
-        <v>975</v>
+        <v>204</v>
       </c>
       <c r="M380" t="s" s="2">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="N380" t="s" s="2">
-        <v>977</v>
-      </c>
-      <c r="O380" t="s" s="2">
-        <v>978</v>
-      </c>
-      <c r="P380" t="s" s="2">
-        <v>979</v>
-      </c>
+        <v>973</v>
+      </c>
+      <c r="O380" s="2"/>
+      <c r="P380" s="2"/>
       <c r="Q380" t="s" s="2">
         <v>73</v>
       </c>
@@ -44100,13 +44145,13 @@
         <v>73</v>
       </c>
       <c r="Y380" t="s" s="2">
-        <v>183</v>
+        <v>265</v>
       </c>
       <c r="Z380" t="s" s="2">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="AA380" t="s" s="2">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="AB380" t="s" s="2">
         <v>73</v>
@@ -44124,7 +44169,7 @@
         <v>73</v>
       </c>
       <c r="AG380" t="s" s="2">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="AH380" t="s" s="2">
         <v>74</v>
@@ -44141,13 +44186,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -44158,7 +44203,7 @@
         <v>74</v>
       </c>
       <c r="H381" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I381" t="s" s="2">
         <v>73</v>
@@ -44170,13 +44215,13 @@
         <v>73</v>
       </c>
       <c r="L381" t="s" s="2">
-        <v>347</v>
+        <v>544</v>
       </c>
       <c r="M381" t="s" s="2">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="N381" t="s" s="2">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="O381" s="2"/>
       <c r="P381" s="2"/>
@@ -44203,10 +44248,10 @@
         <v>73</v>
       </c>
       <c r="Y381" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z381" t="s" s="2">
-        <v>73</v>
+        <v>978</v>
       </c>
       <c r="AA381" t="s" s="2">
         <v>73</v>
@@ -44227,13 +44272,13 @@
         <v>73</v>
       </c>
       <c r="AG381" t="s" s="2">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="AH381" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI381" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ381" t="s" s="2">
         <v>73</v>
@@ -44244,13 +44289,13 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" t="s" s="2">
@@ -44273,13 +44318,13 @@
         <v>73</v>
       </c>
       <c r="L382" t="s" s="2">
-        <v>173</v>
+        <v>980</v>
       </c>
       <c r="M382" t="s" s="2">
-        <v>162</v>
+        <v>981</v>
       </c>
       <c r="N382" t="s" s="2">
-        <v>163</v>
+        <v>982</v>
       </c>
       <c r="O382" s="2"/>
       <c r="P382" s="2"/>
@@ -44330,7 +44375,7 @@
         <v>73</v>
       </c>
       <c r="AG382" t="s" s="2">
-        <v>164</v>
+        <v>979</v>
       </c>
       <c r="AH382" t="s" s="2">
         <v>74</v>
@@ -44339,32 +44384,32 @@
         <v>81</v>
       </c>
       <c r="AJ382" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK382" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F383" s="2"/>
       <c r="G383" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H383" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I383" t="s" s="2">
         <v>73</v>
@@ -44376,16 +44421,16 @@
         <v>73</v>
       </c>
       <c r="L383" t="s" s="2">
-        <v>127</v>
+        <v>984</v>
       </c>
       <c r="M383" t="s" s="2">
-        <v>128</v>
+        <v>985</v>
       </c>
       <c r="N383" t="s" s="2">
-        <v>167</v>
+        <v>986</v>
       </c>
       <c r="O383" t="s" s="2">
-        <v>130</v>
+        <v>987</v>
       </c>
       <c r="P383" s="2"/>
       <c r="Q383" t="s" s="2">
@@ -44411,13 +44456,13 @@
         <v>73</v>
       </c>
       <c r="Y383" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z383" t="s" s="2">
-        <v>73</v>
+        <v>835</v>
       </c>
       <c r="AA383" t="s" s="2">
-        <v>73</v>
+        <v>836</v>
       </c>
       <c r="AB383" t="s" s="2">
         <v>73</v>
@@ -44435,65 +44480,65 @@
         <v>73</v>
       </c>
       <c r="AG383" t="s" s="2">
-        <v>171</v>
+        <v>983</v>
       </c>
       <c r="AH383" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI383" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ383" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK383" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F384" s="2"/>
       <c r="G384" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H384" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I384" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J384" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K384" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L384" t="s" s="2">
-        <v>127</v>
+        <v>989</v>
       </c>
       <c r="M384" t="s" s="2">
-        <v>355</v>
+        <v>990</v>
       </c>
       <c r="N384" t="s" s="2">
-        <v>356</v>
+        <v>991</v>
       </c>
       <c r="O384" t="s" s="2">
-        <v>130</v>
+        <v>992</v>
       </c>
       <c r="P384" t="s" s="2">
-        <v>136</v>
+        <v>993</v>
       </c>
       <c r="Q384" t="s" s="2">
         <v>73</v>
@@ -44518,13 +44563,13 @@
         <v>73</v>
       </c>
       <c r="Y384" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="Z384" t="s" s="2">
-        <v>73</v>
+        <v>994</v>
       </c>
       <c r="AA384" t="s" s="2">
-        <v>73</v>
+        <v>995</v>
       </c>
       <c r="AB384" t="s" s="2">
         <v>73</v>
@@ -44542,30 +44587,30 @@
         <v>73</v>
       </c>
       <c r="AG384" t="s" s="2">
-        <v>357</v>
+        <v>988</v>
       </c>
       <c r="AH384" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI384" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ384" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK384" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -44576,7 +44621,7 @@
         <v>74</v>
       </c>
       <c r="H385" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I385" t="s" s="2">
         <v>73</v>
@@ -44588,13 +44633,13 @@
         <v>73</v>
       </c>
       <c r="L385" t="s" s="2">
-        <v>173</v>
+        <v>347</v>
       </c>
       <c r="M385" t="s" s="2">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="N385" t="s" s="2">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="O385" s="2"/>
       <c r="P385" s="2"/>
@@ -44645,13 +44690,13 @@
         <v>73</v>
       </c>
       <c r="AG385" t="s" s="2">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="AH385" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI385" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ385" t="s" s="2">
         <v>73</v>
@@ -44662,13 +44707,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" t="s" s="2">
@@ -44691,13 +44736,13 @@
         <v>73</v>
       </c>
       <c r="L386" t="s" s="2">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="M386" t="s" s="2">
-        <v>992</v>
+        <v>162</v>
       </c>
       <c r="N386" t="s" s="2">
-        <v>993</v>
+        <v>163</v>
       </c>
       <c r="O386" s="2"/>
       <c r="P386" s="2"/>
@@ -44724,13 +44769,13 @@
         <v>73</v>
       </c>
       <c r="Y386" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Z386" t="s" s="2">
-        <v>994</v>
+        <v>73</v>
       </c>
       <c r="AA386" t="s" s="2">
-        <v>995</v>
+        <v>73</v>
       </c>
       <c r="AB386" t="s" s="2">
         <v>73</v>
@@ -44748,7 +44793,7 @@
         <v>73</v>
       </c>
       <c r="AG386" t="s" s="2">
-        <v>991</v>
+        <v>164</v>
       </c>
       <c r="AH386" t="s" s="2">
         <v>74</v>
@@ -44757,25 +44802,25 @@
         <v>81</v>
       </c>
       <c r="AJ386" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK386" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F387" s="2"/>
       <c r="G387" t="s" s="2">
@@ -44794,15 +44839,17 @@
         <v>73</v>
       </c>
       <c r="L387" t="s" s="2">
-        <v>997</v>
+        <v>127</v>
       </c>
       <c r="M387" t="s" s="2">
-        <v>998</v>
+        <v>128</v>
       </c>
       <c r="N387" t="s" s="2">
-        <v>999</v>
-      </c>
-      <c r="O387" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O387" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P387" s="2"/>
       <c r="Q387" t="s" s="2">
         <v>73</v>
@@ -44851,7 +44898,7 @@
         <v>73</v>
       </c>
       <c r="AG387" t="s" s="2">
-        <v>996</v>
+        <v>171</v>
       </c>
       <c r="AH387" t="s" s="2">
         <v>74</v>
@@ -44863,50 +44910,54 @@
         <v>73</v>
       </c>
       <c r="AK387" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F388" s="2"/>
       <c r="G388" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H388" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I388" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J388" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K388" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L388" t="s" s="2">
-        <v>1001</v>
+        <v>127</v>
       </c>
       <c r="M388" t="s" s="2">
-        <v>1002</v>
+        <v>355</v>
       </c>
       <c r="N388" t="s" s="2">
-        <v>1003</v>
-      </c>
-      <c r="O388" s="2"/>
-      <c r="P388" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O388" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P388" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q388" t="s" s="2">
         <v>73</v>
       </c>
@@ -44954,30 +45005,30 @@
         <v>73</v>
       </c>
       <c r="AG388" t="s" s="2">
-        <v>1000</v>
+        <v>357</v>
       </c>
       <c r="AH388" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI388" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ388" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK388" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -44985,10 +45036,10 @@
       </c>
       <c r="F389" s="2"/>
       <c r="G389" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H389" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I389" t="s" s="2">
         <v>73</v>
@@ -45000,13 +45051,13 @@
         <v>73</v>
       </c>
       <c r="L389" t="s" s="2">
-        <v>347</v>
+        <v>173</v>
       </c>
       <c r="M389" t="s" s="2">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="N389" t="s" s="2">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="O389" s="2"/>
       <c r="P389" s="2"/>
@@ -45057,13 +45108,13 @@
         <v>73</v>
       </c>
       <c r="AG389" t="s" s="2">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="AH389" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI389" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ389" t="s" s="2">
         <v>73</v>
@@ -45074,13 +45125,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
@@ -45103,13 +45154,13 @@
         <v>73</v>
       </c>
       <c r="L390" t="s" s="2">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="M390" t="s" s="2">
-        <v>162</v>
+        <v>1006</v>
       </c>
       <c r="N390" t="s" s="2">
-        <v>163</v>
+        <v>1007</v>
       </c>
       <c r="O390" s="2"/>
       <c r="P390" s="2"/>
@@ -45136,13 +45187,13 @@
         <v>73</v>
       </c>
       <c r="Y390" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Z390" t="s" s="2">
-        <v>73</v>
+        <v>1008</v>
       </c>
       <c r="AA390" t="s" s="2">
-        <v>73</v>
+        <v>1009</v>
       </c>
       <c r="AB390" t="s" s="2">
         <v>73</v>
@@ -45160,7 +45211,7 @@
         <v>73</v>
       </c>
       <c r="AG390" t="s" s="2">
-        <v>164</v>
+        <v>1005</v>
       </c>
       <c r="AH390" t="s" s="2">
         <v>74</v>
@@ -45169,25 +45220,25 @@
         <v>81</v>
       </c>
       <c r="AJ390" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AK390" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F391" s="2"/>
       <c r="G391" t="s" s="2">
@@ -45206,17 +45257,15 @@
         <v>73</v>
       </c>
       <c r="L391" t="s" s="2">
-        <v>127</v>
+        <v>1011</v>
       </c>
       <c r="M391" t="s" s="2">
-        <v>128</v>
+        <v>1012</v>
       </c>
       <c r="N391" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O391" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>1013</v>
+      </c>
+      <c r="O391" s="2"/>
       <c r="P391" s="2"/>
       <c r="Q391" t="s" s="2">
         <v>73</v>
@@ -45265,7 +45314,7 @@
         <v>73</v>
       </c>
       <c r="AG391" t="s" s="2">
-        <v>171</v>
+        <v>1010</v>
       </c>
       <c r="AH391" t="s" s="2">
         <v>74</v>
@@ -45277,54 +45326,50 @@
         <v>73</v>
       </c>
       <c r="AK391" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" t="s" s="2">
-        <v>354</v>
+        <v>73</v>
       </c>
       <c r="F392" s="2"/>
       <c r="G392" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H392" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I392" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J392" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K392" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L392" t="s" s="2">
-        <v>127</v>
+        <v>1015</v>
       </c>
       <c r="M392" t="s" s="2">
-        <v>355</v>
+        <v>1016</v>
       </c>
       <c r="N392" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O392" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P392" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>1017</v>
+      </c>
+      <c r="O392" s="2"/>
+      <c r="P392" s="2"/>
       <c r="Q392" t="s" s="2">
         <v>73</v>
       </c>
@@ -45372,30 +45417,30 @@
         <v>73</v>
       </c>
       <c r="AG392" t="s" s="2">
-        <v>357</v>
+        <v>1014</v>
       </c>
       <c r="AH392" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI392" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ392" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK392" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" t="s" s="2">
@@ -45406,7 +45451,7 @@
         <v>81</v>
       </c>
       <c r="H393" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I393" t="s" s="2">
         <v>73</v>
@@ -45418,13 +45463,13 @@
         <v>73</v>
       </c>
       <c r="L393" t="s" s="2">
-        <v>557</v>
+        <v>347</v>
       </c>
       <c r="M393" t="s" s="2">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="N393" t="s" s="2">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="O393" s="2"/>
       <c r="P393" s="2"/>
@@ -45475,13 +45520,13 @@
         <v>73</v>
       </c>
       <c r="AG393" t="s" s="2">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="AH393" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI393" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ393" t="s" s="2">
         <v>73</v>
@@ -45492,13 +45537,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" t="s" s="2">
@@ -45521,13 +45566,13 @@
         <v>73</v>
       </c>
       <c r="L394" t="s" s="2">
-        <v>276</v>
+        <v>173</v>
       </c>
       <c r="M394" t="s" s="2">
-        <v>1014</v>
+        <v>162</v>
       </c>
       <c r="N394" t="s" s="2">
-        <v>1015</v>
+        <v>163</v>
       </c>
       <c r="O394" s="2"/>
       <c r="P394" s="2"/>
@@ -45578,7 +45623,7 @@
         <v>73</v>
       </c>
       <c r="AG394" t="s" s="2">
-        <v>1013</v>
+        <v>164</v>
       </c>
       <c r="AH394" t="s" s="2">
         <v>74</v>
@@ -45587,32 +45632,32 @@
         <v>81</v>
       </c>
       <c r="AJ394" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AK394" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F395" s="2"/>
       <c r="G395" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H395" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I395" t="s" s="2">
         <v>73</v>
@@ -45624,15 +45669,17 @@
         <v>73</v>
       </c>
       <c r="L395" t="s" s="2">
-        <v>954</v>
+        <v>127</v>
       </c>
       <c r="M395" t="s" s="2">
-        <v>1017</v>
+        <v>128</v>
       </c>
       <c r="N395" t="s" s="2">
-        <v>1018</v>
-      </c>
-      <c r="O395" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O395" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P395" s="2"/>
       <c r="Q395" t="s" s="2">
         <v>73</v>
@@ -45681,34 +45728,34 @@
         <v>73</v>
       </c>
       <c r="AG395" t="s" s="2">
-        <v>1016</v>
+        <v>171</v>
       </c>
       <c r="AH395" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI395" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ395" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK395" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
-        <v>73</v>
+        <v>354</v>
       </c>
       <c r="F396" s="2"/>
       <c r="G396" t="s" s="2">
@@ -45721,25 +45768,25 @@
         <v>73</v>
       </c>
       <c r="J396" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K396" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L396" t="s" s="2">
-        <v>204</v>
+        <v>127</v>
       </c>
       <c r="M396" t="s" s="2">
-        <v>1020</v>
+        <v>355</v>
       </c>
       <c r="N396" t="s" s="2">
-        <v>1021</v>
+        <v>356</v>
       </c>
       <c r="O396" t="s" s="2">
-        <v>1022</v>
+        <v>130</v>
       </c>
       <c r="P396" t="s" s="2">
-        <v>1023</v>
+        <v>136</v>
       </c>
       <c r="Q396" t="s" s="2">
         <v>73</v>
@@ -45764,13 +45811,13 @@
         <v>73</v>
       </c>
       <c r="Y396" t="s" s="2">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="Z396" t="s" s="2">
-        <v>1024</v>
+        <v>73</v>
       </c>
       <c r="AA396" t="s" s="2">
-        <v>1025</v>
+        <v>73</v>
       </c>
       <c r="AB396" t="s" s="2">
         <v>73</v>
@@ -45788,7 +45835,7 @@
         <v>73</v>
       </c>
       <c r="AG396" t="s" s="2">
-        <v>1019</v>
+        <v>357</v>
       </c>
       <c r="AH396" t="s" s="2">
         <v>74</v>
@@ -45800,18 +45847,18 @@
         <v>73</v>
       </c>
       <c r="AK396" t="s" s="2">
-        <v>93</v>
+        <v>132</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" t="s" s="2">
@@ -45819,10 +45866,10 @@
       </c>
       <c r="F397" s="2"/>
       <c r="G397" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H397" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I397" t="s" s="2">
         <v>73</v>
@@ -45834,13 +45881,13 @@
         <v>73</v>
       </c>
       <c r="L397" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="M397" t="s" s="2">
-        <v>50</v>
+        <v>1025</v>
       </c>
       <c r="N397" t="s" s="2">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="O397" s="2"/>
       <c r="P397" s="2"/>
@@ -45891,18 +45938,434 @@
         <v>73</v>
       </c>
       <c r="AG397" t="s" s="2">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="AH397" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AI397" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ397" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK397" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B398" t="s" s="2">
+        <v>1027</v>
+      </c>
+      <c r="C398" t="s" s="2">
+        <v>1027</v>
+      </c>
+      <c r="D398" s="2"/>
+      <c r="E398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F398" s="2"/>
+      <c r="G398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H398" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L398" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M398" t="s" s="2">
+        <v>1028</v>
+      </c>
+      <c r="N398" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="O398" s="2"/>
+      <c r="P398" s="2"/>
+      <c r="Q398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R398" s="2"/>
+      <c r="S398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG398" t="s" s="2">
+        <v>1027</v>
+      </c>
+      <c r="AH398" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI398" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ398" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK398" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B399" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="C399" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D399" s="2"/>
+      <c r="E399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F399" s="2"/>
+      <c r="G399" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H399" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L399" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="M399" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="N399" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="O399" s="2"/>
+      <c r="P399" s="2"/>
+      <c r="Q399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R399" s="2"/>
+      <c r="S399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG399" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="AH399" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI399" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ399" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK399" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B400" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="C400" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="D400" s="2"/>
+      <c r="E400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F400" s="2"/>
+      <c r="G400" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H400" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AJ397" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK397" t="s" s="2">
+      <c r="I400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K400" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L400" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M400" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="N400" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="O400" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="P400" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="Q400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R400" s="2"/>
+      <c r="S400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y400" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z400" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AA400" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="AB400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG400" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="AH400" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI400" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ400" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK400" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B401" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="C401" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="D401" s="2"/>
+      <c r="E401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F401" s="2"/>
+      <c r="G401" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H401" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L401" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M401" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="N401" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="O401" s="2"/>
+      <c r="P401" s="2"/>
+      <c r="Q401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R401" s="2"/>
+      <c r="S401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG401" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="AH401" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI401" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ401" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK401" t="s" s="2">
         <v>93</v>
       </c>
     </row>
